--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Korolkova\Модус\Дабл Харт\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Documents\Codex\2026-09-22\new-chat\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{7507C5CA-7790-4149-A3F2-DC57AF24E95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AF33A1-72F4-4E08-8AD1-199E0154AA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="153">
   <si>
     <t>№ п/п</t>
   </si>
@@ -467,10 +466,6 @@
     <t>Работы выполнняютсся. Ожидаемый срок завершения - 23-24.09.26</t>
   </si>
   <si>
-    <t>планируемый срок завершения - 24.09.26
-(Необходимо предоставить строительные леса)</t>
-  </si>
-  <si>
     <t>Подключение и маркировка:</t>
   </si>
   <si>
@@ -485,6 +480,48 @@
   </si>
   <si>
     <t>Подливка фланцев колонн зоны стрелки техобслуживания и треков зоны техобслуживания</t>
+  </si>
+  <si>
+    <t>по состоянию на 24.09</t>
+  </si>
+  <si>
+    <t>не приступили. Начало работ планируется 30.09.26
+(после заврешения работ по регулировки стрелки тех.обслуживания)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">планируемый срок завершения - 24.09.26
+</t>
+  </si>
+  <si>
+    <t>не заверешено. Идет процесс выверения отклонений. Планируемый срок заврешения - 29.09.26
+у Замперла запрошена проектная документация для передачи в Модус во избежание бесконечных подвижек</t>
+  </si>
+  <si>
+    <t>приступят к началу выполнения работ через 7 дней после завершения п.1.5</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">выполнено/done
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>питание не подавать пока не будет высушено помещение и шкафы</t>
+    </r>
+  </si>
+  <si>
+    <t>23.09.26
+выполнено/done</t>
+  </si>
+  <si>
+    <t>приступили 23.09.26</t>
   </si>
 </sst>
 </file>
@@ -494,7 +531,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,6 +542,8 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
@@ -539,6 +578,8 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -592,15 +633,8 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -616,12 +650,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -698,8 +726,260 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -708,308 +988,44 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1226,1104 +1242,1193 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:R33"/>
+  <dimension ref="A2:T33"/>
   <sheetFormatPr defaultRowHeight="15.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.453125" customWidth="1"/>
-    <col min="2" max="2" width="61.36328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="0.90625" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="51.453125" style="22" customWidth="1"/>
+    <col min="1" max="1" width="6.6328125" customWidth="1"/>
+    <col min="2" max="2" width="46.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="51.26953125" hidden="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="51.453125" style="15" customWidth="1"/>
     <col min="5" max="5" width="15.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.36328125" style="16" customWidth="1"/>
+    <col min="6" max="6" width="29.36328125" style="11" customWidth="1"/>
     <col min="7" max="7" width="13.6328125" customWidth="1"/>
-    <col min="8" max="8" width="15" style="9" customWidth="1"/>
-    <col min="9" max="9" width="17.08984375" style="9" customWidth="1"/>
-    <col min="10" max="10" width="15" style="9" customWidth="1"/>
-    <col min="11" max="11" width="29.36328125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="15.08984375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="29.7265625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="20.7265625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="24.08984375" style="17" customWidth="1"/>
-    <col min="16" max="16" width="24.6328125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="27.7265625" customWidth="1"/>
-    <col min="18" max="18" width="38.453125" customWidth="1"/>
+    <col min="8" max="8" width="15" style="5" customWidth="1"/>
+    <col min="9" max="9" width="17.08984375" style="5" customWidth="1"/>
+    <col min="10" max="10" width="15" style="5" customWidth="1"/>
+    <col min="11" max="11" width="19.90625" style="5" customWidth="1"/>
+    <col min="12" max="12" width="37.453125" style="5" customWidth="1"/>
+    <col min="13" max="13" width="15.08984375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="29.7265625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="24.1796875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="24.08984375" style="12" customWidth="1"/>
+    <col min="17" max="17" width="24.6328125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="20.36328125" customWidth="1"/>
+    <col min="19" max="19" width="23.08984375" customWidth="1"/>
+    <col min="20" max="20" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-    </row>
-    <row r="3" spans="1:18" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="27" t="s">
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="90"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+    </row>
+    <row r="3" spans="1:20" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D3" s="25" t="s">
+      <c r="D3" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="E3" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="29" t="s">
+      <c r="F3" s="23"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-    </row>
-    <row r="4" spans="1:18" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+    </row>
+    <row r="4" spans="1:20" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="35" t="s">
+      <c r="E4" s="27"/>
+      <c r="F4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="L4" s="34"/>
-      <c r="M4" s="35" t="s">
+      <c r="L4" s="87" t="s">
+        <v>145</v>
+      </c>
+      <c r="M4" s="27"/>
+      <c r="N4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="N4" s="35" t="s">
+      <c r="O4" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="P4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="Q4" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="R4" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="R4" s="36" t="s">
+      <c r="S4" s="29" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="37" t="s">
+      <c r="T4" s="88" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="32">
         <v>46268</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="41"/>
-      <c r="I5" s="41"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="41"/>
-      <c r="L5" s="39">
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="32">
         <v>46277</v>
       </c>
-      <c r="M5" s="42" t="s">
+      <c r="N5" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-    </row>
-    <row r="6" spans="1:18" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="37" t="s">
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+    </row>
+    <row r="6" spans="1:20" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="39">
+      <c r="E6" s="32">
         <v>46274</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="46">
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="39">
         <v>46280</v>
       </c>
-      <c r="M6" s="43" t="s">
+      <c r="N6" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="O6" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="O6" s="42" t="s">
+      <c r="P6" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-    </row>
-    <row r="7" spans="1:18" ht="78" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="47" t="s">
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+    </row>
+    <row r="7" spans="1:20" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="41" t="s">
         <v>39</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="49">
+      <c r="E7" s="42">
         <v>46281</v>
       </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="52" t="s">
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
+      <c r="H7" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="54">
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="78">
         <v>46287</v>
       </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="11" t="s">
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="Q7" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="R7" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="R7" s="94" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="65.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="58" t="s">
+      <c r="S7" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="T7" s="77" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="41" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E8" s="54">
+        <v>144</v>
+      </c>
+      <c r="E8" s="78">
         <v>46288</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="54">
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
+      <c r="H8" s="44"/>
+      <c r="I8" s="44"/>
+      <c r="J8" s="44"/>
+      <c r="K8" s="44"/>
+      <c r="L8" s="92" t="s">
+        <v>146</v>
+      </c>
+      <c r="M8" s="78">
         <v>46289</v>
       </c>
-      <c r="M8" s="55"/>
-      <c r="N8" s="55"/>
-      <c r="O8" s="55"/>
-      <c r="P8" s="55"/>
-      <c r="Q8" s="55"/>
-      <c r="R8" s="55"/>
-    </row>
-    <row r="9" spans="1:18" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="58"/>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
+      <c r="N8" s="47"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="47"/>
+      <c r="Q8" s="47"/>
+      <c r="R8" s="47"/>
+      <c r="S8" s="47"/>
+      <c r="T8" s="47"/>
+    </row>
+    <row r="9" spans="1:20" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="2"/>
-      <c r="E9" s="59"/>
-      <c r="F9" s="60"/>
-      <c r="G9" s="61"/>
-      <c r="H9" s="61"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="61"/>
-      <c r="K9" s="61"/>
-      <c r="L9" s="59" t="s">
+      <c r="E9" s="50"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="M9" s="62"/>
-      <c r="N9" s="62"/>
-      <c r="O9" s="62"/>
-      <c r="P9" s="62"/>
-      <c r="Q9" s="57"/>
-      <c r="R9" s="57"/>
-    </row>
-    <row r="10" spans="1:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="58" t="s">
+      <c r="N9" s="52"/>
+      <c r="O9" s="52"/>
+      <c r="P9" s="52"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+    </row>
+    <row r="10" spans="1:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="41" t="s">
         <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="54">
+      <c r="E10" s="42">
         <v>46290</v>
       </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
-      <c r="H10" s="51"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="51"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="54">
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
+      <c r="I10" s="44"/>
+      <c r="J10" s="44"/>
+      <c r="K10" s="44"/>
+      <c r="L10" s="44"/>
+      <c r="M10" s="42">
         <v>46292</v>
       </c>
-      <c r="M10" s="55"/>
-      <c r="N10" s="55"/>
-      <c r="O10" s="55"/>
-      <c r="P10" s="55"/>
-      <c r="Q10" s="55"/>
-      <c r="R10" s="55"/>
-    </row>
-    <row r="11" spans="1:18" ht="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="58"/>
-      <c r="B11" s="48"/>
-      <c r="C11" s="48"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47"/>
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="52"/>
+    </row>
+    <row r="11" spans="1:20" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="49"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="2"/>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="F11" s="60"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="61"/>
-      <c r="K11" s="61"/>
-      <c r="L11" s="59" t="s">
+      <c r="F11" s="45"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="M11" s="62"/>
-      <c r="N11" s="62"/>
-      <c r="O11" s="62"/>
-      <c r="P11" s="62"/>
-      <c r="Q11" s="57"/>
-      <c r="R11" s="57"/>
-    </row>
-    <row r="12" spans="1:18" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="58" t="s">
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+    </row>
+    <row r="12" spans="1:20" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="41" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="54">
+      <c r="E12" s="42">
         <v>46290</v>
       </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="54">
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="44"/>
+      <c r="I12" s="44"/>
+      <c r="J12" s="44"/>
+      <c r="K12" s="44"/>
+      <c r="L12" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="42">
         <v>46292</v>
       </c>
-      <c r="M12" s="55"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="55"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="R12" s="55"/>
-    </row>
-    <row r="13" spans="1:18" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="58" t="s">
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="93" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="41" t="s">
         <v>47</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="54">
+      <c r="E13" s="42">
         <v>45197</v>
       </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="51"/>
-      <c r="H13" s="51"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="51"/>
-      <c r="K13" s="51"/>
-      <c r="L13" s="54">
+      <c r="F13" s="43"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="44"/>
+      <c r="L13" s="44"/>
+      <c r="M13" s="42">
         <v>46295</v>
       </c>
-      <c r="M13" s="55"/>
-      <c r="N13" s="55"/>
-      <c r="O13" s="55"/>
-      <c r="P13" s="55"/>
-      <c r="Q13" s="55"/>
-      <c r="R13" s="55"/>
-    </row>
-    <row r="14" spans="1:18" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="58" t="s">
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+    </row>
+    <row r="14" spans="1:20" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="41" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="42">
         <v>46296</v>
       </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="51"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="51"/>
-      <c r="K14" s="51"/>
-      <c r="L14" s="54">
+      <c r="F14" s="43"/>
+      <c r="G14" s="44"/>
+      <c r="H14" s="44"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
+      <c r="L14" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="M14" s="42">
         <v>46300</v>
       </c>
-      <c r="M14" s="55"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="55"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="55"/>
-      <c r="R14" s="55"/>
-    </row>
-    <row r="15" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="104"/>
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="60"/>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="49"/>
-      <c r="M15" s="62"/>
-      <c r="N15" s="62"/>
-      <c r="O15" s="62"/>
-      <c r="P15" s="62"/>
-      <c r="Q15" s="62"/>
-      <c r="R15" s="62"/>
-    </row>
-    <row r="16" spans="1:18" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63" t="s">
+      <c r="N14" s="47"/>
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="47"/>
+      <c r="S14" s="47"/>
+      <c r="T14" s="47"/>
+    </row>
+    <row r="15" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="49"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
+      <c r="I15" s="51"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="51"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="52"/>
+      <c r="O15" s="52"/>
+      <c r="P15" s="52"/>
+      <c r="Q15" s="52"/>
+      <c r="R15" s="52"/>
+      <c r="S15" s="52"/>
+      <c r="T15" s="52"/>
+    </row>
+    <row r="16" spans="1:20" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="64" t="s">
+      <c r="C16" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="65"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="67"/>
-      <c r="J16" s="67"/>
-      <c r="K16" s="67"/>
-      <c r="L16" s="65"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-      <c r="O16" s="68"/>
-      <c r="P16" s="68"/>
-      <c r="Q16" s="68"/>
-      <c r="R16" s="68"/>
-    </row>
-    <row r="17" spans="1:18" ht="134" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="99" t="s">
+      <c r="E16" s="55"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
+      <c r="J16" s="57"/>
+      <c r="K16" s="57"/>
+      <c r="L16" s="57"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="58"/>
+      <c r="O16" s="58"/>
+      <c r="P16" s="58"/>
+      <c r="Q16" s="58"/>
+      <c r="R16" s="58"/>
+      <c r="S16" s="58"/>
+      <c r="T16" s="58"/>
+    </row>
+    <row r="17" spans="1:20" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="38" t="s">
+      <c r="C17" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="32">
         <v>46274</v>
       </c>
-      <c r="F17" s="83" t="s">
+      <c r="F17" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="103">
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="84">
         <v>46278</v>
       </c>
-      <c r="M17" s="8" t="s">
+      <c r="N17" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="N17" s="13" t="s">
+      <c r="O17" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="O17" s="8" t="s">
+      <c r="P17" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="Q17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="R17" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="R17" s="19" t="s">
+      <c r="S17" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="T17" s="14"/>
+    </row>
+    <row r="18" spans="1:20" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="80" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="84">
+        <v>46279</v>
+      </c>
+      <c r="F18" s="96" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="I18" s="97" t="s">
+        <v>100</v>
+      </c>
+      <c r="J18" s="98" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="98" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="70">
-        <v>46279</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" s="72" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="K18" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="L18" s="70">
+      <c r="L18" s="38"/>
+      <c r="M18" s="84">
         <v>46280</v>
       </c>
-      <c r="M18" s="10" t="s">
+      <c r="N18" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="N18" s="10" t="s">
+      <c r="O18" s="99" t="s">
         <v>111</v>
       </c>
-      <c r="O18" s="10" t="s">
+      <c r="P18" s="99" t="s">
         <v>134</v>
       </c>
-      <c r="P18" s="10" t="s">
+      <c r="Q18" s="99" t="s">
         <v>135</v>
       </c>
-      <c r="Q18" s="21" t="s">
+      <c r="R18" s="100" t="s">
         <v>131</v>
       </c>
-      <c r="R18" s="94" t="s">
+      <c r="S18" s="101" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" ht="53" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="98" t="s">
+      <c r="T18" s="95" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="23" t="s">
+      <c r="D19" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="101">
+      <c r="E19" s="82">
         <v>46282</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="G19" s="45"/>
-      <c r="H19" s="45"/>
-      <c r="I19" s="45"/>
-      <c r="J19" s="45"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="39">
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="32">
         <v>46288</v>
       </c>
-      <c r="M19" s="43" t="s">
+      <c r="N19" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="N19" s="43" t="s">
+      <c r="O19" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="O19" s="43" t="s">
+      <c r="P19" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="P19" s="43" t="s">
+      <c r="Q19" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="Q19" s="19" t="s">
+      <c r="R19" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="R19" s="102"/>
-    </row>
-    <row r="20" spans="1:18" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="47" t="s">
+      <c r="S19" s="83"/>
+      <c r="T19" s="83"/>
+    </row>
+    <row r="20" spans="1:20" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="73">
+      <c r="E20" s="82">
         <v>46282</v>
       </c>
-      <c r="F20" s="75"/>
-      <c r="G20" s="76"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="77" t="s">
+      <c r="F20" s="33"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="74"/>
-      <c r="K20" s="74"/>
-      <c r="L20" s="54">
+      <c r="J20" s="38"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="38"/>
+      <c r="M20" s="32">
         <v>46288</v>
       </c>
-      <c r="M20" s="55"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="55"/>
-      <c r="P20" s="11" t="s">
+      <c r="N20" s="79"/>
+      <c r="O20" s="79"/>
+      <c r="P20" s="79"/>
+      <c r="Q20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="R20" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="R20" s="11" t="s">
+      <c r="S20" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="99" t="s">
+      <c r="T20" s="95" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="23" t="s">
+      <c r="D21" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="39">
+      <c r="E21" s="32">
         <v>46276</v>
       </c>
-      <c r="F21" s="83" t="s">
+      <c r="F21" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="39">
+      <c r="G21" s="38"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="32">
         <v>46288</v>
       </c>
-      <c r="M21" s="13" t="s">
+      <c r="N21" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="N21" s="13" t="s">
+      <c r="O21" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="O21" s="13" t="s">
+      <c r="P21" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="P21" s="13" t="s">
+      <c r="Q21" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="Q21" s="19" t="s">
+      <c r="R21" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="R21" s="100"/>
-    </row>
-    <row r="22" spans="1:18" ht="43" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="99" t="s">
+      <c r="S21" s="81"/>
+      <c r="T21" s="81"/>
+    </row>
+    <row r="22" spans="1:20" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="32">
         <v>46289</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="15" t="s">
+      <c r="F22" s="33"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="K22" s="41"/>
-      <c r="L22" s="39">
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="32">
         <v>46289</v>
       </c>
-      <c r="M22" s="97"/>
-      <c r="N22" s="97"/>
-      <c r="O22" s="97"/>
-      <c r="P22" s="97"/>
-      <c r="Q22" s="19" t="s">
+      <c r="N22" s="79"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="79"/>
+      <c r="Q22" s="79"/>
+      <c r="R22" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="R22" s="97"/>
-    </row>
-    <row r="23" spans="1:18" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="58" t="s">
+      <c r="S22" s="79"/>
+      <c r="T22" s="79"/>
+    </row>
+    <row r="23" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="48" t="s">
+      <c r="C23" s="41" t="s">
         <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E23" s="42">
+        <v>46275</v>
+      </c>
+      <c r="F23" s="60" t="s">
+        <v>96</v>
+      </c>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+      <c r="J23" s="59"/>
+      <c r="K23" s="59"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="42">
+        <v>46319</v>
+      </c>
+      <c r="N23" s="47"/>
+      <c r="O23" s="47"/>
+      <c r="P23" s="47"/>
+      <c r="Q23" s="47"/>
+      <c r="R23" s="47"/>
+      <c r="S23" s="47"/>
+      <c r="T23" s="47"/>
+    </row>
+    <row r="24" spans="1:20" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B24" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>69</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="32">
+        <v>46275</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="64"/>
+      <c r="H24" s="64"/>
+      <c r="I24" s="64"/>
+      <c r="J24" s="64"/>
+      <c r="K24" s="64"/>
+      <c r="L24" s="64"/>
+      <c r="M24" s="32">
+        <v>46278</v>
+      </c>
+      <c r="N24" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+    </row>
+    <row r="25" spans="1:20" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="B25" s="62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="62" t="s">
+        <v>70</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" s="39">
+        <v>46278</v>
+      </c>
+      <c r="F25" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="G25" s="65" t="s">
+        <v>104</v>
+      </c>
+      <c r="H25" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="39">
+        <v>46281</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="P25" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+    </row>
+    <row r="26" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="80" t="s">
+        <v>80</v>
+      </c>
+      <c r="B26" s="62" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="62" t="s">
+        <v>117</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E26" s="82">
+        <v>46281</v>
+      </c>
+      <c r="F26" s="66"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="32">
+        <v>46285</v>
+      </c>
+      <c r="N26" s="102"/>
+      <c r="O26" s="102"/>
+      <c r="P26" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="S26" s="101" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="49">
-        <v>46275</v>
-      </c>
-      <c r="F23" s="77" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="69"/>
-      <c r="K23" s="69"/>
-      <c r="L23" s="54">
-        <v>46319</v>
-      </c>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="55"/>
-    </row>
-    <row r="24" spans="1:18" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="78" t="s">
-        <v>78</v>
-      </c>
-      <c r="B24" s="79" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="79" t="s">
-        <v>69</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="39">
-        <v>46275</v>
-      </c>
-      <c r="F24" s="80" t="s">
-        <v>96</v>
-      </c>
-      <c r="G24" s="81"/>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="81"/>
-      <c r="K24" s="81"/>
-      <c r="L24" s="39">
-        <v>46278</v>
-      </c>
-      <c r="M24" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-    </row>
-    <row r="25" spans="1:18" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="B25" s="79" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="46">
-        <v>46278</v>
-      </c>
-      <c r="F25" s="82" t="s">
-        <v>104</v>
-      </c>
-      <c r="G25" s="82" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="82" t="s">
-        <v>96</v>
-      </c>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="46">
-        <v>46281</v>
-      </c>
-      <c r="M25" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="N25" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="O25" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-    </row>
-    <row r="26" spans="1:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="B26" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="C26" s="84" t="s">
-        <v>117</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E26" s="73">
-        <v>46281</v>
-      </c>
-      <c r="F26" s="53"/>
-      <c r="G26" s="69"/>
-      <c r="H26" s="56" t="s">
-        <v>96</v>
-      </c>
-      <c r="I26" s="69"/>
-      <c r="J26" s="69"/>
-      <c r="K26" s="69"/>
-      <c r="L26" s="96">
-        <v>46285</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="R26" s="94" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="47" t="s">
+      <c r="T26" s="95" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="84" t="s">
+      <c r="B27" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="84" t="s">
+      <c r="C27" s="67" t="s">
         <v>118</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="96">
+      <c r="E27" s="78">
         <v>46286</v>
       </c>
-      <c r="F27" s="53"/>
-      <c r="G27" s="69"/>
-      <c r="H27" s="85"/>
-      <c r="I27" s="69"/>
-      <c r="J27" s="69"/>
-      <c r="K27" s="95" t="s">
+      <c r="F27" s="46"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="59"/>
+      <c r="J27" s="59"/>
+      <c r="K27" s="104" t="s">
         <v>137</v>
       </c>
-      <c r="L27" s="54">
+      <c r="L27" s="104" t="s">
+        <v>152</v>
+      </c>
+      <c r="M27" s="42">
         <v>46293</v>
       </c>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="55"/>
-      <c r="P27" s="55"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="55"/>
-    </row>
-    <row r="28" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="86" t="s">
+      <c r="N27" s="47"/>
+      <c r="O27" s="47"/>
+      <c r="P27" s="47"/>
+      <c r="Q27" s="47"/>
+      <c r="R27" s="47"/>
+      <c r="S27" s="47"/>
+      <c r="T27" s="103" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="84" t="s">
+      <c r="B28" s="67" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="84" t="s">
+      <c r="C28" s="67" t="s">
         <v>119</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="54">
+      <c r="E28" s="42">
         <v>46294</v>
       </c>
-      <c r="F28" s="87"/>
-      <c r="G28" s="85"/>
-      <c r="H28" s="85"/>
-      <c r="I28" s="69"/>
-      <c r="J28" s="69"/>
-      <c r="K28" s="69"/>
-      <c r="L28" s="54">
+      <c r="F28" s="70"/>
+      <c r="G28" s="68"/>
+      <c r="H28" s="68"/>
+      <c r="I28" s="59"/>
+      <c r="J28" s="59"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="59"/>
+      <c r="M28" s="42">
         <v>46319</v>
       </c>
-      <c r="M28" s="55"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="55"/>
-      <c r="P28" s="55"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="55"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="88"/>
-      <c r="M29" s="89"/>
-      <c r="N29" s="89"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="89"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="E30" s="88"/>
-      <c r="F30" s="88"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="88"/>
-      <c r="M30" s="89"/>
-      <c r="N30" s="89"/>
-      <c r="O30" s="89"/>
-      <c r="P30" s="89"/>
-      <c r="Q30" s="32"/>
-      <c r="R30" s="32"/>
-    </row>
-    <row r="31" spans="1:18" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="32"/>
-      <c r="B31" s="90" t="s">
+      <c r="N28" s="47"/>
+      <c r="O28" s="47"/>
+      <c r="P28" s="47"/>
+      <c r="Q28" s="47"/>
+      <c r="R28" s="47"/>
+      <c r="S28" s="47"/>
+      <c r="T28" s="47"/>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="71"/>
+      <c r="N29" s="72"/>
+      <c r="O29" s="72"/>
+      <c r="P29" s="72"/>
+      <c r="Q29" s="72"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="72"/>
+      <c r="P30" s="72"/>
+      <c r="Q30" s="72"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+    </row>
+    <row r="31" spans="1:20" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="25"/>
+      <c r="B31" s="73" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="74" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="88"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="89"/>
-      <c r="O31" s="89"/>
-      <c r="P31" s="89"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="E32" s="88"/>
-      <c r="F32" s="88"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="88"/>
-      <c r="M32" s="89"/>
-      <c r="N32" s="89"/>
-      <c r="O32" s="89"/>
-      <c r="P32" s="89"/>
-      <c r="Q32" s="32"/>
-      <c r="R32" s="32"/>
-    </row>
-    <row r="33" spans="1:18" ht="173" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="32"/>
-      <c r="B33" s="92" t="s">
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="72"/>
+      <c r="O31" s="72"/>
+      <c r="P31" s="72"/>
+      <c r="Q31" s="72"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="72"/>
+      <c r="O32" s="72"/>
+      <c r="P32" s="72"/>
+      <c r="Q32" s="72"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+    </row>
+    <row r="33" spans="1:20" ht="173" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="25"/>
+      <c r="B33" s="75" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="93" t="s">
+      <c r="C33" s="76" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="88"/>
-      <c r="M33" s="89"/>
-      <c r="N33" s="89"/>
-      <c r="O33" s="89"/>
-      <c r="P33" s="89"/>
-      <c r="Q33" s="32"/>
-      <c r="R33" s="32"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="71"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="71"/>
+      <c r="N33" s="72"/>
+      <c r="O33" s="72"/>
+      <c r="P33" s="72"/>
+      <c r="Q33" s="72"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="26" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="35" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Documents\Codex\2026-09-22\new-chat\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0AF33A1-72F4-4E08-8AD1-199E0154AA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C382709C-ECC2-4316-8F3F-2C2EFD4E3997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="162">
   <si>
     <t>№ п/п</t>
   </si>
@@ -266,9 +266,6 @@
     <t>connection the cabinet inside the room</t>
   </si>
   <si>
-    <t>подключение к полевой распределительной коробке</t>
-  </si>
-  <si>
     <t>2.7.1</t>
   </si>
   <si>
@@ -282,9 +279,6 @@
   </si>
   <si>
     <t>2.7.5</t>
-  </si>
-  <si>
-    <t>подключение шкафов внутри помещения</t>
   </si>
   <si>
     <t>Примечание Замперла : "Время указано ориентировочно и зависит от укомплектованности персоналом и погодных условий"</t>
@@ -483,10 +477,6 @@
   </si>
   <si>
     <t>по состоянию на 24.09</t>
-  </si>
-  <si>
-    <t>не приступили. Начало работ планируется 30.09.26
-(после заврешения работ по регулировки стрелки тех.обслуживания)</t>
   </si>
   <si>
     <t xml:space="preserve">планируемый срок завершения - 24.09.26
@@ -522,6 +512,47 @@
   </si>
   <si>
     <t>приступили 23.09.26</t>
+  </si>
+  <si>
+    <t>питание не подавать пока не будет высушено помещение и шкафы</t>
+  </si>
+  <si>
+    <t>по состоянию на 28.09</t>
+  </si>
+  <si>
+    <t>не приступили. Начало работ планируется 30.09.26
+(после заврешения работ по регулировки треков тех.обслуживания)</t>
+  </si>
+  <si>
+    <t>Идет подготовка к подливке.
+По возможности работы будут выполняться по зонам (параллельно с зонами готовности по п.1.3.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">не приступили.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">не приступили. Зависимость от п.1.4
+</t>
+  </si>
+  <si>
+    <t>работы выполняются.  Завершение планируется 29.09.26</t>
+  </si>
+  <si>
+    <t>подключение к полевой распределительной коробке (улица)</t>
+  </si>
+  <si>
+    <t>подключение шкафов внутри тех.помещения</t>
+  </si>
+  <si>
+    <t>приступили с 25.09.26</t>
+  </si>
+  <si>
+    <t>работы выполняются. Выполнено 50%.
+Ожидаемый срок завершения - 02.10.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Планируемый срок завершения - 29.09.26</t>
   </si>
 </sst>
 </file>
@@ -715,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -981,6 +1012,39 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -988,44 +1052,17 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1242,7 +1279,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:T33"/>
+  <dimension ref="A2:V33"/>
   <sheetFormatPr defaultRowHeight="15.5" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.6328125" customWidth="1"/>
@@ -1250,55 +1287,57 @@
     <col min="3" max="3" width="51.26953125" hidden="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="51.453125" style="15" customWidth="1"/>
     <col min="5" max="5" width="15.81640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.36328125" style="11" customWidth="1"/>
-    <col min="7" max="7" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="29.36328125" style="11" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="15" style="5" customWidth="1"/>
     <col min="9" max="9" width="17.08984375" style="5" customWidth="1"/>
     <col min="10" max="10" width="15" style="5" customWidth="1"/>
     <col min="11" max="11" width="19.90625" style="5" customWidth="1"/>
     <col min="12" max="12" width="37.453125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="15.08984375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="29.7265625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="24.1796875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="24.08984375" style="12" customWidth="1"/>
-    <col min="17" max="17" width="24.6328125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="20.36328125" customWidth="1"/>
-    <col min="19" max="19" width="23.08984375" customWidth="1"/>
-    <col min="20" max="20" width="43" customWidth="1"/>
+    <col min="13" max="13" width="44.453125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="15.08984375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="29.7265625" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="16" max="16" width="24.1796875" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="24.08984375" style="12" customWidth="1"/>
+    <col min="18" max="18" width="24.6328125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="21.1796875" customWidth="1"/>
+    <col min="20" max="20" width="23.08984375" customWidth="1"/>
+    <col min="21" max="22" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="89" t="s">
+    <row r="2" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-    </row>
-    <row r="3" spans="1:20" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="102"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
+      <c r="J2" s="102"/>
+      <c r="K2" s="102"/>
+      <c r="L2" s="102"/>
+      <c r="M2" s="102"/>
+      <c r="N2" s="102"/>
+    </row>
+    <row r="3" spans="1:22" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F3" s="23"/>
       <c r="G3" s="24"/>
@@ -1307,18 +1346,20 @@
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
-      <c r="M3" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="N3" s="23"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="22" t="s">
+        <v>84</v>
+      </c>
       <c r="O3" s="23"/>
       <c r="P3" s="23"/>
       <c r="Q3" s="23"/>
-      <c r="R3" s="25"/>
+      <c r="R3" s="23"/>
       <c r="S3" s="25"/>
       <c r="T3" s="25"/>
-    </row>
-    <row r="4" spans="1:20" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+    </row>
+    <row r="4" spans="1:22" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
         <v>2</v>
       </c>
@@ -1333,50 +1374,56 @@
       </c>
       <c r="E4" s="27"/>
       <c r="F4" s="28" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I4" s="28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="J4" s="28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K4" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L4" s="87" t="s">
-        <v>145</v>
-      </c>
-      <c r="M4" s="27"/>
-      <c r="N4" s="28" t="s">
-        <v>94</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="M4" s="87" t="s">
+        <v>151</v>
+      </c>
+      <c r="N4" s="27"/>
       <c r="O4" s="28" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="P4" s="28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="Q4" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>129</v>
+        <v>108</v>
+      </c>
+      <c r="R4" s="28" t="s">
+        <v>114</v>
       </c>
       <c r="S4" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="T4" s="88" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+        <v>127</v>
+      </c>
+      <c r="T4" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="U4" s="88" t="s">
+        <v>143</v>
+      </c>
+      <c r="V4" s="88" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
@@ -1399,20 +1446,22 @@
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="34"/>
-      <c r="M5" s="32">
+      <c r="M5" s="34"/>
+      <c r="N5" s="32">
         <v>46277</v>
       </c>
-      <c r="N5" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="O5" s="36"/>
+      <c r="O5" s="35" t="s">
+        <v>93</v>
+      </c>
       <c r="P5" s="36"/>
       <c r="Q5" s="36"/>
       <c r="R5" s="36"/>
       <c r="S5" s="36"/>
       <c r="T5" s="36"/>
-    </row>
-    <row r="6" spans="1:20" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+    </row>
+    <row r="6" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="30" t="s">
         <v>6</v>
       </c>
@@ -1429,7 +1478,7 @@
         <v>46274</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G6" s="38"/>
       <c r="H6" s="38"/>
@@ -1437,24 +1486,26 @@
       <c r="J6" s="38"/>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
-      <c r="M6" s="39">
+      <c r="M6" s="38"/>
+      <c r="N6" s="39">
         <v>46280</v>
       </c>
-      <c r="N6" s="36" t="s">
-        <v>98</v>
-      </c>
       <c r="O6" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="P6" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q6" s="36"/>
+        <v>96</v>
+      </c>
+      <c r="P6" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q6" s="35" t="s">
+        <v>93</v>
+      </c>
       <c r="R6" s="36"/>
       <c r="S6" s="36"/>
       <c r="T6" s="36"/>
-    </row>
-    <row r="7" spans="1:20" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+    </row>
+    <row r="7" spans="1:22" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="40" t="s">
         <v>7</v>
       </c>
@@ -1473,34 +1524,38 @@
       <c r="F7" s="43"/>
       <c r="G7" s="44"/>
       <c r="H7" s="45" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I7" s="46"/>
       <c r="J7" s="46"/>
       <c r="K7" s="46"/>
       <c r="L7" s="46"/>
-      <c r="M7" s="78">
+      <c r="M7" s="46"/>
+      <c r="N7" s="78">
         <v>46287</v>
       </c>
-      <c r="N7" s="13"/>
       <c r="O7" s="13"/>
-      <c r="P7" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="R7" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="S7" s="77" t="s">
-        <v>147</v>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="T7" s="77" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+      <c r="U7" s="77" t="s">
+        <v>145</v>
+      </c>
+      <c r="V7" s="77" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="40" t="s">
         <v>8</v>
       </c>
@@ -1511,7 +1566,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E8" s="78">
         <v>46288</v>
@@ -1522,21 +1577,27 @@
       <c r="I8" s="44"/>
       <c r="J8" s="44"/>
       <c r="K8" s="44"/>
-      <c r="L8" s="92" t="s">
-        <v>146</v>
-      </c>
-      <c r="M8" s="78">
+      <c r="L8" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="M8" s="99" t="s">
+        <v>154</v>
+      </c>
+      <c r="N8" s="78">
         <v>46289</v>
       </c>
-      <c r="N8" s="47"/>
       <c r="O8" s="47"/>
       <c r="P8" s="47"/>
       <c r="Q8" s="47"/>
       <c r="R8" s="47"/>
       <c r="S8" s="47"/>
       <c r="T8" s="47"/>
-    </row>
-    <row r="9" spans="1:20" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U8" s="47"/>
+      <c r="V8" s="105" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="49"/>
       <c r="B9" s="41"/>
       <c r="C9" s="41"/>
@@ -1549,19 +1610,21 @@
       <c r="J9" s="51"/>
       <c r="K9" s="51"/>
       <c r="L9" s="51"/>
-      <c r="M9" s="50" t="s">
-        <v>126</v>
-      </c>
-      <c r="N9" s="52"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="50" t="s">
+        <v>124</v>
+      </c>
       <c r="O9" s="52"/>
       <c r="P9" s="52"/>
       <c r="Q9" s="52"/>
-      <c r="R9" s="48"/>
+      <c r="R9" s="52"/>
       <c r="S9" s="48"/>
       <c r="T9" s="48"/>
-    </row>
-    <row r="10" spans="1:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49" t="s">
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+    </row>
+    <row r="10" spans="1:22" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="40" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="41" t="s">
@@ -1573,7 +1636,7 @@
       <c r="D10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="78">
         <v>46290</v>
       </c>
       <c r="F10" s="43"/>
@@ -1582,25 +1645,29 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="42">
+      <c r="L10" s="104"/>
+      <c r="M10" s="99" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="78">
         <v>46292</v>
       </c>
-      <c r="N10" s="47"/>
       <c r="O10" s="47"/>
       <c r="P10" s="47"/>
       <c r="Q10" s="47"/>
       <c r="R10" s="47"/>
       <c r="S10" s="47"/>
-      <c r="T10" s="52"/>
-    </row>
-    <row r="11" spans="1:20" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+    </row>
+    <row r="11" spans="1:22" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="49"/>
       <c r="B11" s="41"/>
       <c r="C11" s="41"/>
       <c r="D11" s="2"/>
       <c r="E11" s="50" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F11" s="45"/>
       <c r="G11" s="51"/>
@@ -1609,18 +1676,20 @@
       <c r="J11" s="51"/>
       <c r="K11" s="51"/>
       <c r="L11" s="51"/>
-      <c r="M11" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="N11" s="52"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="50" t="s">
+        <v>126</v>
+      </c>
       <c r="O11" s="52"/>
       <c r="P11" s="52"/>
       <c r="Q11" s="52"/>
-      <c r="R11" s="48"/>
+      <c r="R11" s="52"/>
       <c r="S11" s="48"/>
       <c r="T11" s="48"/>
-    </row>
-    <row r="12" spans="1:20" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+    </row>
+    <row r="12" spans="1:22" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="40" t="s">
         <v>11</v>
       </c>
@@ -1642,24 +1711,28 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44"/>
-      <c r="L12" s="60" t="s">
-        <v>96</v>
-      </c>
-      <c r="M12" s="42">
+      <c r="L12" s="106" t="s">
+        <v>94</v>
+      </c>
+      <c r="M12" s="60"/>
+      <c r="N12" s="78">
         <v>46292</v>
       </c>
-      <c r="N12" s="47"/>
       <c r="O12" s="47"/>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
       <c r="R12" s="47"/>
       <c r="S12" s="47"/>
-      <c r="T12" s="93" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="49" t="s">
+      <c r="T12" s="47"/>
+      <c r="U12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="V12" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="40" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="41" t="s">
@@ -1681,18 +1754,24 @@
       <c r="J13" s="44"/>
       <c r="K13" s="44"/>
       <c r="L13" s="44"/>
-      <c r="M13" s="42">
+      <c r="M13" s="106" t="s">
+        <v>119</v>
+      </c>
+      <c r="N13" s="42">
         <v>46295</v>
       </c>
-      <c r="N13" s="47"/>
       <c r="O13" s="47"/>
       <c r="P13" s="47"/>
       <c r="Q13" s="47"/>
       <c r="R13" s="47"/>
       <c r="S13" s="47"/>
       <c r="T13" s="47"/>
-    </row>
-    <row r="14" spans="1:20" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U13" s="47"/>
+      <c r="V13" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="49" t="s">
         <v>15</v>
       </c>
@@ -1714,21 +1793,23 @@
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
       <c r="K14" s="44"/>
-      <c r="L14" s="94" t="s">
-        <v>149</v>
-      </c>
-      <c r="M14" s="42">
+      <c r="L14" s="90" t="s">
+        <v>146</v>
+      </c>
+      <c r="M14" s="44"/>
+      <c r="N14" s="42">
         <v>46300</v>
       </c>
-      <c r="N14" s="47"/>
       <c r="O14" s="47"/>
       <c r="P14" s="47"/>
       <c r="Q14" s="47"/>
       <c r="R14" s="47"/>
       <c r="S14" s="47"/>
       <c r="T14" s="47"/>
-    </row>
-    <row r="15" spans="1:20" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U14" s="47"/>
+      <c r="V14" s="47"/>
+    </row>
+    <row r="15" spans="1:22" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="49"/>
       <c r="B15" s="85"/>
       <c r="C15" s="41"/>
@@ -1741,16 +1822,18 @@
       <c r="J15" s="51"/>
       <c r="K15" s="51"/>
       <c r="L15" s="51"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="52"/>
+      <c r="M15" s="51"/>
+      <c r="N15" s="42"/>
       <c r="O15" s="52"/>
       <c r="P15" s="52"/>
       <c r="Q15" s="52"/>
       <c r="R15" s="52"/>
       <c r="S15" s="52"/>
       <c r="T15" s="52"/>
-    </row>
-    <row r="16" spans="1:20" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U15" s="52"/>
+      <c r="V15" s="52"/>
+    </row>
+    <row r="16" spans="1:22" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="53" t="s">
         <v>17</v>
       </c>
@@ -1771,16 +1854,18 @@
       <c r="J16" s="57"/>
       <c r="K16" s="57"/>
       <c r="L16" s="57"/>
-      <c r="M16" s="55"/>
-      <c r="N16" s="58"/>
+      <c r="M16" s="57"/>
+      <c r="N16" s="55"/>
       <c r="O16" s="58"/>
       <c r="P16" s="58"/>
       <c r="Q16" s="58"/>
       <c r="R16" s="58"/>
       <c r="S16" s="58"/>
       <c r="T16" s="58"/>
-    </row>
-    <row r="17" spans="1:20" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U16" s="58"/>
+      <c r="V16" s="58"/>
+    </row>
+    <row r="17" spans="1:22" ht="134" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="80" t="s">
         <v>19</v>
       </c>
@@ -1797,7 +1882,7 @@
         <v>46274</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G17" s="38"/>
       <c r="H17" s="38"/>
@@ -1805,30 +1890,36 @@
       <c r="J17" s="38"/>
       <c r="K17" s="38"/>
       <c r="L17" s="38"/>
-      <c r="M17" s="84">
+      <c r="M17" s="38"/>
+      <c r="N17" s="84">
         <v>46278</v>
       </c>
-      <c r="N17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="P17" s="4" t="s">
-        <v>113</v>
+      <c r="O17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="Q17" s="4" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="R17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="S17" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="T17" s="14"/>
-    </row>
-    <row r="18" spans="1:20" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="T17" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="U17" s="103" t="s">
+        <v>150</v>
+      </c>
+      <c r="V17" s="103" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="80" t="s">
         <v>21</v>
       </c>
@@ -1844,51 +1935,53 @@
       <c r="E18" s="84">
         <v>46279</v>
       </c>
-      <c r="F18" s="96" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="I18" s="97" t="s">
-        <v>100</v>
-      </c>
-      <c r="J18" s="98" t="s">
+      <c r="F18" s="92" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="H18" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="I18" s="93" t="s">
+        <v>98</v>
+      </c>
+      <c r="J18" s="94" t="s">
+        <v>131</v>
+      </c>
+      <c r="K18" s="94" t="s">
+        <v>141</v>
+      </c>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="84">
+        <v>46280</v>
+      </c>
+      <c r="O18" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="P18" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q18" s="95" t="s">
+        <v>132</v>
+      </c>
+      <c r="R18" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="K18" s="98" t="s">
-        <v>143</v>
-      </c>
-      <c r="L18" s="38"/>
-      <c r="M18" s="84">
-        <v>46280</v>
-      </c>
-      <c r="N18" s="99" t="s">
-        <v>111</v>
-      </c>
-      <c r="O18" s="99" t="s">
-        <v>111</v>
-      </c>
-      <c r="P18" s="99" t="s">
-        <v>134</v>
-      </c>
-      <c r="Q18" s="99" t="s">
-        <v>135</v>
-      </c>
-      <c r="R18" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="S18" s="101" t="s">
-        <v>139</v>
-      </c>
-      <c r="T18" s="95" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S18" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="T18" s="96" t="s">
+        <v>137</v>
+      </c>
+      <c r="U18" s="91" t="s">
+        <v>147</v>
+      </c>
+      <c r="V18" s="91"/>
+    </row>
+    <row r="19" spans="1:22" ht="53" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="80" t="s">
         <v>23</v>
       </c>
@@ -1905,7 +1998,7 @@
         <v>46282</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
@@ -1913,28 +2006,30 @@
       <c r="J19" s="38"/>
       <c r="K19" s="38"/>
       <c r="L19" s="38"/>
-      <c r="M19" s="32">
+      <c r="M19" s="38"/>
+      <c r="N19" s="32">
         <v>46288</v>
       </c>
-      <c r="N19" s="36" t="s">
-        <v>101</v>
-      </c>
       <c r="O19" s="36" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="P19" s="36" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Q19" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="R19" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="S19" s="83"/>
+        <v>112</v>
+      </c>
+      <c r="R19" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="S19" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="T19" s="83"/>
-    </row>
-    <row r="20" spans="1:20" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U19" s="83"/>
+      <c r="V19" s="83"/>
+    </row>
+    <row r="20" spans="1:22" ht="68" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="80" t="s">
         <v>24</v>
       </c>
@@ -1954,31 +2049,33 @@
       <c r="G20" s="34"/>
       <c r="H20" s="34"/>
       <c r="I20" s="66" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20" s="38"/>
       <c r="K20" s="38"/>
       <c r="L20" s="38"/>
-      <c r="M20" s="32">
+      <c r="M20" s="38"/>
+      <c r="N20" s="32">
         <v>46288</v>
       </c>
-      <c r="N20" s="79"/>
       <c r="O20" s="79"/>
       <c r="P20" s="79"/>
-      <c r="Q20" s="4" t="s">
-        <v>97</v>
-      </c>
+      <c r="Q20" s="79"/>
       <c r="R20" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S20" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="T20" s="95" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="U20" s="91" t="s">
+        <v>148</v>
+      </c>
+      <c r="V20" s="91"/>
+    </row>
+    <row r="21" spans="1:22" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="80" t="s">
         <v>26</v>
       </c>
@@ -1995,7 +2092,7 @@
         <v>46276</v>
       </c>
       <c r="F21" s="66" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G21" s="38"/>
       <c r="H21" s="38"/>
@@ -2003,28 +2100,30 @@
       <c r="J21" s="38"/>
       <c r="K21" s="38"/>
       <c r="L21" s="38"/>
-      <c r="M21" s="32">
+      <c r="M21" s="38"/>
+      <c r="N21" s="32">
         <v>46288</v>
       </c>
-      <c r="N21" s="8" t="s">
-        <v>103</v>
-      </c>
       <c r="O21" s="8" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="Q21" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="R21" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="S21" s="81"/>
+        <v>113</v>
+      </c>
+      <c r="R21" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="S21" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="T21" s="81"/>
-    </row>
-    <row r="22" spans="1:20" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U21" s="81"/>
+      <c r="V21" s="81"/>
+    </row>
+    <row r="22" spans="1:22" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="80" t="s">
         <v>28</v>
       </c>
@@ -2045,24 +2144,26 @@
       <c r="H22" s="34"/>
       <c r="I22" s="34"/>
       <c r="J22" s="10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="K22" s="34"/>
       <c r="L22" s="34"/>
-      <c r="M22" s="32">
+      <c r="M22" s="34"/>
+      <c r="N22" s="32">
         <v>46289</v>
       </c>
-      <c r="N22" s="79"/>
       <c r="O22" s="79"/>
       <c r="P22" s="79"/>
       <c r="Q22" s="79"/>
-      <c r="R22" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="S22" s="79"/>
+      <c r="R22" s="79"/>
+      <c r="S22" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="T22" s="79"/>
-    </row>
-    <row r="23" spans="1:20" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U22" s="79"/>
+      <c r="V22" s="79"/>
+    </row>
+    <row r="23" spans="1:22" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="49" t="s">
         <v>29</v>
       </c>
@@ -2073,13 +2174,13 @@
         <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E23" s="42">
         <v>46275</v>
       </c>
       <c r="F23" s="60" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="59"/>
       <c r="H23" s="59"/>
@@ -2087,20 +2188,22 @@
       <c r="J23" s="59"/>
       <c r="K23" s="59"/>
       <c r="L23" s="59"/>
-      <c r="M23" s="42">
+      <c r="M23" s="59"/>
+      <c r="N23" s="42">
         <v>46319</v>
       </c>
-      <c r="N23" s="47"/>
       <c r="O23" s="47"/>
       <c r="P23" s="47"/>
       <c r="Q23" s="47"/>
       <c r="R23" s="47"/>
       <c r="S23" s="47"/>
       <c r="T23" s="47"/>
-    </row>
-    <row r="24" spans="1:20" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U23" s="47"/>
+      <c r="V23" s="47"/>
+    </row>
+    <row r="24" spans="1:22" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" s="62" t="s">
         <v>72</v>
@@ -2115,7 +2218,7 @@
         <v>46275</v>
       </c>
       <c r="F24" s="63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G24" s="64"/>
       <c r="H24" s="64"/>
@@ -2123,22 +2226,24 @@
       <c r="J24" s="64"/>
       <c r="K24" s="64"/>
       <c r="L24" s="64"/>
-      <c r="M24" s="32">
+      <c r="M24" s="64"/>
+      <c r="N24" s="32">
         <v>46278</v>
       </c>
-      <c r="N24" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="O24" s="4"/>
+      <c r="O24" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-    </row>
-    <row r="25" spans="1:20" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+    </row>
+    <row r="25" spans="1:22" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="62" t="s">
         <v>73</v>
@@ -2147,53 +2252,55 @@
         <v>70</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E25" s="39">
         <v>46278</v>
       </c>
       <c r="F25" s="65" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G25" s="65" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H25" s="65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I25" s="66"/>
       <c r="J25" s="66"/>
       <c r="K25" s="66"/>
       <c r="L25" s="66"/>
-      <c r="M25" s="39">
+      <c r="M25" s="66"/>
+      <c r="N25" s="39">
         <v>46281</v>
       </c>
-      <c r="N25" s="8" t="s">
-        <v>97</v>
-      </c>
       <c r="O25" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="P25" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="Q25" s="4"/>
+      <c r="P25" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q25" s="14" t="s">
+        <v>93</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-    </row>
-    <row r="26" spans="1:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+    </row>
+    <row r="26" spans="1:22" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="62" t="s">
         <v>74</v>
       </c>
       <c r="C26" s="62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E26" s="82">
         <v>46281</v>
@@ -2201,45 +2308,47 @@
       <c r="F26" s="66"/>
       <c r="G26" s="38"/>
       <c r="H26" s="63" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="I26" s="38"/>
       <c r="J26" s="38"/>
       <c r="K26" s="38"/>
       <c r="L26" s="38"/>
-      <c r="M26" s="32">
+      <c r="M26" s="38"/>
+      <c r="N26" s="32">
         <v>46285</v>
       </c>
-      <c r="N26" s="102"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="8" t="s">
-        <v>97</v>
-      </c>
+      <c r="O26" s="97"/>
+      <c r="P26" s="97"/>
       <c r="Q26" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R26" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="S26" s="101" t="s">
-        <v>141</v>
-      </c>
-      <c r="T26" s="95" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>95</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="T26" s="96" t="s">
+        <v>139</v>
+      </c>
+      <c r="U26" s="91" t="s">
+        <v>148</v>
+      </c>
+      <c r="V26" s="91"/>
+    </row>
+    <row r="27" spans="1:22" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="67" t="s">
         <v>75</v>
       </c>
       <c r="C27" s="67" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="E27" s="78">
         <v>46286</v>
@@ -2249,37 +2358,41 @@
       <c r="H27" s="68"/>
       <c r="I27" s="59"/>
       <c r="J27" s="59"/>
-      <c r="K27" s="104" t="s">
-        <v>137</v>
-      </c>
-      <c r="L27" s="104" t="s">
-        <v>152</v>
-      </c>
-      <c r="M27" s="42">
+      <c r="K27" s="99" t="s">
+        <v>135</v>
+      </c>
+      <c r="L27" s="99" t="s">
+        <v>149</v>
+      </c>
+      <c r="M27" s="59"/>
+      <c r="N27" s="78">
         <v>46293</v>
       </c>
-      <c r="N27" s="47"/>
       <c r="O27" s="47"/>
       <c r="P27" s="47"/>
       <c r="Q27" s="47"/>
       <c r="R27" s="47"/>
       <c r="S27" s="47"/>
-      <c r="T27" s="103" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="T27" s="47"/>
+      <c r="U27" s="98" t="s">
+        <v>95</v>
+      </c>
+      <c r="V27" s="98" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="67" t="s">
         <v>76</v>
       </c>
       <c r="C28" s="67" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E28" s="42">
         <v>46294</v>
@@ -2291,18 +2404,24 @@
       <c r="J28" s="59"/>
       <c r="K28" s="59"/>
       <c r="L28" s="59"/>
-      <c r="M28" s="42">
+      <c r="M28" s="99" t="s">
+        <v>159</v>
+      </c>
+      <c r="N28" s="42">
         <v>46319</v>
       </c>
-      <c r="N28" s="47"/>
       <c r="O28" s="47"/>
       <c r="P28" s="47"/>
       <c r="Q28" s="47"/>
       <c r="R28" s="47"/>
       <c r="S28" s="47"/>
       <c r="T28" s="47"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U28" s="47"/>
+      <c r="V28" s="98" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A29" s="25"/>
       <c r="B29" s="25"/>
       <c r="C29" s="25"/>
@@ -2315,16 +2434,18 @@
       <c r="J29" s="25"/>
       <c r="K29" s="25"/>
       <c r="L29" s="25"/>
-      <c r="M29" s="71"/>
-      <c r="N29" s="72"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="71"/>
       <c r="O29" s="72"/>
       <c r="P29" s="72"/>
       <c r="Q29" s="72"/>
-      <c r="R29" s="25"/>
+      <c r="R29" s="72"/>
       <c r="S29" s="25"/>
       <c r="T29" s="25"/>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A30" s="25"/>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
@@ -2336,25 +2457,27 @@
       <c r="J30" s="25"/>
       <c r="K30" s="25"/>
       <c r="L30" s="25"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="72"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="71"/>
       <c r="O30" s="72"/>
       <c r="P30" s="72"/>
       <c r="Q30" s="72"/>
-      <c r="R30" s="25"/>
+      <c r="R30" s="72"/>
       <c r="S30" s="25"/>
       <c r="T30" s="25"/>
-    </row>
-    <row r="31" spans="1:20" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U30" s="25"/>
+      <c r="V30" s="25"/>
+    </row>
+    <row r="31" spans="1:22" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="25"/>
       <c r="B31" s="73" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C31" s="74" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E31" s="71"/>
       <c r="F31" s="71"/>
@@ -2364,16 +2487,18 @@
       <c r="J31" s="25"/>
       <c r="K31" s="25"/>
       <c r="L31" s="25"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="72"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="71"/>
       <c r="O31" s="72"/>
       <c r="P31" s="72"/>
       <c r="Q31" s="72"/>
-      <c r="R31" s="25"/>
+      <c r="R31" s="72"/>
       <c r="S31" s="25"/>
       <c r="T31" s="25"/>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="U31" s="25"/>
+      <c r="V31" s="25"/>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A32" s="25"/>
       <c r="B32" s="25"/>
       <c r="C32" s="25"/>
@@ -2385,25 +2510,27 @@
       <c r="J32" s="25"/>
       <c r="K32" s="25"/>
       <c r="L32" s="25"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="72"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="71"/>
       <c r="O32" s="72"/>
       <c r="P32" s="72"/>
       <c r="Q32" s="72"/>
-      <c r="R32" s="25"/>
+      <c r="R32" s="72"/>
       <c r="S32" s="25"/>
       <c r="T32" s="25"/>
-    </row>
-    <row r="33" spans="1:20" ht="173" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U32" s="25"/>
+      <c r="V32" s="25"/>
+    </row>
+    <row r="33" spans="1:22" ht="173" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="25"/>
       <c r="B33" s="75" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C33" s="76" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E33" s="71"/>
       <c r="F33" s="71"/>
@@ -2413,22 +2540,24 @@
       <c r="J33" s="25"/>
       <c r="K33" s="25"/>
       <c r="L33" s="25"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="72"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="71"/>
       <c r="O33" s="72"/>
       <c r="P33" s="72"/>
       <c r="Q33" s="72"/>
-      <c r="R33" s="25"/>
+      <c r="R33" s="72"/>
       <c r="S33" s="25"/>
       <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="35" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="25" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Documents\Codex\2026-09-22\new-chat\work\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C382709C-ECC2-4316-8F3F-2C2EFD4E3997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51C52DB-703A-4A5C-8AB9-2669A4F002D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -746,7 +746,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1045,6 +1045,12 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1052,18 +1058,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1306,22 +1300,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
     </row>
     <row r="3" spans="1:22" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="20" t="s">
@@ -1593,7 +1587,7 @@
       <c r="S8" s="47"/>
       <c r="T8" s="47"/>
       <c r="U8" s="47"/>
-      <c r="V8" s="105" t="s">
+      <c r="V8" s="52" t="s">
         <v>153</v>
       </c>
     </row>
@@ -1645,7 +1639,7 @@
       <c r="I10" s="44"/>
       <c r="J10" s="44"/>
       <c r="K10" s="44"/>
-      <c r="L10" s="104"/>
+      <c r="L10" s="51"/>
       <c r="M10" s="99" t="s">
         <v>155</v>
       </c>
@@ -1711,7 +1705,7 @@
       <c r="I12" s="44"/>
       <c r="J12" s="44"/>
       <c r="K12" s="44"/>
-      <c r="L12" s="106" t="s">
+      <c r="L12" s="101" t="s">
         <v>94</v>
       </c>
       <c r="M12" s="60"/>
@@ -1754,7 +1748,7 @@
       <c r="J13" s="44"/>
       <c r="K13" s="44"/>
       <c r="L13" s="44"/>
-      <c r="M13" s="106" t="s">
+      <c r="M13" s="101" t="s">
         <v>119</v>
       </c>
       <c r="N13" s="42">
@@ -1912,10 +1906,10 @@
       <c r="T17" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="U17" s="103" t="s">
+      <c r="U17" s="100" t="s">
         <v>150</v>
       </c>
-      <c r="V17" s="103" t="s">
+      <c r="V17" s="100" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2558,6 +2552,6 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="25" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="37" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Documents\Codex\2026-09-22\new-chat\work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBC3BB33-5C63-45E5-8165-B06F89DEDCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9936FC7-299D-4C7E-9CD9-2B57E0570E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="179">
   <si>
     <t>№ п/п</t>
   </si>
@@ -588,6 +588,36 @@
   </si>
   <si>
     <t>приступят к началу выполнения работ  после завершения п.1.5</t>
+  </si>
+  <si>
+    <t>по состоянию на 01.10</t>
+  </si>
+  <si>
+    <t>работы выполняются
+завершение планируется 04.10.26</t>
+  </si>
+  <si>
+    <t>работф выполняются. план завершения 07.10.2026</t>
+  </si>
+  <si>
+    <t>улица:
+выполнено/ done
+техническое помещение: работы выполняются (на завершение влияют работы по электрике)</t>
+  </si>
+  <si>
+    <t>работы выполняются.
+План завершения - 10.10.26</t>
+  </si>
+  <si>
+    <t>не приступили.
+приступят к началу выполнения работ  05.10.26</t>
+  </si>
+  <si>
+    <t>к работам не приступили</t>
+  </si>
+  <si>
+    <t>работы выполняются. 
+Ожидаемый срок завершения - 08.10.26</t>
   </si>
 </sst>
 </file>
@@ -781,7 +811,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -840,9 +870,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1002,12 +1029,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1044,6 +1065,42 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1051,41 +1108,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1302,13 +1341,13 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:X33"/>
+  <dimension ref="A2:Z33"/>
   <sheetFormatPr defaultRowHeight="21" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="46.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="0.36328125" style="97" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="51.453125" style="97" customWidth="1"/>
+    <col min="2" max="2" width="51.54296875" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="0.36328125" style="91" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="51.453125" style="91" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
@@ -1317,47 +1356,48 @@
     <col min="10" max="10" width="15" style="4" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="19.90625" style="4" customWidth="1" outlineLevel="1"/>
     <col min="12" max="12" width="37.453125" style="4" customWidth="1"/>
-    <col min="13" max="14" width="44.453125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="15.08984375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="29.7265625" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="24.1796875" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="24.08984375" style="9" customWidth="1"/>
-    <col min="19" max="19" width="24.6328125" style="2" customWidth="1"/>
-    <col min="20" max="20" width="21.1796875" customWidth="1"/>
-    <col min="21" max="21" width="23.08984375" customWidth="1"/>
-    <col min="22" max="24" width="43" customWidth="1"/>
+    <col min="13" max="15" width="44.453125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="15.08984375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="29.7265625" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="23.1796875" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="24.08984375" style="9" customWidth="1"/>
+    <col min="20" max="20" width="24.6328125" style="2" customWidth="1"/>
+    <col min="21" max="21" width="21.1796875" customWidth="1"/>
+    <col min="22" max="22" width="23.08984375" customWidth="1"/>
+    <col min="23" max="26" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:24" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="88" t="s">
+    <row r="2" spans="1:26" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-    </row>
-    <row r="3" spans="1:24" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="97"/>
+      <c r="C2" s="97"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
+      <c r="I2" s="99"/>
+      <c r="J2" s="99"/>
+      <c r="K2" s="99"/>
+      <c r="L2" s="99"/>
+      <c r="M2" s="99"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+    </row>
+    <row r="3" spans="1:26" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="91" t="s">
+      <c r="C3" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="91" t="s">
+      <c r="D3" s="85" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -1372,30 +1412,32 @@
       <c r="L3" s="15"/>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
-      <c r="O3" s="13" t="s">
+      <c r="O3" s="15"/>
+      <c r="P3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
-      <c r="T3" s="16"/>
+      <c r="T3" s="14"/>
       <c r="U3" s="16"/>
       <c r="V3" s="16"/>
       <c r="W3" s="16"/>
       <c r="X3" s="16"/>
-    </row>
-    <row r="4" spans="1:24" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+    </row>
+    <row r="4" spans="1:26" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="92" t="s">
+      <c r="C4" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="92" t="s">
+      <c r="D4" s="86" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="18"/>
@@ -1417,916 +1459,976 @@
       <c r="K4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="L4" s="74" t="s">
+      <c r="L4" s="100" t="s">
         <v>143</v>
       </c>
-      <c r="M4" s="74" t="s">
+      <c r="M4" s="100" t="s">
         <v>150</v>
       </c>
-      <c r="N4" s="74" t="s">
+      <c r="N4" s="100" t="s">
         <v>161</v>
       </c>
-      <c r="O4" s="18"/>
-      <c r="P4" s="19" t="s">
+      <c r="O4" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="102" t="s">
         <v>92</v>
       </c>
-      <c r="Q4" s="19" t="s">
+      <c r="R4" s="102" t="s">
         <v>105</v>
       </c>
-      <c r="R4" s="19" t="s">
+      <c r="S4" s="102" t="s">
         <v>108</v>
       </c>
-      <c r="S4" s="19" t="s">
+      <c r="T4" s="102" t="s">
         <v>114</v>
       </c>
-      <c r="T4" s="20" t="s">
+      <c r="U4" s="103" t="s">
         <v>127</v>
       </c>
-      <c r="U4" s="20" t="s">
+      <c r="V4" s="103" t="s">
         <v>128</v>
       </c>
-      <c r="V4" s="75" t="s">
+      <c r="W4" s="104" t="s">
         <v>143</v>
       </c>
-      <c r="W4" s="75" t="s">
+      <c r="X4" s="104" t="s">
         <v>150</v>
       </c>
-      <c r="X4" s="74" t="s">
+      <c r="Y4" s="104" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" ht="69" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="21" t="s">
+      <c r="Z4" s="104" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="87" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="93" t="s">
+      <c r="C5" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="95" t="s">
+      <c r="D5" s="89" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="22">
         <v>46268</v>
       </c>
-      <c r="F5" s="24"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="23">
+      <c r="F5" s="23"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="22">
         <v>46277</v>
       </c>
-      <c r="P5" s="26" t="s">
+      <c r="Q5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-    </row>
-    <row r="6" spans="1:24" ht="64" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="R5" s="26"/>
+      <c r="S5" s="26"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="26"/>
+      <c r="V5" s="26"/>
+      <c r="W5" s="26"/>
+      <c r="X5" s="26"/>
+      <c r="Y5" s="26"/>
+      <c r="Z5" s="26"/>
+    </row>
+    <row r="6" spans="1:26" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="93" t="s">
+      <c r="C6" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="95" t="s">
+      <c r="D6" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="22">
         <v>46274</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="30">
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="29">
         <v>46280</v>
       </c>
-      <c r="P6" s="27" t="s">
+      <c r="Q6" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="Q6" s="27" t="s">
+      <c r="R6" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="S6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-    </row>
-    <row r="7" spans="1:24" ht="95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="67" t="s">
+      <c r="T6" s="26"/>
+      <c r="U6" s="26"/>
+      <c r="V6" s="26"/>
+      <c r="W6" s="26"/>
+      <c r="X6" s="26"/>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="26"/>
+    </row>
+    <row r="7" spans="1:26" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="87" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="93" t="s">
+      <c r="C7" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="95" t="s">
+      <c r="D7" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="22">
         <v>46281</v>
       </c>
-      <c r="F7" s="24"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="24" t="s">
+      <c r="F7" s="23"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="23">
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="22">
         <v>46287</v>
       </c>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="3" t="s">
+      <c r="Q7" s="80"/>
+      <c r="R7" s="80"/>
+      <c r="S7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="S7" s="83" t="s">
+      <c r="T7" s="80" t="s">
         <v>118</v>
       </c>
-      <c r="T7" s="100" t="s">
+      <c r="U7" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="U7" s="82" t="s">
+      <c r="V7" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="V7" s="82" t="s">
+      <c r="W7" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="W7" s="82" t="s">
+      <c r="X7" s="79" t="s">
         <v>160</v>
       </c>
-      <c r="X7" s="77" t="s">
+      <c r="Y7" s="74" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="31" t="s">
+      <c r="Z7" s="74" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="88" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="88" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="96" t="s">
+      <c r="D8" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="E8" s="65">
+      <c r="E8" s="64">
         <v>46288</v>
       </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="76" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="73" t="s">
         <v>151</v>
       </c>
-      <c r="M8" s="85" t="s">
+      <c r="M8" s="82" t="s">
         <v>153</v>
       </c>
-      <c r="N8" s="85" t="s">
+      <c r="N8" s="82" t="s">
         <v>164</v>
       </c>
-      <c r="O8" s="65">
+      <c r="O8" s="34"/>
+      <c r="P8" s="64">
         <v>46289</v>
       </c>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="38"/>
-      <c r="S8" s="38"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="38"/>
-      <c r="V8" s="85" t="s">
+      <c r="Q8" s="37"/>
+      <c r="R8" s="37"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="37"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="82" t="s">
         <v>162</v>
       </c>
-      <c r="W8" s="43" t="s">
+      <c r="X8" s="42" t="s">
         <v>152</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="Y8" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="40"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="94"/>
-      <c r="D9" s="96"/>
-      <c r="E9" s="41"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="41" t="s">
+      <c r="Z8" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="39"/>
+      <c r="B9" s="88"/>
+      <c r="C9" s="88"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="39"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="39"/>
-    </row>
-    <row r="10" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="31" t="s">
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
+    </row>
+    <row r="10" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="94" t="s">
+      <c r="C10" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="96" t="s">
+      <c r="D10" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="65">
+      <c r="E10" s="64">
         <v>46290</v>
       </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="85" t="s">
+      <c r="F10" s="33"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="82" t="s">
         <v>154</v>
       </c>
-      <c r="N10" s="85" t="s">
+      <c r="N10" s="82" t="s">
         <v>164</v>
       </c>
-      <c r="O10" s="65">
+      <c r="O10" s="34"/>
+      <c r="P10" s="64">
         <v>46292</v>
       </c>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="38"/>
-      <c r="U10" s="38"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="85" t="s">
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="82" t="s">
         <v>169</v>
       </c>
-      <c r="X10" s="5" t="s">
+      <c r="Y10" s="5" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" ht="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="40"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="94"/>
-      <c r="D11" s="96"/>
-      <c r="E11" s="41" t="s">
+      <c r="Z10" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="39"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="36"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="41" t="s">
+      <c r="F11" s="35"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="41"/>
+      <c r="P11" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="39"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="39"/>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-    </row>
-    <row r="12" spans="1:24" ht="59.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="31" t="s">
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="38"/>
+      <c r="Y11" s="38"/>
+      <c r="Z11" s="38"/>
+    </row>
+    <row r="12" spans="1:26" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="94" t="s">
+      <c r="C12" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="96" t="s">
+      <c r="D12" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="32">
         <v>46290</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="87" t="s">
+      <c r="F12" s="33"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="84" t="s">
         <v>94</v>
       </c>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="65">
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="64">
         <v>46292</v>
       </c>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="38"/>
-      <c r="S12" s="38"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="38"/>
-      <c r="V12" s="5" t="s">
+      <c r="Q12" s="37"/>
+      <c r="R12" s="37"/>
+      <c r="S12" s="37"/>
+      <c r="T12" s="37"/>
+      <c r="U12" s="37"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="W12" s="5" t="s">
+      <c r="X12" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="X12" s="5" t="s">
+      <c r="Y12" s="5" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" ht="82" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="31" t="s">
+      <c r="Z12" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="94" t="s">
+      <c r="C13" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="90" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="32">
         <v>45197</v>
       </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="87" t="s">
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="84" t="s">
         <v>119</v>
       </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="33">
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="64">
         <v>46295</v>
       </c>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="38"/>
-      <c r="V13" s="38"/>
-      <c r="W13" s="5" t="s">
-        <v>95</v>
-      </c>
+      <c r="Q13" s="37"/>
+      <c r="R13" s="37"/>
+      <c r="S13" s="37"/>
+      <c r="T13" s="37"/>
+      <c r="U13" s="37"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
       <c r="X13" s="5" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
+      <c r="Y13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="94" t="s">
+      <c r="C14" s="88" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="96" t="s">
+      <c r="D14" s="90" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="64">
         <v>46296</v>
       </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="101" t="s">
+      <c r="F14" s="33"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="95" t="s">
         <v>166</v>
       </c>
-      <c r="M14" s="35"/>
-      <c r="N14" s="102" t="s">
+      <c r="M14" s="34"/>
+      <c r="N14" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="96" t="s">
+        <v>176</v>
+      </c>
+      <c r="P14" s="32">
         <v>46300</v>
       </c>
-      <c r="P14" s="38"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="38"/>
-      <c r="S14" s="38"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="38"/>
-      <c r="V14" s="38"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="38"/>
-    </row>
-    <row r="15" spans="1:24" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="40"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-    </row>
-    <row r="16" spans="1:24" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="44" t="s">
+      <c r="Q14" s="37"/>
+      <c r="R14" s="37"/>
+      <c r="S14" s="37"/>
+      <c r="T14" s="37"/>
+      <c r="U14" s="37"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+      <c r="Y14" s="37"/>
+      <c r="Z14" s="105" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="39"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="72"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="42"/>
+      <c r="W15" s="42"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
+    </row>
+    <row r="16" spans="1:26" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="43" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="92" t="s">
+      <c r="C16" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="92" t="s">
+      <c r="D16" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="46"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="48"/>
-      <c r="M16" s="48"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="46"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49"/>
-      <c r="R16" s="49"/>
-      <c r="S16" s="49"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49"/>
-    </row>
-    <row r="17" spans="1:24" ht="134" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="67" t="s">
+      <c r="E16" s="45"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="47"/>
+      <c r="L16" s="47"/>
+      <c r="M16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47"/>
+      <c r="P16" s="45"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="48"/>
+      <c r="X16" s="48"/>
+      <c r="Y16" s="48"/>
+      <c r="Z16" s="48"/>
+    </row>
+    <row r="17" spans="1:26" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="93" t="s">
+      <c r="C17" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="95" t="s">
+      <c r="D17" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="22">
         <v>46274</v>
       </c>
-      <c r="F17" s="57" t="s">
+      <c r="F17" s="56" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29"/>
-      <c r="O17" s="71">
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="70">
         <v>46278</v>
       </c>
-      <c r="P17" s="3" t="s">
+      <c r="Q17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="R17" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="T17" s="3" t="s">
+      <c r="U17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="U17" s="10" t="s">
+      <c r="V17" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="V17" s="86" t="s">
+      <c r="W17" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="W17" s="86" t="s">
+      <c r="X17" s="83" t="s">
         <v>149</v>
       </c>
-      <c r="X17" s="86" t="s">
+      <c r="Y17" s="83" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="67" t="s">
+      <c r="Z17" s="83" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="95" t="s">
+      <c r="D18" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="71">
+      <c r="E18" s="70">
         <v>46279</v>
       </c>
-      <c r="F18" s="78" t="s">
+      <c r="F18" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="79" t="s">
+      <c r="G18" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="79" t="s">
+      <c r="H18" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="79" t="s">
+      <c r="I18" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="80" t="s">
+      <c r="J18" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="80" t="s">
+      <c r="K18" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="L18" s="29"/>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29"/>
-      <c r="O18" s="71">
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="70">
         <v>46280</v>
       </c>
-      <c r="P18" s="81" t="s">
+      <c r="Q18" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="Q18" s="81" t="s">
+      <c r="R18" s="78" t="s">
         <v>109</v>
       </c>
-      <c r="R18" s="81" t="s">
+      <c r="S18" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="S18" s="81" t="s">
+      <c r="T18" s="78" t="s">
         <v>133</v>
       </c>
-      <c r="T18" s="3" t="s">
+      <c r="U18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="U18" s="82" t="s">
+      <c r="V18" s="79" t="s">
         <v>137</v>
       </c>
-      <c r="V18" s="77" t="s">
+      <c r="W18" s="74" t="s">
         <v>146</v>
       </c>
-      <c r="W18" s="77"/>
-      <c r="X18" s="77"/>
-    </row>
-    <row r="19" spans="1:24" ht="53" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="67" t="s">
+      <c r="X18" s="74"/>
+      <c r="Y18" s="74"/>
+      <c r="Z18" s="74"/>
+    </row>
+    <row r="19" spans="1:26" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="93" t="s">
+      <c r="C19" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="95" t="s">
+      <c r="D19" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="69">
+      <c r="E19" s="68">
         <v>46282</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="F19" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="23">
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="22">
         <v>46288</v>
       </c>
-      <c r="P19" s="27" t="s">
+      <c r="Q19" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="Q19" s="27" t="s">
+      <c r="R19" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="R19" s="27" t="s">
+      <c r="S19" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="S19" s="27" t="s">
+      <c r="T19" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="T19" s="10" t="s">
+      <c r="U19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="U19" s="70"/>
-      <c r="V19" s="70"/>
-      <c r="W19" s="70"/>
-      <c r="X19" s="70"/>
-    </row>
-    <row r="20" spans="1:24" ht="68" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="67" t="s">
+      <c r="V19" s="69"/>
+      <c r="W19" s="69"/>
+      <c r="X19" s="69"/>
+      <c r="Y19" s="69"/>
+      <c r="Z19" s="69"/>
+    </row>
+    <row r="20" spans="1:26" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="87" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="95" t="s">
+      <c r="D20" s="89" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="69">
+      <c r="E20" s="68">
         <v>46282</v>
       </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="57" t="s">
+      <c r="F20" s="23"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="56" t="s">
         <v>119</v>
       </c>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="23">
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="22">
         <v>46288</v>
       </c>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="66"/>
-      <c r="R20" s="66"/>
-      <c r="S20" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="Q20" s="65"/>
+      <c r="R20" s="65"/>
+      <c r="S20" s="65"/>
       <c r="T20" s="3" t="s">
         <v>95</v>
       </c>
       <c r="U20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="V20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="V20" s="77" t="s">
+      <c r="W20" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="W20" s="77"/>
-      <c r="X20" s="77"/>
-    </row>
-    <row r="21" spans="1:24" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="67" t="s">
+      <c r="X20" s="74"/>
+      <c r="Y20" s="74"/>
+      <c r="Z20" s="74"/>
+    </row>
+    <row r="21" spans="1:26" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="93" t="s">
+      <c r="C21" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="95" t="s">
+      <c r="D21" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="22">
         <v>46276</v>
       </c>
-      <c r="F21" s="57" t="s">
+      <c r="F21" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29"/>
-      <c r="O21" s="23">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
+      <c r="O21" s="28"/>
+      <c r="P21" s="22">
         <v>46288</v>
       </c>
-      <c r="P21" s="6" t="s">
+      <c r="Q21" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="R21" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="T21" s="10" t="s">
+      <c r="U21" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="U21" s="68"/>
-      <c r="V21" s="68"/>
-      <c r="W21" s="68"/>
-      <c r="X21" s="68"/>
-    </row>
-    <row r="22" spans="1:24" ht="43" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="67" t="s">
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
+      <c r="Y21" s="67"/>
+      <c r="Z21" s="67"/>
+    </row>
+    <row r="22" spans="1:26" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="93" t="s">
+      <c r="C22" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="95" t="s">
+      <c r="D22" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="22">
         <v>46289</v>
       </c>
-      <c r="F22" s="24"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="23">
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="22">
         <v>46289</v>
       </c>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="10" t="s">
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66"/>
-    </row>
-    <row r="23" spans="1:24" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="40" t="s">
+      <c r="V22" s="65"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+    </row>
+    <row r="23" spans="1:26" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="94" t="s">
+      <c r="C23" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="96" t="s">
+      <c r="D23" s="90" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="33">
+      <c r="E23" s="32">
         <v>46275</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="50" t="s">
         <v>94</v>
       </c>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="50"/>
-      <c r="J23" s="50"/>
-      <c r="K23" s="50"/>
-      <c r="L23" s="50"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="33">
+      <c r="G23" s="49"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="49"/>
+      <c r="J23" s="49"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="32">
         <v>46319</v>
       </c>
-      <c r="P23" s="38"/>
-      <c r="Q23" s="38"/>
-      <c r="R23" s="38"/>
-      <c r="S23" s="38"/>
-      <c r="T23" s="38"/>
-      <c r="U23" s="38"/>
-      <c r="V23" s="38"/>
-      <c r="W23" s="38"/>
-      <c r="X23" s="38"/>
-    </row>
-    <row r="24" spans="1:24" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="52" t="s">
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="37"/>
+      <c r="U23" s="37"/>
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="37"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
+    </row>
+    <row r="24" spans="1:26" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="95" t="s">
+      <c r="C24" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="95" t="s">
+      <c r="D24" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="22">
         <v>46275</v>
       </c>
-      <c r="F24" s="54" t="s">
+      <c r="F24" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="23">
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="54"/>
+      <c r="K24" s="54"/>
+      <c r="L24" s="54"/>
+      <c r="M24" s="54"/>
+      <c r="N24" s="54"/>
+      <c r="O24" s="54"/>
+      <c r="P24" s="22">
         <v>46278</v>
       </c>
-      <c r="P24" s="10" t="s">
+      <c r="Q24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2334,205 +2436,219 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-    </row>
-    <row r="25" spans="1:24" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="52" t="s">
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+    </row>
+    <row r="25" spans="1:26" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="53" t="s">
+      <c r="B25" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="95" t="s">
+      <c r="D25" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="29">
         <v>46278</v>
       </c>
-      <c r="F25" s="56" t="s">
+      <c r="F25" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="56" t="s">
+      <c r="G25" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="56" t="s">
+      <c r="H25" s="55" t="s">
         <v>94</v>
       </c>
-      <c r="I25" s="57"/>
-      <c r="J25" s="57"/>
-      <c r="K25" s="57"/>
-      <c r="L25" s="57"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="57"/>
-      <c r="O25" s="30">
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="29">
         <v>46281</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="R25" s="10" t="s">
+      <c r="R25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="S25" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
-    </row>
-    <row r="26" spans="1:24" ht="52" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="67" t="s">
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+    </row>
+    <row r="26" spans="1:26" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="53" t="s">
+      <c r="B26" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="89" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="95" t="s">
+      <c r="D26" s="89" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="68">
         <v>46281</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="54" t="s">
+      <c r="F26" s="56"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="23">
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="22">
         <v>46285</v>
       </c>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="6" t="s">
-        <v>95</v>
-      </c>
+      <c r="Q26" s="80"/>
+      <c r="R26" s="80"/>
       <c r="S26" s="6" t="s">
         <v>95</v>
       </c>
       <c r="T26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="U26" s="82" t="s">
+      <c r="U26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="V26" s="79" t="s">
         <v>139</v>
       </c>
-      <c r="V26" s="77" t="s">
+      <c r="W26" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="W26" s="77"/>
-      <c r="X26" s="77"/>
-    </row>
-    <row r="27" spans="1:24" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="31" t="s">
+      <c r="X26" s="74"/>
+      <c r="Y26" s="74"/>
+      <c r="Z26" s="74"/>
+    </row>
+    <row r="27" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="58" t="s">
+      <c r="B27" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="96" t="s">
+      <c r="C27" s="90" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="96" t="s">
+      <c r="D27" s="90" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="65">
+      <c r="E27" s="64">
         <v>46286</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="59"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="85" t="s">
+      <c r="F27" s="36"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="49"/>
+      <c r="J27" s="49"/>
+      <c r="K27" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="L27" s="85" t="s">
+      <c r="L27" s="82" t="s">
         <v>148</v>
       </c>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="65">
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="64">
         <v>46293</v>
       </c>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="38"/>
-      <c r="T27" s="38"/>
-      <c r="U27" s="38"/>
-      <c r="V27" s="84" t="s">
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
+      <c r="U27" s="37"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="W27" s="84" t="s">
+      <c r="X27" s="81" t="s">
         <v>159</v>
       </c>
-      <c r="X27" s="84" t="s">
+      <c r="Y27" s="81" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="31" t="s">
+      <c r="Z27" s="81" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="58" t="s">
+      <c r="B28" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="96" t="s">
+      <c r="C28" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="96" t="s">
+      <c r="D28" s="90" t="s">
         <v>157</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="32">
         <v>46294</v>
       </c>
-      <c r="F28" s="60"/>
-      <c r="G28" s="59"/>
-      <c r="H28" s="59"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="85" t="s">
+      <c r="F28" s="59"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="82" t="s">
         <v>158</v>
       </c>
-      <c r="N28" s="50"/>
-      <c r="O28" s="33">
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="32">
         <v>46319</v>
       </c>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
-      <c r="T28" s="38"/>
-      <c r="U28" s="38"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="84" t="s">
+      <c r="Q28" s="37"/>
+      <c r="R28" s="37"/>
+      <c r="S28" s="37"/>
+      <c r="T28" s="37"/>
+      <c r="U28" s="37"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="X28" s="84" t="s">
+      <c r="Y28" s="81" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Z28" s="81" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
+      <c r="D29" s="93"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
       <c r="G29" s="16"/>
       <c r="H29" s="16"/>
       <c r="I29" s="16"/>
@@ -2541,22 +2657,24 @@
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="62"/>
-      <c r="Q29" s="62"/>
-      <c r="R29" s="62"/>
-      <c r="S29" s="62"/>
-      <c r="T29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="60"/>
+      <c r="Q29" s="61"/>
+      <c r="R29" s="61"/>
+      <c r="S29" s="61"/>
+      <c r="T29" s="61"/>
       <c r="U29" s="16"/>
       <c r="V29" s="16"/>
       <c r="W29" s="16"/>
       <c r="X29" s="16"/>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
       <c r="I30" s="16"/>
@@ -2565,30 +2683,32 @@
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="62"/>
-      <c r="Q30" s="62"/>
-      <c r="R30" s="62"/>
-      <c r="S30" s="62"/>
-      <c r="T30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="60"/>
+      <c r="Q30" s="61"/>
+      <c r="R30" s="61"/>
+      <c r="S30" s="61"/>
+      <c r="T30" s="61"/>
       <c r="U30" s="16"/>
       <c r="V30" s="16"/>
       <c r="W30" s="16"/>
       <c r="X30" s="16"/>
-    </row>
-    <row r="31" spans="1:24" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+    </row>
+    <row r="31" spans="1:26" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16"/>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="98" t="s">
+      <c r="C31" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="99" t="s">
+      <c r="D31" s="93" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
       <c r="G31" s="16"/>
       <c r="H31" s="16"/>
       <c r="I31" s="16"/>
@@ -2597,22 +2717,24 @@
       <c r="L31" s="16"/>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
-      <c r="O31" s="61"/>
-      <c r="P31" s="62"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="62"/>
-      <c r="S31" s="62"/>
-      <c r="T31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="61"/>
+      <c r="R31" s="61"/>
+      <c r="S31" s="61"/>
+      <c r="T31" s="61"/>
       <c r="U31" s="16"/>
       <c r="V31" s="16"/>
       <c r="W31" s="16"/>
       <c r="X31" s="16"/>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="Y31" s="16"/>
+      <c r="Z31" s="16"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
       <c r="G32" s="16"/>
       <c r="H32" s="16"/>
       <c r="I32" s="16"/>
@@ -2621,30 +2743,32 @@
       <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
-      <c r="O32" s="61"/>
-      <c r="P32" s="62"/>
-      <c r="Q32" s="62"/>
-      <c r="R32" s="62"/>
-      <c r="S32" s="62"/>
-      <c r="T32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="61"/>
+      <c r="R32" s="61"/>
+      <c r="S32" s="61"/>
+      <c r="T32" s="61"/>
       <c r="U32" s="16"/>
       <c r="V32" s="16"/>
       <c r="W32" s="16"/>
       <c r="X32" s="16"/>
-    </row>
-    <row r="33" spans="1:24" ht="173" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y32" s="16"/>
+      <c r="Z32" s="16"/>
+    </row>
+    <row r="33" spans="1:26" ht="173" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16"/>
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="99" t="s">
+      <c r="C33" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="99" t="s">
+      <c r="D33" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
       <c r="G33" s="16"/>
       <c r="H33" s="16"/>
       <c r="I33" s="16"/>
@@ -2653,24 +2777,26 @@
       <c r="L33" s="16"/>
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
-      <c r="O33" s="61"/>
-      <c r="P33" s="62"/>
-      <c r="Q33" s="62"/>
-      <c r="R33" s="62"/>
-      <c r="S33" s="62"/>
-      <c r="T33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="60"/>
+      <c r="Q33" s="61"/>
+      <c r="R33" s="61"/>
+      <c r="S33" s="61"/>
+      <c r="T33" s="61"/>
       <c r="U33" s="16"/>
       <c r="V33" s="16"/>
       <c r="W33" s="16"/>
       <c r="X33" s="16"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="31" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="27" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9936FC7-299D-4C7E-9CD9-2B57E0570E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061DC89F-BE13-4A24-B510-C60BCECF2079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="182">
   <si>
     <t>№ п/п</t>
   </si>
@@ -511,9 +511,6 @@
     <t>приступили 23.09.26</t>
   </si>
   <si>
-    <t>питание не подавать пока не будет высушено помещение и шкафы</t>
-  </si>
-  <si>
     <t>по состоянию на 28.09</t>
   </si>
   <si>
@@ -597,14 +594,6 @@
 завершение планируется 04.10.26</t>
   </si>
   <si>
-    <t>работф выполняются. план завершения 07.10.2026</t>
-  </si>
-  <si>
-    <t>улица:
-выполнено/ done
-техническое помещение: работы выполняются (на завершение влияют работы по электрике)</t>
-  </si>
-  <si>
     <t>работы выполняются.
 План завершения - 10.10.26</t>
   </si>
@@ -618,6 +607,30 @@
   <si>
     <t>работы выполняются. 
 Ожидаемый срок завершения - 08.10.26</t>
+  </si>
+  <si>
+    <t>по состоянию на 05.10</t>
+  </si>
+  <si>
+    <t>19.09.26
+выполнено/done
+питание не подавать пока не будет высушено помещение и шкафы</t>
+  </si>
+  <si>
+    <t>04.10.26
+выполнено/done</t>
+  </si>
+  <si>
+    <t>работы выполняются. план завершения 07.10.2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+выполнено/done</t>
+  </si>
+  <si>
+    <t>улица:
+01.10. выполнено/ done
+техническое помещение (2 шланга): работы ожидают завершения  (на завершение влияют работы по электрике- 2.7.5.)</t>
   </si>
 </sst>
 </file>
@@ -627,7 +640,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -729,6 +742,13 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -811,7 +831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1029,9 +1049,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1095,11 +1112,20 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1108,24 +1134,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1341,63 +1365,68 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:Z33"/>
+  <dimension ref="A2:AB33"/>
   <sheetFormatPr defaultRowHeight="21" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.453125" customWidth="1"/>
-    <col min="2" max="2" width="51.54296875" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="0.36328125" style="91" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="51.453125" style="91" customWidth="1"/>
+    <col min="1" max="1" width="6.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="69.1796875" style="90" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="65.54296875" style="90" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="15" style="4" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="9" max="9" width="17.08984375" style="4" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="15" style="4" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.90625" style="4" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="37.453125" style="4" customWidth="1"/>
-    <col min="13" max="15" width="44.453125" style="4" customWidth="1"/>
-    <col min="16" max="16" width="15.08984375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="29.7265625" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="23.1796875" style="2" bestFit="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="24.08984375" style="9" customWidth="1"/>
-    <col min="20" max="20" width="24.6328125" style="2" customWidth="1"/>
-    <col min="21" max="21" width="21.1796875" customWidth="1"/>
-    <col min="22" max="22" width="23.08984375" customWidth="1"/>
-    <col min="23" max="26" width="43" customWidth="1"/>
+    <col min="6" max="6" width="29.36328125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="15" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="9" max="9" width="17.08984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="15" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.90625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="31" style="4" customWidth="1" collapsed="1"/>
+    <col min="13" max="13" width="30.7265625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="29.1796875" style="4" customWidth="1"/>
+    <col min="15" max="15" width="25.7265625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="44.453125" style="4" customWidth="1"/>
+    <col min="17" max="17" width="15.08984375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="29.7265625" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="23.1796875" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
+    <col min="21" max="21" width="24.6328125" style="2" customWidth="1"/>
+    <col min="22" max="22" width="21.1796875" customWidth="1"/>
+    <col min="23" max="23" width="23.08984375" customWidth="1"/>
+    <col min="24" max="27" width="43" customWidth="1"/>
+    <col min="28" max="28" width="47.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:26" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="97" t="s">
+    <row r="2" spans="1:28" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="97"/>
-      <c r="C2" s="97"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-    </row>
-    <row r="3" spans="1:26" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+    </row>
+    <row r="3" spans="1:28" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="84" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="85" t="s">
+      <c r="D3" s="84" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -1413,31 +1442,33 @@
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="15"/>
+      <c r="Q3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="Q3" s="14"/>
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
       <c r="T3" s="14"/>
-      <c r="U3" s="16"/>
+      <c r="U3" s="14"/>
       <c r="V3" s="16"/>
       <c r="W3" s="16"/>
       <c r="X3" s="16"/>
       <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
-    </row>
-    <row r="4" spans="1:26" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+    </row>
+    <row r="4" spans="1:28" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="85" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="86" t="s">
+      <c r="D4" s="85" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="18"/>
@@ -1459,61 +1490,67 @@
       <c r="K4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="L4" s="100" t="s">
+      <c r="L4" s="94" t="s">
         <v>143</v>
       </c>
-      <c r="M4" s="100" t="s">
-        <v>150</v>
-      </c>
-      <c r="N4" s="100" t="s">
-        <v>161</v>
-      </c>
-      <c r="O4" s="100" t="s">
-        <v>171</v>
-      </c>
-      <c r="P4" s="101"/>
-      <c r="Q4" s="102" t="s">
+      <c r="M4" s="94" t="s">
+        <v>149</v>
+      </c>
+      <c r="N4" s="94" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="94" t="s">
+        <v>170</v>
+      </c>
+      <c r="P4" s="94" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q4" s="95"/>
+      <c r="R4" s="96" t="s">
         <v>92</v>
       </c>
-      <c r="R4" s="102" t="s">
+      <c r="S4" s="96" t="s">
         <v>105</v>
       </c>
-      <c r="S4" s="102" t="s">
+      <c r="T4" s="96" t="s">
         <v>108</v>
       </c>
-      <c r="T4" s="102" t="s">
+      <c r="U4" s="96" t="s">
         <v>114</v>
       </c>
-      <c r="U4" s="103" t="s">
+      <c r="V4" s="97" t="s">
         <v>127</v>
       </c>
-      <c r="V4" s="103" t="s">
+      <c r="W4" s="97" t="s">
         <v>128</v>
       </c>
-      <c r="W4" s="104" t="s">
+      <c r="X4" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="X4" s="104" t="s">
-        <v>150</v>
-      </c>
-      <c r="Y4" s="104" t="s">
-        <v>161</v>
-      </c>
-      <c r="Z4" s="104" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y4" s="98" t="s">
+        <v>149</v>
+      </c>
+      <c r="Z4" s="98" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA4" s="98" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB4" s="98" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="87" t="s">
+      <c r="C5" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="88" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="22">
@@ -1529,13 +1566,13 @@
       <c r="M5" s="24"/>
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
-      <c r="P5" s="22">
+      <c r="P5" s="24"/>
+      <c r="Q5" s="22">
         <v>46277</v>
       </c>
-      <c r="Q5" s="25" t="s">
+      <c r="R5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="R5" s="26"/>
       <c r="S5" s="26"/>
       <c r="T5" s="26"/>
       <c r="U5" s="26"/>
@@ -1544,18 +1581,20 @@
       <c r="X5" s="26"/>
       <c r="Y5" s="26"/>
       <c r="Z5" s="26"/>
-    </row>
-    <row r="6" spans="1:26" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+    </row>
+    <row r="6" spans="1:28" ht="64" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="87" t="s">
+      <c r="C6" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="89" t="s">
+      <c r="D6" s="88" t="s">
         <v>66</v>
       </c>
       <c r="E6" s="22">
@@ -1573,37 +1612,39 @@
       <c r="M6" s="28"/>
       <c r="N6" s="28"/>
       <c r="O6" s="28"/>
-      <c r="P6" s="29">
+      <c r="P6" s="28"/>
+      <c r="Q6" s="29">
         <v>46280</v>
       </c>
-      <c r="Q6" s="26" t="s">
+      <c r="R6" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="S6" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="T6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="T6" s="26"/>
       <c r="U6" s="26"/>
       <c r="V6" s="26"/>
       <c r="W6" s="26"/>
       <c r="X6" s="26"/>
       <c r="Y6" s="26"/>
       <c r="Z6" s="26"/>
-    </row>
-    <row r="7" spans="1:26" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA6" s="26"/>
+      <c r="AB6" s="26"/>
+    </row>
+    <row r="7" spans="1:28" ht="95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="87" t="s">
+      <c r="C7" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="89" t="s">
+      <c r="D7" s="88" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="22">
@@ -1621,95 +1662,103 @@
       <c r="M7" s="56"/>
       <c r="N7" s="56"/>
       <c r="O7" s="56"/>
-      <c r="P7" s="22">
+      <c r="P7" s="56"/>
+      <c r="Q7" s="22">
         <v>46287</v>
       </c>
-      <c r="Q7" s="80"/>
-      <c r="R7" s="80"/>
-      <c r="S7" s="3" t="s">
+      <c r="R7" s="79"/>
+      <c r="S7" s="79"/>
+      <c r="T7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="T7" s="80" t="s">
+      <c r="U7" s="79" t="s">
         <v>118</v>
       </c>
-      <c r="U7" s="94" t="s">
+      <c r="V7" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="V7" s="79" t="s">
+      <c r="W7" s="78" t="s">
         <v>144</v>
       </c>
-      <c r="W7" s="79" t="s">
+      <c r="X7" s="78" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="79" t="s">
-        <v>160</v>
-      </c>
-      <c r="Y7" s="74" t="s">
+      <c r="Y7" s="78" t="s">
+        <v>159</v>
+      </c>
+      <c r="Z7" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA7" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="AB7" s="73" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="88" t="s">
+        <v>142</v>
+      </c>
+      <c r="E8" s="22">
+        <v>46288</v>
+      </c>
+      <c r="F8" s="23"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="M8" s="102" t="s">
+        <v>152</v>
+      </c>
+      <c r="N8" s="102" t="s">
         <v>163</v>
       </c>
-      <c r="Z7" s="74" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="88" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="88" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="90" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="64">
-        <v>46288</v>
-      </c>
-      <c r="F8" s="33"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="73" t="s">
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="22">
+        <v>46289</v>
+      </c>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="65"/>
+      <c r="V8" s="65"/>
+      <c r="W8" s="65"/>
+      <c r="X8" s="102" t="s">
+        <v>161</v>
+      </c>
+      <c r="Y8" s="65" t="s">
         <v>151</v>
       </c>
-      <c r="M8" s="82" t="s">
-        <v>153</v>
-      </c>
-      <c r="N8" s="82" t="s">
-        <v>164</v>
-      </c>
-      <c r="O8" s="34"/>
-      <c r="P8" s="64">
-        <v>46289</v>
-      </c>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="82" t="s">
-        <v>162</v>
-      </c>
-      <c r="X8" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Z8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Z8" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AB8" s="73" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39"/>
-      <c r="B9" s="88"/>
-      <c r="C9" s="88"/>
-      <c r="D9" s="90"/>
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="89"/>
       <c r="E9" s="40"/>
       <c r="F9" s="35"/>
       <c r="G9" s="41"/>
@@ -1721,31 +1770,33 @@
       <c r="M9" s="41"/>
       <c r="N9" s="41"/>
       <c r="O9" s="41"/>
-      <c r="P9" s="40" t="s">
+      <c r="P9" s="41"/>
+      <c r="Q9" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="Q9" s="42"/>
       <c r="R9" s="42"/>
       <c r="S9" s="42"/>
       <c r="T9" s="42"/>
-      <c r="U9" s="38"/>
+      <c r="U9" s="42"/>
       <c r="V9" s="38"/>
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
       <c r="Y9" s="38"/>
       <c r="Z9" s="38"/>
-    </row>
-    <row r="10" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+    </row>
+    <row r="10" spans="1:28" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="88" t="s">
+      <c r="C10" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="90" t="s">
+      <c r="D10" s="89" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="64">
@@ -1758,38 +1809,42 @@
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
       <c r="L10" s="41"/>
-      <c r="M10" s="82" t="s">
-        <v>154</v>
-      </c>
-      <c r="N10" s="82" t="s">
-        <v>164</v>
+      <c r="M10" s="81" t="s">
+        <v>153</v>
+      </c>
+      <c r="N10" s="81" t="s">
+        <v>163</v>
       </c>
       <c r="O10" s="34"/>
-      <c r="P10" s="64">
+      <c r="P10" s="34"/>
+      <c r="Q10" s="64">
         <v>46292</v>
       </c>
-      <c r="Q10" s="37"/>
       <c r="R10" s="37"/>
       <c r="S10" s="37"/>
       <c r="T10" s="37"/>
       <c r="U10" s="37"/>
       <c r="V10" s="37"/>
       <c r="W10" s="37"/>
-      <c r="X10" s="82" t="s">
-        <v>169</v>
-      </c>
-      <c r="Y10" s="5" t="s">
-        <v>167</v>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="81" t="s">
+        <v>168</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+      <c r="AA10" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB10" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="90"/>
+      <c r="B11" s="87"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="89"/>
       <c r="E11" s="40" t="s">
         <v>125</v>
       </c>
@@ -1803,31 +1858,33 @@
       <c r="M11" s="41"/>
       <c r="N11" s="41"/>
       <c r="O11" s="41"/>
-      <c r="P11" s="40" t="s">
+      <c r="P11" s="41"/>
+      <c r="Q11" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="Q11" s="42"/>
       <c r="R11" s="42"/>
       <c r="S11" s="42"/>
       <c r="T11" s="42"/>
-      <c r="U11" s="38"/>
+      <c r="U11" s="42"/>
       <c r="V11" s="38"/>
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
       <c r="Y11" s="38"/>
       <c r="Z11" s="38"/>
-    </row>
-    <row r="12" spans="1:26" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA11" s="38"/>
+      <c r="AB11" s="38"/>
+    </row>
+    <row r="12" spans="1:28" ht="78" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="90" t="s">
+      <c r="D12" s="89" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="32">
@@ -1839,45 +1896,49 @@
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
-      <c r="L12" s="84" t="s">
+      <c r="L12" s="83" t="s">
         <v>94</v>
       </c>
       <c r="M12" s="34"/>
       <c r="N12" s="34"/>
       <c r="O12" s="34"/>
-      <c r="P12" s="64">
+      <c r="P12" s="34"/>
+      <c r="Q12" s="64">
         <v>46292</v>
       </c>
-      <c r="Q12" s="37"/>
       <c r="R12" s="37"/>
       <c r="S12" s="37"/>
       <c r="T12" s="37"/>
       <c r="U12" s="37"/>
       <c r="V12" s="37"/>
-      <c r="W12" s="5" t="s">
+      <c r="W12" s="37"/>
+      <c r="X12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="X12" s="5" t="s">
-        <v>155</v>
-      </c>
       <c r="Y12" s="5" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+      <c r="AA12" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB12" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="88" t="s">
+      <c r="C13" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="90" t="s">
+      <c r="D13" s="89" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="32">
@@ -1890,84 +1951,94 @@
       <c r="J13" s="34"/>
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
-      <c r="M13" s="84" t="s">
+      <c r="M13" s="83" t="s">
         <v>119</v>
       </c>
       <c r="N13" s="34"/>
       <c r="O13" s="34"/>
-      <c r="P13" s="64">
+      <c r="P13" s="34"/>
+      <c r="Q13" s="64">
         <v>46295</v>
       </c>
-      <c r="Q13" s="37"/>
       <c r="R13" s="37"/>
       <c r="S13" s="37"/>
       <c r="T13" s="37"/>
       <c r="U13" s="37"/>
       <c r="V13" s="37"/>
       <c r="W13" s="37"/>
-      <c r="X13" s="5" t="s">
-        <v>95</v>
-      </c>
+      <c r="X13" s="37"/>
       <c r="Y13" s="5" t="s">
         <v>95</v>
       </c>
       <c r="Z13" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="30" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" s="107" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="88" t="s">
+      <c r="B14" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="88" t="s">
+      <c r="C14" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="90" t="s">
+      <c r="D14" s="88" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="64">
+      <c r="E14" s="22">
         <v>46296</v>
       </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="95" t="s">
-        <v>166</v>
-      </c>
-      <c r="M14" s="34"/>
-      <c r="N14" s="96" t="s">
-        <v>170</v>
-      </c>
-      <c r="O14" s="96" t="s">
-        <v>176</v>
-      </c>
-      <c r="P14" s="32">
+      <c r="F14" s="23"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="104" t="s">
+        <v>165</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="105" t="s">
+        <v>169</v>
+      </c>
+      <c r="O14" s="105" t="s">
+        <v>173</v>
+      </c>
+      <c r="P14" s="106" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q14" s="22">
         <v>46300</v>
       </c>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="37"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="37"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="37"/>
-      <c r="Z14" s="105" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="R14" s="65"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="65"/>
+      <c r="U14" s="65"/>
+      <c r="V14" s="65"/>
+      <c r="W14" s="65"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="65"/>
+      <c r="Z14" s="65"/>
+      <c r="AA14" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="AB14" s="73" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39"/>
       <c r="B15" s="71"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="90"/>
+      <c r="C15" s="87"/>
+      <c r="D15" s="89"/>
       <c r="E15" s="72"/>
       <c r="F15" s="35"/>
       <c r="G15" s="41"/>
@@ -1979,8 +2050,8 @@
       <c r="M15" s="41"/>
       <c r="N15" s="41"/>
       <c r="O15" s="41"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="42"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="32"/>
       <c r="R15" s="42"/>
       <c r="S15" s="42"/>
       <c r="T15" s="42"/>
@@ -1990,18 +2061,20 @@
       <c r="X15" s="42"/>
       <c r="Y15" s="42"/>
       <c r="Z15" s="42"/>
-    </row>
-    <row r="16" spans="1:26" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+    </row>
+    <row r="16" spans="1:28" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="43" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="85" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="45"/>
@@ -2015,8 +2088,8 @@
       <c r="M16" s="47"/>
       <c r="N16" s="47"/>
       <c r="O16" s="47"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="47"/>
+      <c r="Q16" s="45"/>
       <c r="R16" s="48"/>
       <c r="S16" s="48"/>
       <c r="T16" s="48"/>
@@ -2026,18 +2099,20 @@
       <c r="X16" s="48"/>
       <c r="Y16" s="48"/>
       <c r="Z16" s="48"/>
-    </row>
-    <row r="17" spans="1:26" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA16" s="48"/>
+      <c r="AB16" s="48"/>
+    </row>
+    <row r="17" spans="1:28" ht="134" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="66" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="87" t="s">
+      <c r="C17" s="86" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="89" t="s">
+      <c r="D17" s="88" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="22">
@@ -2055,117 +2130,123 @@
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
-      <c r="P17" s="70">
+      <c r="P17" s="28"/>
+      <c r="Q17" s="70">
         <v>46278</v>
       </c>
-      <c r="Q17" s="3" t="s">
+      <c r="R17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="S17" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="T17" s="3" t="s">
+      <c r="U17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="U17" s="3" t="s">
+      <c r="V17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="V17" s="10" t="s">
+      <c r="W17" s="73" t="s">
         <v>140</v>
       </c>
-      <c r="W17" s="83" t="s">
-        <v>149</v>
-      </c>
-      <c r="X17" s="83" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y17" s="83" t="s">
-        <v>149</v>
-      </c>
-      <c r="Z17" s="83" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X17" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y17" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z17" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="AA17" s="82" t="s">
+        <v>177</v>
+      </c>
+      <c r="AB17" s="82" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="66" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="87" t="s">
+      <c r="C18" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="89" t="s">
+      <c r="D18" s="88" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="70">
         <v>46279</v>
       </c>
-      <c r="F18" s="75" t="s">
+      <c r="F18" s="74" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="76" t="s">
+      <c r="G18" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="76" t="s">
+      <c r="I18" s="75" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="77" t="s">
+      <c r="J18" s="76" t="s">
         <v>131</v>
       </c>
-      <c r="K18" s="77" t="s">
+      <c r="K18" s="76" t="s">
         <v>141</v>
       </c>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
-      <c r="P18" s="70">
+      <c r="P18" s="28"/>
+      <c r="Q18" s="70">
         <v>46280</v>
       </c>
-      <c r="Q18" s="78" t="s">
+      <c r="R18" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="R18" s="78" t="s">
+      <c r="S18" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="S18" s="78" t="s">
+      <c r="T18" s="77" t="s">
         <v>132</v>
       </c>
-      <c r="T18" s="78" t="s">
+      <c r="U18" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="U18" s="3" t="s">
+      <c r="V18" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="V18" s="79" t="s">
+      <c r="W18" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="W18" s="74" t="s">
+      <c r="X18" s="73" t="s">
         <v>146</v>
       </c>
-      <c r="X18" s="74"/>
-      <c r="Y18" s="74"/>
-      <c r="Z18" s="74"/>
-    </row>
-    <row r="19" spans="1:26" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y18" s="73"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="73"/>
+      <c r="AB18" s="73"/>
+    </row>
+    <row r="19" spans="1:28" ht="53" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="66" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="87" t="s">
+      <c r="C19" s="86" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="89" t="s">
+      <c r="D19" s="88" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="68">
@@ -2183,41 +2264,43 @@
       <c r="M19" s="28"/>
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
-      <c r="P19" s="22">
+      <c r="P19" s="28"/>
+      <c r="Q19" s="22">
         <v>46288</v>
-      </c>
-      <c r="Q19" s="26" t="s">
-        <v>99</v>
       </c>
       <c r="R19" s="26" t="s">
         <v>99</v>
       </c>
       <c r="S19" s="26" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="T19" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="U19" s="10" t="s">
+      <c r="U19" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="V19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="V19" s="69"/>
       <c r="W19" s="69"/>
       <c r="X19" s="69"/>
       <c r="Y19" s="69"/>
       <c r="Z19" s="69"/>
-    </row>
-    <row r="20" spans="1:26" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA19" s="69"/>
+      <c r="AB19" s="69"/>
+    </row>
+    <row r="20" spans="1:28" ht="68" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="66" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="87" t="s">
+      <c r="C20" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="89" t="s">
+      <c r="D20" s="88" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="68">
@@ -2235,39 +2318,41 @@
       <c r="M20" s="28"/>
       <c r="N20" s="28"/>
       <c r="O20" s="28"/>
-      <c r="P20" s="22">
+      <c r="P20" s="28"/>
+      <c r="Q20" s="22">
         <v>46288</v>
       </c>
-      <c r="Q20" s="65"/>
       <c r="R20" s="65"/>
       <c r="S20" s="65"/>
-      <c r="T20" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="T20" s="65"/>
       <c r="U20" s="3" t="s">
         <v>95</v>
       </c>
       <c r="V20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="W20" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="W20" s="74" t="s">
+      <c r="X20" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="X20" s="74"/>
-      <c r="Y20" s="74"/>
-      <c r="Z20" s="74"/>
-    </row>
-    <row r="21" spans="1:26" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="73"/>
+      <c r="AB20" s="73"/>
+    </row>
+    <row r="21" spans="1:28" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="66" t="s">
         <v>26</v>
       </c>
       <c r="B21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="88" t="s">
         <v>68</v>
       </c>
       <c r="E21" s="22">
@@ -2285,41 +2370,43 @@
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
-      <c r="P21" s="22">
+      <c r="P21" s="28"/>
+      <c r="Q21" s="22">
         <v>46288</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="R21" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="U21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="U21" s="10" t="s">
+      <c r="V21" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="V21" s="67"/>
       <c r="W21" s="67"/>
       <c r="X21" s="67"/>
       <c r="Y21" s="67"/>
       <c r="Z21" s="67"/>
-    </row>
-    <row r="22" spans="1:26" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA21" s="67"/>
+      <c r="AB21" s="67"/>
+    </row>
+    <row r="22" spans="1:28" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="87" t="s">
+      <c r="C22" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="89" t="s">
+      <c r="D22" s="88" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="22">
@@ -2337,33 +2424,35 @@
       <c r="M22" s="24"/>
       <c r="N22" s="24"/>
       <c r="O22" s="24"/>
-      <c r="P22" s="22">
+      <c r="P22" s="24"/>
+      <c r="Q22" s="22">
         <v>46289</v>
       </c>
-      <c r="Q22" s="65"/>
       <c r="R22" s="65"/>
       <c r="S22" s="65"/>
       <c r="T22" s="65"/>
-      <c r="U22" s="10" t="s">
+      <c r="U22" s="65"/>
+      <c r="V22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="V22" s="65"/>
       <c r="W22" s="65"/>
       <c r="X22" s="65"/>
       <c r="Y22" s="65"/>
       <c r="Z22" s="65"/>
-    </row>
-    <row r="23" spans="1:26" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+    </row>
+    <row r="23" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="39" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="88" t="s">
+      <c r="C23" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="90" t="s">
+      <c r="D23" s="89" t="s">
         <v>138</v>
       </c>
       <c r="E23" s="32">
@@ -2381,10 +2470,10 @@
       <c r="M23" s="49"/>
       <c r="N23" s="49"/>
       <c r="O23" s="49"/>
-      <c r="P23" s="32">
+      <c r="P23" s="49"/>
+      <c r="Q23" s="32">
         <v>46319</v>
       </c>
-      <c r="Q23" s="37"/>
       <c r="R23" s="37"/>
       <c r="S23" s="37"/>
       <c r="T23" s="37"/>
@@ -2394,18 +2483,20 @@
       <c r="X23" s="37"/>
       <c r="Y23" s="37"/>
       <c r="Z23" s="37"/>
-    </row>
-    <row r="24" spans="1:26" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA23" s="37"/>
+      <c r="AB23" s="37"/>
+    </row>
+    <row r="24" spans="1:28" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
         <v>77</v>
       </c>
       <c r="B24" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="89" t="s">
+      <c r="C24" s="88" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="89" t="s">
+      <c r="D24" s="88" t="s">
         <v>71</v>
       </c>
       <c r="E24" s="22">
@@ -2423,13 +2514,13 @@
       <c r="M24" s="54"/>
       <c r="N24" s="54"/>
       <c r="O24" s="54"/>
-      <c r="P24" s="22">
+      <c r="P24" s="54"/>
+      <c r="Q24" s="22">
         <v>46278</v>
       </c>
-      <c r="Q24" s="10" t="s">
+      <c r="R24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -2438,18 +2529,20 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
-    </row>
-    <row r="25" spans="1:26" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+    </row>
+    <row r="25" spans="1:28" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="51" t="s">
         <v>78</v>
       </c>
       <c r="B25" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="89" t="s">
+      <c r="C25" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="89" t="s">
+      <c r="D25" s="88" t="s">
         <v>103</v>
       </c>
       <c r="E25" s="29">
@@ -2471,37 +2564,39 @@
       <c r="M25" s="56"/>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
-      <c r="P25" s="29">
+      <c r="P25" s="56"/>
+      <c r="Q25" s="29">
         <v>46281</v>
-      </c>
-      <c r="Q25" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="S25" s="10" t="s">
+      <c r="S25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="T25" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
-    </row>
-    <row r="26" spans="1:26" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+    </row>
+    <row r="26" spans="1:28" ht="52" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="66" t="s">
         <v>79</v>
       </c>
       <c r="B26" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="89" t="s">
+      <c r="C26" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="89" t="s">
+      <c r="D26" s="88" t="s">
         <v>104</v>
       </c>
       <c r="E26" s="68">
@@ -2519,42 +2614,44 @@
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
       <c r="O26" s="28"/>
-      <c r="P26" s="22">
+      <c r="P26" s="28"/>
+      <c r="Q26" s="22">
         <v>46285</v>
       </c>
-      <c r="Q26" s="80"/>
-      <c r="R26" s="80"/>
-      <c r="S26" s="6" t="s">
-        <v>95</v>
-      </c>
+      <c r="R26" s="79"/>
+      <c r="S26" s="79"/>
       <c r="T26" s="6" t="s">
         <v>95</v>
       </c>
       <c r="U26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="V26" s="79" t="s">
+      <c r="V26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="W26" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="W26" s="74" t="s">
+      <c r="X26" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="X26" s="74"/>
-      <c r="Y26" s="74"/>
-      <c r="Z26" s="74"/>
-    </row>
-    <row r="27" spans="1:26" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="73"/>
+      <c r="AB26" s="73"/>
+    </row>
+    <row r="27" spans="1:28" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="30" t="s">
         <v>80</v>
       </c>
       <c r="B27" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="90" t="s">
+      <c r="C27" s="89" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="90" t="s">
-        <v>156</v>
+      <c r="D27" s="89" t="s">
+        <v>155</v>
       </c>
       <c r="E27" s="64">
         <v>46286</v>
@@ -2564,49 +2661,53 @@
       <c r="H27" s="58"/>
       <c r="I27" s="49"/>
       <c r="J27" s="49"/>
-      <c r="K27" s="82" t="s">
+      <c r="K27" s="81" t="s">
         <v>135</v>
       </c>
-      <c r="L27" s="82" t="s">
+      <c r="L27" s="81" t="s">
         <v>148</v>
       </c>
       <c r="M27" s="49"/>
       <c r="N27" s="49"/>
       <c r="O27" s="49"/>
-      <c r="P27" s="64">
+      <c r="P27" s="49"/>
+      <c r="Q27" s="64">
         <v>46293</v>
       </c>
-      <c r="Q27" s="37"/>
       <c r="R27" s="37"/>
       <c r="S27" s="37"/>
       <c r="T27" s="37"/>
       <c r="U27" s="37"/>
       <c r="V27" s="37"/>
-      <c r="W27" s="81" t="s">
+      <c r="W27" s="37"/>
+      <c r="X27" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="X27" s="81" t="s">
-        <v>159</v>
-      </c>
-      <c r="Y27" s="81" t="s">
-        <v>168</v>
-      </c>
-      <c r="Z27" s="81" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y27" s="80" t="s">
+        <v>158</v>
+      </c>
+      <c r="Z27" s="80" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA27" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB27" s="80" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
         <v>81</v>
       </c>
       <c r="B28" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="90" t="s">
+      <c r="C28" s="89" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="90" t="s">
-        <v>157</v>
+      <c r="D28" s="89" t="s">
+        <v>156</v>
       </c>
       <c r="E28" s="32">
         <v>46294</v>
@@ -2618,35 +2719,39 @@
       <c r="J28" s="49"/>
       <c r="K28" s="49"/>
       <c r="L28" s="49"/>
-      <c r="M28" s="82" t="s">
-        <v>158</v>
+      <c r="M28" s="81" t="s">
+        <v>157</v>
       </c>
       <c r="N28" s="49"/>
       <c r="O28" s="49"/>
-      <c r="P28" s="32">
+      <c r="P28" s="49"/>
+      <c r="Q28" s="32">
         <v>46319</v>
       </c>
-      <c r="Q28" s="37"/>
       <c r="R28" s="37"/>
       <c r="S28" s="37"/>
       <c r="T28" s="37"/>
       <c r="U28" s="37"/>
       <c r="V28" s="37"/>
       <c r="W28" s="37"/>
-      <c r="X28" s="81" t="s">
+      <c r="X28" s="37"/>
+      <c r="Y28" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="Y28" s="81" t="s">
+      <c r="Z28" s="80" t="s">
         <v>95</v>
       </c>
-      <c r="Z28" s="81" t="s">
+      <c r="AA28" s="80" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="AB28" s="80" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
-      <c r="D29" s="93"/>
+      <c r="D29" s="92"/>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
       <c r="G29" s="16"/>
@@ -2658,19 +2763,21 @@
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
-      <c r="P29" s="60"/>
-      <c r="Q29" s="61"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="60"/>
       <c r="R29" s="61"/>
       <c r="S29" s="61"/>
       <c r="T29" s="61"/>
-      <c r="U29" s="16"/>
+      <c r="U29" s="61"/>
       <c r="V29" s="16"/>
       <c r="W29" s="16"/>
       <c r="X29" s="16"/>
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="16"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="E30" s="60"/>
@@ -2684,27 +2791,29 @@
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
-      <c r="P30" s="60"/>
-      <c r="Q30" s="61"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="60"/>
       <c r="R30" s="61"/>
       <c r="S30" s="61"/>
       <c r="T30" s="61"/>
-      <c r="U30" s="16"/>
+      <c r="U30" s="61"/>
       <c r="V30" s="16"/>
       <c r="W30" s="16"/>
       <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
-    </row>
-    <row r="31" spans="1:26" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA30" s="16"/>
+      <c r="AB30" s="16"/>
+    </row>
+    <row r="31" spans="1:28" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16"/>
       <c r="B31" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="92" t="s">
+      <c r="C31" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="92" t="s">
         <v>82</v>
       </c>
       <c r="E31" s="60"/>
@@ -2718,19 +2827,21 @@
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
-      <c r="P31" s="60"/>
-      <c r="Q31" s="61"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="60"/>
       <c r="R31" s="61"/>
       <c r="S31" s="61"/>
       <c r="T31" s="61"/>
-      <c r="U31" s="16"/>
+      <c r="U31" s="61"/>
       <c r="V31" s="16"/>
       <c r="W31" s="16"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
       <c r="Z31" s="16"/>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.35">
+      <c r="AA31" s="16"/>
+      <c r="AB31" s="16"/>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="E32" s="60"/>
@@ -2744,27 +2855,29 @@
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
       <c r="O32" s="16"/>
-      <c r="P32" s="60"/>
-      <c r="Q32" s="61"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="60"/>
       <c r="R32" s="61"/>
       <c r="S32" s="61"/>
       <c r="T32" s="61"/>
-      <c r="U32" s="16"/>
+      <c r="U32" s="61"/>
       <c r="V32" s="16"/>
       <c r="W32" s="16"/>
       <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
-    </row>
-    <row r="33" spans="1:26" ht="173" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AA32" s="16"/>
+      <c r="AB32" s="16"/>
+    </row>
+    <row r="33" spans="1:28" ht="173" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16"/>
       <c r="B33" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="93" t="s">
+      <c r="C33" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="93" t="s">
+      <c r="D33" s="92" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="60"/>
@@ -2778,25 +2891,27 @@
       <c r="M33" s="16"/>
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
-      <c r="P33" s="60"/>
-      <c r="Q33" s="61"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="60"/>
       <c r="R33" s="61"/>
       <c r="S33" s="61"/>
       <c r="T33" s="61"/>
-      <c r="U33" s="16"/>
+      <c r="U33" s="61"/>
       <c r="V33" s="16"/>
       <c r="W33" s="16"/>
       <c r="X33" s="16"/>
       <c r="Y33" s="16"/>
       <c r="Z33" s="16"/>
+      <c r="AA33" s="16"/>
+      <c r="AB33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A2:Q2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="27" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="29" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{061DC89F-BE13-4A24-B510-C60BCECF2079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C923CE41-BF42-4F41-8380-0FDECFBD3053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -483,10 +483,6 @@
 </t>
   </si>
   <si>
-    <t>не заверешено. Идет процесс выверения отклонений. Планируемый срок заврешения - 29.09.26
-у Замперла запрошена проектная документация для передачи в Модус во избежание бесконечных подвижек</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">выполнено/done
 </t>
@@ -631,6 +627,10 @@
     <t>улица:
 01.10. выполнено/ done
 техническое помещение (2 шланга): работы ожидают завершения  (на завершение влияют работы по электрике- 2.7.5.)</t>
+  </si>
+  <si>
+    <t>не заверешено. Идет процесс выверения отклонений. Планируемый срок заврешения - 29.09.26
+у Замперла запрошена проектная документация для  во избежание бесконечных подвижек</t>
   </si>
 </sst>
 </file>
@@ -1127,6 +1127,22 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1134,22 +1150,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1373,13 +1373,13 @@
     <col min="3" max="3" width="69.1796875" style="90" bestFit="1" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="65.54296875" style="90" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.36328125" style="8" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="13.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="8" width="15" style="4" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <col min="9" max="9" width="17.08984375" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="10" max="10" width="15" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="11" max="11" width="19.90625" style="4" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="31" style="4" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="8" width="15" style="4" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <col min="9" max="9" width="17.08984375" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="10" max="10" width="15" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="11" max="11" width="19.90625" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="12" max="12" width="31" style="4" customWidth="1"/>
     <col min="13" max="13" width="30.7265625" style="4" customWidth="1"/>
     <col min="14" max="14" width="29.1796875" style="4" customWidth="1"/>
     <col min="15" max="15" width="25.7265625" style="4" customWidth="1"/>
@@ -1396,25 +1396,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="99"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="101"/>
-      <c r="Q2" s="101"/>
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
     </row>
     <row r="3" spans="1:28" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
@@ -1494,16 +1494,16 @@
         <v>143</v>
       </c>
       <c r="M4" s="94" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N4" s="94" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O4" s="94" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P4" s="94" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q4" s="95"/>
       <c r="R4" s="96" t="s">
@@ -1528,16 +1528,16 @@
         <v>143</v>
       </c>
       <c r="Y4" s="98" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Z4" s="98" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA4" s="98" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB4" s="98" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="69" customHeight="1" x14ac:dyDescent="0.35">
@@ -1681,23 +1681,23 @@
         <v>144</v>
       </c>
       <c r="X7" s="78" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="Y7" s="78" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z7" s="73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AA7" s="73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AB7" s="73" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="100" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="86" t="s">
@@ -1719,13 +1719,13 @@
       <c r="J8" s="24"/>
       <c r="K8" s="24"/>
       <c r="L8" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="M8" s="102" t="s">
-        <v>152</v>
-      </c>
-      <c r="N8" s="102" t="s">
-        <v>163</v>
+        <v>149</v>
+      </c>
+      <c r="M8" s="99" t="s">
+        <v>151</v>
+      </c>
+      <c r="N8" s="99" t="s">
+        <v>162</v>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
@@ -1738,20 +1738,20 @@
       <c r="U8" s="65"/>
       <c r="V8" s="65"/>
       <c r="W8" s="65"/>
-      <c r="X8" s="102" t="s">
-        <v>161</v>
+      <c r="X8" s="99" t="s">
+        <v>160</v>
       </c>
       <c r="Y8" s="65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AB8" s="73" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1810,10 +1810,10 @@
       <c r="K10" s="34"/>
       <c r="L10" s="41"/>
       <c r="M10" s="81" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N10" s="81" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O10" s="34"/>
       <c r="P10" s="34"/>
@@ -1828,16 +1828,16 @@
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
       <c r="Y10" s="81" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="1" customHeight="1" x14ac:dyDescent="0.35">
@@ -1916,16 +1916,16 @@
         <v>95</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="82" customHeight="1" x14ac:dyDescent="0.35">
@@ -1974,13 +1974,13 @@
         <v>95</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB13" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" s="107" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" s="104" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="66" t="s">
         <v>15</v>
       </c>
@@ -2002,17 +2002,17 @@
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="104" t="s">
-        <v>165</v>
+      <c r="L14" s="101" t="s">
+        <v>164</v>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="105" t="s">
-        <v>169</v>
-      </c>
-      <c r="O14" s="105" t="s">
-        <v>173</v>
-      </c>
-      <c r="P14" s="106" t="s">
+      <c r="N14" s="102" t="s">
+        <v>168</v>
+      </c>
+      <c r="O14" s="102" t="s">
+        <v>172</v>
+      </c>
+      <c r="P14" s="103" t="s">
         <v>119</v>
       </c>
       <c r="Q14" s="22">
@@ -2028,10 +2028,10 @@
       <c r="Y14" s="65"/>
       <c r="Z14" s="65"/>
       <c r="AA14" s="26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AB14" s="73" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.35">
@@ -2153,19 +2153,19 @@
         <v>140</v>
       </c>
       <c r="X17" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y17" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z17" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AA17" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB17" s="82" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2229,7 +2229,7 @@
         <v>137</v>
       </c>
       <c r="X18" s="73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y18" s="73"/>
       <c r="Z18" s="73"/>
@@ -2335,7 +2335,7 @@
         <v>136</v>
       </c>
       <c r="X20" s="73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y20" s="73"/>
       <c r="Z20" s="73"/>
@@ -2633,7 +2633,7 @@
         <v>139</v>
       </c>
       <c r="X26" s="73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Y26" s="73"/>
       <c r="Z26" s="73"/>
@@ -2651,7 +2651,7 @@
         <v>116</v>
       </c>
       <c r="D27" s="89" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E27" s="64">
         <v>46286</v>
@@ -2665,7 +2665,7 @@
         <v>135</v>
       </c>
       <c r="L27" s="81" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M27" s="49"/>
       <c r="N27" s="49"/>
@@ -2684,16 +2684,16 @@
         <v>95</v>
       </c>
       <c r="Y27" s="80" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z27" s="80" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AA27" s="80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AB27" s="80" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2707,7 +2707,7 @@
         <v>117</v>
       </c>
       <c r="D28" s="89" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E28" s="32">
         <v>46294</v>
@@ -2720,7 +2720,7 @@
       <c r="K28" s="49"/>
       <c r="L28" s="49"/>
       <c r="M28" s="81" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="N28" s="49"/>
       <c r="O28" s="49"/>

--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C923CE41-BF42-4F41-8380-0FDECFBD3053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EED8E8-E02F-48C3-B3AF-3AE392027FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     <t>по состоянию на 21.09</t>
   </si>
   <si>
-    <t>План выполнить 19.09.26</t>
-  </si>
-  <si>
     <t>Работы выполняются. Ожидаемый срок завершения установки - 19.09.26</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   <si>
     <t>не заверешено. Идет процесс выверения отклонений. Планируемый срок заврешения - 29.09.26
 у Замперла запрошена проектная документация для  во избежание бесконечных подвижек</t>
+  </si>
+  <si>
+    <t>Планируется выполнить 19.09.26</t>
   </si>
 </sst>
 </file>
@@ -1052,17 +1052,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1150,6 +1141,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1370,8 +1370,8 @@
   <cols>
     <col min="1" max="1" width="6.36328125" customWidth="1"/>
     <col min="2" max="2" width="51.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="69.1796875" style="90" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="65.54296875" style="90" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.1796875" style="87" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="65.54296875" style="87" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
@@ -1385,9 +1385,9 @@
     <col min="15" max="15" width="25.7265625" style="4" customWidth="1"/>
     <col min="16" max="16" width="44.453125" style="4" customWidth="1"/>
     <col min="17" max="17" width="15.08984375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.7265625" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="23.1796875" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="24.08984375" style="9" customWidth="1" collapsed="1"/>
+    <col min="18" max="18" width="29.7265625" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="23.1796875" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="24.08984375" style="9" customWidth="1"/>
     <col min="21" max="21" width="24.6328125" style="2" customWidth="1"/>
     <col min="22" max="22" width="21.1796875" customWidth="1"/>
     <col min="23" max="23" width="23.08984375" customWidth="1"/>
@@ -1396,25 +1396,25 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:28" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
+      <c r="B2" s="102"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+      <c r="J2" s="104"/>
+      <c r="K2" s="104"/>
+      <c r="L2" s="104"/>
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
     </row>
     <row r="3" spans="1:28" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
@@ -1423,10 +1423,10 @@
       <c r="B3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="C3" s="81" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="81" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="13" t="s">
@@ -1462,13 +1462,13 @@
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="82" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="82" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="85" t="s">
+      <c r="D4" s="82" t="s">
         <v>3</v>
       </c>
       <c r="E4" s="18"/>
@@ -1490,67 +1490,67 @@
       <c r="K4" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="L4" s="94" t="s">
-        <v>143</v>
-      </c>
-      <c r="M4" s="94" t="s">
-        <v>148</v>
-      </c>
-      <c r="N4" s="94" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="94" t="s">
-        <v>169</v>
-      </c>
-      <c r="P4" s="94" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="96" t="s">
+      <c r="L4" s="91" t="s">
+        <v>142</v>
+      </c>
+      <c r="M4" s="91" t="s">
+        <v>147</v>
+      </c>
+      <c r="N4" s="91" t="s">
+        <v>158</v>
+      </c>
+      <c r="O4" s="91" t="s">
+        <v>168</v>
+      </c>
+      <c r="P4" s="91" t="s">
+        <v>174</v>
+      </c>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="S4" s="96" t="s">
+      <c r="S4" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="T4" s="96" t="s">
+      <c r="T4" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="U4" s="96" t="s">
+      <c r="U4" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="V4" s="97" t="s">
+      <c r="V4" s="94" t="s">
         <v>127</v>
       </c>
-      <c r="W4" s="97" t="s">
+      <c r="W4" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="X4" s="98" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y4" s="98" t="s">
-        <v>148</v>
-      </c>
-      <c r="Z4" s="98" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA4" s="98" t="s">
-        <v>169</v>
-      </c>
-      <c r="AB4" s="98" t="s">
-        <v>175</v>
+      <c r="X4" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="Y4" s="95" t="s">
+        <v>147</v>
+      </c>
+      <c r="Z4" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA4" s="95" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB4" s="95" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="69" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="86" t="s">
+      <c r="B5" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="86" t="s">
+      <c r="C5" s="83" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="88" t="s">
+      <c r="D5" s="85" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="22">
@@ -1567,7 +1567,7 @@
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
-      <c r="Q5" s="22">
+      <c r="Q5" s="70">
         <v>46277</v>
       </c>
       <c r="R5" s="25" t="s">
@@ -1588,13 +1588,13 @@
       <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="83" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="85" t="s">
         <v>66</v>
       </c>
       <c r="E6" s="22">
@@ -1613,7 +1613,7 @@
       <c r="N6" s="28"/>
       <c r="O6" s="28"/>
       <c r="P6" s="28"/>
-      <c r="Q6" s="29">
+      <c r="Q6" s="70">
         <v>46280</v>
       </c>
       <c r="R6" s="26" t="s">
@@ -1638,13 +1638,13 @@
       <c r="A7" s="66" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="83" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="85" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="22">
@@ -1663,53 +1663,53 @@
       <c r="N7" s="56"/>
       <c r="O7" s="56"/>
       <c r="P7" s="56"/>
-      <c r="Q7" s="22">
+      <c r="Q7" s="70">
         <v>46287</v>
       </c>
-      <c r="R7" s="79"/>
-      <c r="S7" s="79"/>
+      <c r="R7" s="76"/>
+      <c r="S7" s="76"/>
       <c r="T7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="U7" s="79" t="s">
+      <c r="U7" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="V7" s="93" t="s">
+      <c r="V7" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="W7" s="78" t="s">
-        <v>144</v>
-      </c>
-      <c r="X7" s="78" t="s">
-        <v>181</v>
-      </c>
-      <c r="Y7" s="78" t="s">
-        <v>158</v>
+      <c r="W7" s="75" t="s">
+        <v>143</v>
+      </c>
+      <c r="X7" s="75" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y7" s="75" t="s">
+        <v>157</v>
       </c>
       <c r="Z7" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AA7" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AB7" s="73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="83" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="88" t="s">
-        <v>142</v>
-      </c>
-      <c r="E8" s="22">
+      <c r="D8" s="85" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="70">
         <v>46288</v>
       </c>
       <c r="F8" s="23"/>
@@ -1719,17 +1719,17 @@
       <c r="J8" s="24"/>
       <c r="K8" s="24"/>
       <c r="L8" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="M8" s="99" t="s">
-        <v>151</v>
-      </c>
-      <c r="N8" s="99" t="s">
-        <v>162</v>
+        <v>148</v>
+      </c>
+      <c r="M8" s="96" t="s">
+        <v>150</v>
+      </c>
+      <c r="N8" s="96" t="s">
+        <v>161</v>
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
-      <c r="Q8" s="22">
+      <c r="Q8" s="70">
         <v>46289</v>
       </c>
       <c r="R8" s="65"/>
@@ -1738,27 +1738,27 @@
       <c r="U8" s="65"/>
       <c r="V8" s="65"/>
       <c r="W8" s="65"/>
-      <c r="X8" s="99" t="s">
-        <v>160</v>
+      <c r="X8" s="96" t="s">
+        <v>159</v>
       </c>
       <c r="Y8" s="65" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>95</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AB8" s="73" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39"/>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="89"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="86"/>
       <c r="E9" s="40"/>
       <c r="F9" s="35"/>
       <c r="G9" s="41"/>
@@ -1790,16 +1790,16 @@
       <c r="A10" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="64">
+      <c r="E10" s="107">
         <v>46290</v>
       </c>
       <c r="F10" s="33"/>
@@ -1809,15 +1809,15 @@
       <c r="J10" s="34"/>
       <c r="K10" s="34"/>
       <c r="L10" s="41"/>
-      <c r="M10" s="81" t="s">
-        <v>152</v>
-      </c>
-      <c r="N10" s="81" t="s">
-        <v>162</v>
+      <c r="M10" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="N10" s="78" t="s">
+        <v>161</v>
       </c>
       <c r="O10" s="34"/>
       <c r="P10" s="34"/>
-      <c r="Q10" s="64">
+      <c r="Q10" s="107">
         <v>46292</v>
       </c>
       <c r="R10" s="37"/>
@@ -1827,24 +1827,24 @@
       <c r="V10" s="37"/>
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
-      <c r="Y10" s="81" t="s">
-        <v>167</v>
+      <c r="Y10" s="78" t="s">
+        <v>166</v>
       </c>
       <c r="Z10" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AA10" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AB10" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39"/>
-      <c r="B11" s="87"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="89"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="86"/>
       <c r="E11" s="40" t="s">
         <v>125</v>
       </c>
@@ -1878,13 +1878,13 @@
       <c r="A12" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="87" t="s">
+      <c r="B12" s="84" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="87" t="s">
+      <c r="C12" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="89" t="s">
+      <c r="D12" s="86" t="s">
         <v>12</v>
       </c>
       <c r="E12" s="32">
@@ -1896,14 +1896,14 @@
       <c r="I12" s="34"/>
       <c r="J12" s="34"/>
       <c r="K12" s="34"/>
-      <c r="L12" s="83" t="s">
+      <c r="L12" s="80" t="s">
         <v>94</v>
       </c>
       <c r="M12" s="34"/>
       <c r="N12" s="34"/>
       <c r="O12" s="34"/>
       <c r="P12" s="34"/>
-      <c r="Q12" s="64">
+      <c r="Q12" s="107">
         <v>46292</v>
       </c>
       <c r="R12" s="37"/>
@@ -1916,29 +1916,29 @@
         <v>95</v>
       </c>
       <c r="Y12" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Z12" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AA12" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB12" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="82" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="84" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="87" t="s">
+      <c r="C13" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="86" t="s">
         <v>14</v>
       </c>
       <c r="E13" s="32">
@@ -1951,13 +1951,13 @@
       <c r="J13" s="34"/>
       <c r="K13" s="34"/>
       <c r="L13" s="34"/>
-      <c r="M13" s="83" t="s">
+      <c r="M13" s="80" t="s">
         <v>119</v>
       </c>
       <c r="N13" s="34"/>
       <c r="O13" s="34"/>
       <c r="P13" s="34"/>
-      <c r="Q13" s="64">
+      <c r="Q13" s="107">
         <v>46295</v>
       </c>
       <c r="R13" s="37"/>
@@ -1974,26 +1974,26 @@
         <v>95</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AB13" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" s="104" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" s="101" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="83" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="88" t="s">
+      <c r="D14" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="70">
         <v>46296</v>
       </c>
       <c r="F14" s="23"/>
@@ -2002,17 +2002,17 @@
       <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="101" t="s">
-        <v>164</v>
+      <c r="L14" s="98" t="s">
+        <v>163</v>
       </c>
       <c r="M14" s="24"/>
-      <c r="N14" s="102" t="s">
-        <v>168</v>
-      </c>
-      <c r="O14" s="102" t="s">
-        <v>172</v>
-      </c>
-      <c r="P14" s="103" t="s">
+      <c r="N14" s="99" t="s">
+        <v>167</v>
+      </c>
+      <c r="O14" s="99" t="s">
+        <v>171</v>
+      </c>
+      <c r="P14" s="100" t="s">
         <v>119</v>
       </c>
       <c r="Q14" s="22">
@@ -2028,17 +2028,17 @@
       <c r="Y14" s="65"/>
       <c r="Z14" s="65"/>
       <c r="AA14" s="26" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AB14" s="73" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39"/>
       <c r="B15" s="71"/>
-      <c r="C15" s="87"/>
-      <c r="D15" s="89"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="86"/>
       <c r="E15" s="72"/>
       <c r="F15" s="35"/>
       <c r="G15" s="41"/>
@@ -2071,10 +2071,10 @@
       <c r="B16" s="44" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="85" t="s">
+      <c r="C16" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="85" t="s">
+      <c r="D16" s="82" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="45"/>
@@ -2109,10 +2109,10 @@
       <c r="B17" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="86" t="s">
+      <c r="C17" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="88" t="s">
+      <c r="D17" s="85" t="s">
         <v>20</v>
       </c>
       <c r="E17" s="22">
@@ -2138,7 +2138,7 @@
         <v>97</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>111</v>
@@ -2147,25 +2147,25 @@
         <v>123</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="W17" s="73" t="s">
-        <v>140</v>
-      </c>
-      <c r="X17" s="82" t="s">
-        <v>176</v>
-      </c>
-      <c r="Y17" s="82" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z17" s="82" t="s">
-        <v>176</v>
-      </c>
-      <c r="AA17" s="82" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB17" s="82" t="s">
-        <v>176</v>
+        <v>139</v>
+      </c>
+      <c r="X17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB17" s="79" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2175,32 +2175,32 @@
       <c r="B18" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="83" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="88" t="s">
+      <c r="D18" s="85" t="s">
         <v>22</v>
       </c>
       <c r="E18" s="70">
         <v>46279</v>
       </c>
-      <c r="F18" s="74" t="s">
+      <c r="F18" s="105" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="75" t="s">
+      <c r="G18" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="75" t="s">
+      <c r="H18" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="75" t="s">
+      <c r="I18" s="106" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="76" t="s">
-        <v>131</v>
-      </c>
-      <c r="K18" s="76" t="s">
-        <v>141</v>
+      <c r="J18" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="K18" s="74" t="s">
+        <v>140</v>
       </c>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
@@ -2210,26 +2210,26 @@
       <c r="Q18" s="70">
         <v>46280</v>
       </c>
-      <c r="R18" s="77" t="s">
+      <c r="R18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="S18" s="77" t="s">
+      <c r="S18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="T18" s="77" t="s">
+      <c r="T18" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="U18" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="U18" s="77" t="s">
-        <v>133</v>
-      </c>
       <c r="V18" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="W18" s="78" t="s">
-        <v>137</v>
+        <v>181</v>
+      </c>
+      <c r="W18" s="75" t="s">
+        <v>136</v>
       </c>
       <c r="X18" s="73" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y18" s="73"/>
       <c r="Z18" s="73"/>
@@ -2243,10 +2243,10 @@
       <c r="B19" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="86" t="s">
+      <c r="C19" s="83" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="88" t="s">
+      <c r="D19" s="85" t="s">
         <v>25</v>
       </c>
       <c r="E19" s="68">
@@ -2297,10 +2297,10 @@
       <c r="B20" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="86" t="s">
+      <c r="C20" s="83" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="88" t="s">
+      <c r="D20" s="85" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="68">
@@ -2332,10 +2332,10 @@
         <v>95</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="X20" s="73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y20" s="73"/>
       <c r="Z20" s="73"/>
@@ -2349,10 +2349,10 @@
       <c r="B21" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="86" t="s">
+      <c r="C21" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="88" t="s">
+      <c r="D21" s="85" t="s">
         <v>68</v>
       </c>
       <c r="E21" s="22">
@@ -2403,10 +2403,10 @@
       <c r="B22" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="86" t="s">
+      <c r="C22" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="88" t="s">
+      <c r="D22" s="85" t="s">
         <v>30</v>
       </c>
       <c r="E22" s="22">
@@ -2449,11 +2449,11 @@
       <c r="B23" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="87" t="s">
+      <c r="C23" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="89" t="s">
-        <v>138</v>
+      <c r="D23" s="86" t="s">
+        <v>137</v>
       </c>
       <c r="E23" s="32">
         <v>46275</v>
@@ -2493,10 +2493,10 @@
       <c r="B24" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="88" t="s">
+      <c r="C24" s="85" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="88" t="s">
+      <c r="D24" s="85" t="s">
         <v>71</v>
       </c>
       <c r="E24" s="22">
@@ -2515,7 +2515,7 @@
       <c r="N24" s="54"/>
       <c r="O24" s="54"/>
       <c r="P24" s="54"/>
-      <c r="Q24" s="22">
+      <c r="Q24" s="70">
         <v>46278</v>
       </c>
       <c r="R24" s="10" t="s">
@@ -2539,10 +2539,10 @@
       <c r="B25" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="88" t="s">
+      <c r="C25" s="85" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="88" t="s">
+      <c r="D25" s="85" t="s">
         <v>103</v>
       </c>
       <c r="E25" s="29">
@@ -2593,10 +2593,10 @@
       <c r="B26" s="52" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="88" t="s">
+      <c r="C26" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="88" t="s">
+      <c r="D26" s="85" t="s">
         <v>104</v>
       </c>
       <c r="E26" s="68">
@@ -2615,11 +2615,11 @@
       <c r="N26" s="28"/>
       <c r="O26" s="28"/>
       <c r="P26" s="28"/>
-      <c r="Q26" s="22">
+      <c r="Q26" s="70">
         <v>46285</v>
       </c>
-      <c r="R26" s="79"/>
-      <c r="S26" s="79"/>
+      <c r="R26" s="76"/>
+      <c r="S26" s="76"/>
       <c r="T26" s="6" t="s">
         <v>95</v>
       </c>
@@ -2629,11 +2629,11 @@
       <c r="V26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="W26" s="78" t="s">
-        <v>139</v>
+      <c r="W26" s="75" t="s">
+        <v>138</v>
       </c>
       <c r="X26" s="73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Y26" s="73"/>
       <c r="Z26" s="73"/>
@@ -2647,11 +2647,11 @@
       <c r="B27" s="57" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="86" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="89" t="s">
-        <v>154</v>
+      <c r="D27" s="86" t="s">
+        <v>153</v>
       </c>
       <c r="E27" s="64">
         <v>46286</v>
@@ -2661,17 +2661,17 @@
       <c r="H27" s="58"/>
       <c r="I27" s="49"/>
       <c r="J27" s="49"/>
-      <c r="K27" s="81" t="s">
-        <v>135</v>
-      </c>
-      <c r="L27" s="81" t="s">
-        <v>147</v>
+      <c r="K27" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="L27" s="78" t="s">
+        <v>146</v>
       </c>
       <c r="M27" s="49"/>
       <c r="N27" s="49"/>
       <c r="O27" s="49"/>
       <c r="P27" s="49"/>
-      <c r="Q27" s="64">
+      <c r="Q27" s="107">
         <v>46293</v>
       </c>
       <c r="R27" s="37"/>
@@ -2680,20 +2680,20 @@
       <c r="U27" s="37"/>
       <c r="V27" s="37"/>
       <c r="W27" s="37"/>
-      <c r="X27" s="80" t="s">
+      <c r="X27" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="Y27" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z27" s="80" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA27" s="80" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB27" s="80" t="s">
-        <v>174</v>
+      <c r="Y27" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z27" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="AA27" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="AB27" s="77" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2703,11 +2703,11 @@
       <c r="B28" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="86" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="89" t="s">
-        <v>155</v>
+      <c r="D28" s="86" t="s">
+        <v>154</v>
       </c>
       <c r="E28" s="32">
         <v>46294</v>
@@ -2719,8 +2719,8 @@
       <c r="J28" s="49"/>
       <c r="K28" s="49"/>
       <c r="L28" s="49"/>
-      <c r="M28" s="81" t="s">
-        <v>156</v>
+      <c r="M28" s="78" t="s">
+        <v>155</v>
       </c>
       <c r="N28" s="49"/>
       <c r="O28" s="49"/>
@@ -2735,23 +2735,23 @@
       <c r="V28" s="37"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
-      <c r="Y28" s="80" t="s">
+      <c r="Y28" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="Z28" s="80" t="s">
+      <c r="Z28" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="AA28" s="80" t="s">
+      <c r="AA28" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="AB28" s="80" t="s">
+      <c r="AB28" s="77" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
-      <c r="D29" s="92"/>
+      <c r="D29" s="89"/>
       <c r="E29" s="60"/>
       <c r="F29" s="60"/>
       <c r="G29" s="16"/>
@@ -2810,10 +2810,10 @@
       <c r="B31" s="62" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="91" t="s">
+      <c r="C31" s="88" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="92" t="s">
+      <c r="D31" s="89" t="s">
         <v>82</v>
       </c>
       <c r="E31" s="60"/>
@@ -2874,10 +2874,10 @@
       <c r="B33" s="63" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="92" t="s">
+      <c r="C33" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="92" t="s">
+      <c r="D33" s="89" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="60"/>

--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EED8E8-E02F-48C3-B3AF-3AE392027FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413395A2-674F-4822-8728-F0824E460520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="183">
   <si>
     <t>№ п/п</t>
   </si>
@@ -621,16 +621,39 @@
 выполнено/done</t>
   </si>
   <si>
-    <t>улица:
-01.10. выполнено/ done
-техническое помещение (2 шланга): работы ожидают завершения  (на завершение влияют работы по электрике- 2.7.5.)</t>
-  </si>
-  <si>
     <t>не заверешено. Идет процесс выверения отклонений. Планируемый срок заврешения - 29.09.26
 у Замперла запрошена проектная документация для  во избежание бесконечных подвижек</t>
   </si>
   <si>
     <t>Планируется выполнить 19.09.26</t>
+  </si>
+  <si>
+    <t>по состоянию на 07.10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve">улица:
+01.10. выполнено/ done
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>техническое помещение (2 шланга): работы ожидают завершения  (на завершение влияют работы по электрике- 2.7.5.)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -831,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="109">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1134,6 +1157,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1141,14 +1173,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1365,12 +1391,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AB33"/>
-  <sheetFormatPr defaultRowHeight="21" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A2:AD33"/>
+  <sheetFormatPr defaultRowHeight="21" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.36328125" customWidth="1"/>
+    <col min="1" max="1" width="6.26953125" customWidth="1"/>
     <col min="2" max="2" width="51.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="69.1796875" style="87" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="8.984375E-2" style="87" customWidth="1" collapsed="1"/>
     <col min="4" max="4" width="65.54296875" style="87" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
     <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
@@ -1379,44 +1405,49 @@
     <col min="9" max="9" width="17.08984375" style="4" customWidth="1" outlineLevel="1"/>
     <col min="10" max="10" width="15" style="4" customWidth="1" outlineLevel="1"/>
     <col min="11" max="11" width="19.90625" style="4" customWidth="1" outlineLevel="1"/>
-    <col min="12" max="12" width="31" style="4" customWidth="1"/>
-    <col min="13" max="13" width="30.7265625" style="4" customWidth="1"/>
-    <col min="14" max="14" width="29.1796875" style="4" customWidth="1"/>
-    <col min="15" max="15" width="25.7265625" style="4" customWidth="1"/>
-    <col min="16" max="16" width="44.453125" style="4" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="29.7265625" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="23.1796875" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="20" max="20" width="24.08984375" style="9" customWidth="1"/>
-    <col min="21" max="21" width="24.6328125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="21.1796875" customWidth="1"/>
-    <col min="23" max="23" width="23.08984375" customWidth="1"/>
-    <col min="24" max="27" width="43" customWidth="1"/>
-    <col min="28" max="28" width="47.6328125" customWidth="1"/>
+    <col min="12" max="12" width="19.36328125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="17.453125" style="4" customWidth="1"/>
+    <col min="15" max="15" width="19" style="4" customWidth="1"/>
+    <col min="16" max="17" width="18.36328125" style="4" customWidth="1"/>
+    <col min="18" max="18" width="15.08984375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="29.7265625" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="20" max="20" width="23.1796875" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="21" max="21" width="17" style="9" customWidth="1"/>
+    <col min="22" max="22" width="16.26953125" style="2" customWidth="1"/>
+    <col min="23" max="23" width="14.453125" customWidth="1"/>
+    <col min="24" max="24" width="19.36328125" customWidth="1"/>
+    <col min="25" max="25" width="20.7265625" customWidth="1"/>
+    <col min="26" max="26" width="28" customWidth="1"/>
+    <col min="27" max="27" width="20.08984375" customWidth="1"/>
+    <col min="28" max="28" width="22.08984375" customWidth="1"/>
+    <col min="29" max="29" width="18" customWidth="1"/>
+    <col min="30" max="30" width="30.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="102" t="s">
+    <row r="2" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="102"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
-      <c r="J2" s="104"/>
-      <c r="K2" s="104"/>
-      <c r="L2" s="104"/>
-      <c r="M2" s="104"/>
-      <c r="N2" s="104"/>
-      <c r="O2" s="104"/>
-      <c r="P2" s="104"/>
-      <c r="Q2" s="104"/>
-    </row>
-    <row r="3" spans="1:28" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="105"/>
+      <c r="C2" s="105"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="107"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="107"/>
+      <c r="M2" s="107"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="107"/>
+      <c r="P2" s="107"/>
+      <c r="Q2" s="107"/>
+      <c r="R2" s="107"/>
+    </row>
+    <row r="3" spans="1:30" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
         <v>0</v>
       </c>
@@ -1443,22 +1474,24 @@
       <c r="N3" s="15"/>
       <c r="O3" s="15"/>
       <c r="P3" s="15"/>
-      <c r="Q3" s="13" t="s">
+      <c r="Q3" s="15"/>
+      <c r="R3" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="R3" s="14"/>
       <c r="S3" s="14"/>
       <c r="T3" s="14"/>
       <c r="U3" s="14"/>
-      <c r="V3" s="16"/>
+      <c r="V3" s="14"/>
       <c r="W3" s="16"/>
       <c r="X3" s="16"/>
       <c r="Y3" s="16"/>
       <c r="Z3" s="16"/>
       <c r="AA3" s="16"/>
       <c r="AB3" s="16"/>
-    </row>
-    <row r="4" spans="1:28" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+    </row>
+    <row r="4" spans="1:30" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="17" t="s">
         <v>2</v>
       </c>
@@ -1505,42 +1538,48 @@
       <c r="P4" s="91" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="93" t="s">
+      <c r="Q4" s="91" t="s">
+        <v>181</v>
+      </c>
+      <c r="R4" s="92"/>
+      <c r="S4" s="93" t="s">
         <v>92</v>
       </c>
-      <c r="S4" s="93" t="s">
+      <c r="T4" s="93" t="s">
         <v>105</v>
       </c>
-      <c r="T4" s="93" t="s">
+      <c r="U4" s="93" t="s">
         <v>108</v>
       </c>
-      <c r="U4" s="93" t="s">
+      <c r="V4" s="93" t="s">
         <v>114</v>
       </c>
-      <c r="V4" s="94" t="s">
+      <c r="W4" s="94" t="s">
         <v>127</v>
       </c>
-      <c r="W4" s="94" t="s">
+      <c r="X4" s="94" t="s">
         <v>128</v>
       </c>
-      <c r="X4" s="95" t="s">
+      <c r="Y4" s="95" t="s">
         <v>142</v>
       </c>
-      <c r="Y4" s="95" t="s">
+      <c r="Z4" s="95" t="s">
         <v>147</v>
       </c>
-      <c r="Z4" s="95" t="s">
+      <c r="AA4" s="95" t="s">
         <v>158</v>
       </c>
-      <c r="AA4" s="95" t="s">
+      <c r="AB4" s="95" t="s">
         <v>168</v>
       </c>
-      <c r="AB4" s="95" t="s">
+      <c r="AC4" s="95" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="5" spans="1:28" ht="69" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD4" s="95" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="69" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A5" s="20" t="s">
         <v>4</v>
       </c>
@@ -1567,13 +1606,13 @@
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24"/>
-      <c r="Q5" s="70">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="70">
         <v>46277</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="S5" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="S5" s="26"/>
       <c r="T5" s="26"/>
       <c r="U5" s="26"/>
       <c r="V5" s="26"/>
@@ -1583,8 +1622,10 @@
       <c r="Z5" s="26"/>
       <c r="AA5" s="26"/>
       <c r="AB5" s="26"/>
-    </row>
-    <row r="6" spans="1:28" ht="64" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="26"/>
+    </row>
+    <row r="6" spans="1:30" ht="64" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
@@ -1613,19 +1654,19 @@
       <c r="N6" s="28"/>
       <c r="O6" s="28"/>
       <c r="P6" s="28"/>
-      <c r="Q6" s="70">
+      <c r="Q6" s="28"/>
+      <c r="R6" s="70">
         <v>46280</v>
       </c>
-      <c r="R6" s="26" t="s">
+      <c r="S6" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="S6" s="26" t="s">
+      <c r="T6" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="U6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="U6" s="26"/>
       <c r="V6" s="26"/>
       <c r="W6" s="26"/>
       <c r="X6" s="26"/>
@@ -1633,8 +1674,10 @@
       <c r="Z6" s="26"/>
       <c r="AA6" s="26"/>
       <c r="AB6" s="26"/>
-    </row>
-    <row r="7" spans="1:28" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC6" s="26"/>
+      <c r="AD6" s="26"/>
+    </row>
+    <row r="7" spans="1:30" ht="95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
         <v>7</v>
       </c>
@@ -1663,31 +1706,29 @@
       <c r="N7" s="56"/>
       <c r="O7" s="56"/>
       <c r="P7" s="56"/>
-      <c r="Q7" s="70">
+      <c r="Q7" s="56"/>
+      <c r="R7" s="70">
         <v>46287</v>
       </c>
-      <c r="R7" s="76"/>
       <c r="S7" s="76"/>
-      <c r="T7" s="3" t="s">
+      <c r="T7" s="76"/>
+      <c r="U7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="U7" s="76" t="s">
+      <c r="V7" s="76" t="s">
         <v>118</v>
       </c>
-      <c r="V7" s="90" t="s">
+      <c r="W7" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="W7" s="75" t="s">
+      <c r="X7" s="75" t="s">
         <v>143</v>
       </c>
-      <c r="X7" s="75" t="s">
-        <v>180</v>
-      </c>
       <c r="Y7" s="75" t="s">
+        <v>179</v>
+      </c>
+      <c r="Z7" s="75" t="s">
         <v>157</v>
-      </c>
-      <c r="Z7" s="73" t="s">
-        <v>160</v>
       </c>
       <c r="AA7" s="73" t="s">
         <v>160</v>
@@ -1695,8 +1736,14 @@
       <c r="AB7" s="73" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" ht="75.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC7" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="AD7" s="73" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" ht="75.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A8" s="97" t="s">
         <v>8</v>
       </c>
@@ -1729,32 +1776,36 @@
       </c>
       <c r="O8" s="24"/>
       <c r="P8" s="24"/>
-      <c r="Q8" s="70">
+      <c r="Q8" s="24"/>
+      <c r="R8" s="70">
         <v>46289</v>
       </c>
-      <c r="R8" s="65"/>
       <c r="S8" s="65"/>
       <c r="T8" s="65"/>
       <c r="U8" s="65"/>
       <c r="V8" s="65"/>
       <c r="W8" s="65"/>
-      <c r="X8" s="96" t="s">
+      <c r="X8" s="65"/>
+      <c r="Y8" s="96" t="s">
         <v>159</v>
       </c>
-      <c r="Y8" s="65" t="s">
+      <c r="Z8" s="65" t="s">
         <v>149</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="AA8" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AB8" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AB8" s="73" t="s">
+      <c r="AC8" s="73" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD8" s="73" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39"/>
       <c r="B9" s="84"/>
       <c r="C9" s="84"/>
@@ -1771,22 +1822,24 @@
       <c r="N9" s="41"/>
       <c r="O9" s="41"/>
       <c r="P9" s="41"/>
-      <c r="Q9" s="40" t="s">
+      <c r="Q9" s="41"/>
+      <c r="R9" s="40" t="s">
         <v>124</v>
       </c>
-      <c r="R9" s="42"/>
       <c r="S9" s="42"/>
       <c r="T9" s="42"/>
       <c r="U9" s="42"/>
-      <c r="V9" s="38"/>
+      <c r="V9" s="42"/>
       <c r="W9" s="38"/>
       <c r="X9" s="38"/>
       <c r="Y9" s="38"/>
       <c r="Z9" s="38"/>
       <c r="AA9" s="38"/>
       <c r="AB9" s="38"/>
-    </row>
-    <row r="10" spans="1:28" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC9" s="38"/>
+      <c r="AD9" s="38"/>
+    </row>
+    <row r="10" spans="1:30" ht="142" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>9</v>
       </c>
@@ -1799,7 +1852,7 @@
       <c r="D10" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="107">
+      <c r="E10" s="104">
         <v>46290</v>
       </c>
       <c r="F10" s="33"/>
@@ -1817,30 +1870,32 @@
       </c>
       <c r="O10" s="34"/>
       <c r="P10" s="34"/>
-      <c r="Q10" s="107">
+      <c r="Q10" s="34"/>
+      <c r="R10" s="104">
         <v>46292</v>
       </c>
-      <c r="R10" s="37"/>
       <c r="S10" s="37"/>
       <c r="T10" s="37"/>
       <c r="U10" s="37"/>
       <c r="V10" s="37"/>
       <c r="W10" s="37"/>
       <c r="X10" s="37"/>
-      <c r="Y10" s="78" t="s">
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="78" t="s">
         <v>166</v>
       </c>
-      <c r="Z10" s="5" t="s">
+      <c r="AA10" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="AA10" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="AB10" s="5" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="AD10" s="5"/>
+    </row>
+    <row r="11" spans="1:30" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39"/>
       <c r="B11" s="84"/>
       <c r="C11" s="84"/>
@@ -1859,22 +1914,24 @@
       <c r="N11" s="41"/>
       <c r="O11" s="41"/>
       <c r="P11" s="41"/>
-      <c r="Q11" s="40" t="s">
+      <c r="Q11" s="41"/>
+      <c r="R11" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="R11" s="42"/>
       <c r="S11" s="42"/>
       <c r="T11" s="42"/>
       <c r="U11" s="42"/>
-      <c r="V11" s="38"/>
+      <c r="V11" s="42"/>
       <c r="W11" s="38"/>
       <c r="X11" s="38"/>
       <c r="Y11" s="38"/>
       <c r="Z11" s="38"/>
       <c r="AA11" s="38"/>
       <c r="AB11" s="38"/>
-    </row>
-    <row r="12" spans="1:28" ht="78" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC11" s="38"/>
+      <c r="AD11" s="38"/>
+    </row>
+    <row r="12" spans="1:30" ht="172" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="30" t="s">
         <v>11</v>
       </c>
@@ -1903,32 +1960,36 @@
       <c r="N12" s="34"/>
       <c r="O12" s="34"/>
       <c r="P12" s="34"/>
-      <c r="Q12" s="107">
+      <c r="Q12" s="34"/>
+      <c r="R12" s="104">
         <v>46292</v>
       </c>
-      <c r="R12" s="37"/>
       <c r="S12" s="37"/>
       <c r="T12" s="37"/>
       <c r="U12" s="37"/>
       <c r="V12" s="37"/>
       <c r="W12" s="37"/>
-      <c r="X12" s="5" t="s">
+      <c r="X12" s="37"/>
+      <c r="Y12" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Z12" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="AA12" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="AA12" s="5" t="s">
-        <v>179</v>
-      </c>
       <c r="AB12" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" ht="82" customHeight="1" x14ac:dyDescent="0.35">
+        <v>182</v>
+      </c>
+      <c r="AC12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="AD12" s="5" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="122" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="30" t="s">
         <v>13</v>
       </c>
@@ -1957,30 +2018,32 @@
       <c r="N13" s="34"/>
       <c r="O13" s="34"/>
       <c r="P13" s="34"/>
-      <c r="Q13" s="107">
+      <c r="Q13" s="34"/>
+      <c r="R13" s="104">
         <v>46295</v>
       </c>
-      <c r="R13" s="37"/>
       <c r="S13" s="37"/>
       <c r="T13" s="37"/>
       <c r="U13" s="37"/>
       <c r="V13" s="37"/>
       <c r="W13" s="37"/>
       <c r="X13" s="37"/>
-      <c r="Y13" s="5" t="s">
-        <v>95</v>
-      </c>
+      <c r="Y13" s="37"/>
       <c r="Z13" s="5" t="s">
         <v>95</v>
       </c>
       <c r="AA13" s="5" t="s">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AB13" s="5" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" s="101" customFormat="1" ht="56.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC13" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD13" s="5"/>
+    </row>
+    <row r="14" spans="1:30" s="101" customFormat="1" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A14" s="66" t="s">
         <v>15</v>
       </c>
@@ -2015,10 +2078,10 @@
       <c r="P14" s="100" t="s">
         <v>119</v>
       </c>
-      <c r="Q14" s="22">
+      <c r="Q14" s="100"/>
+      <c r="R14" s="22">
         <v>46300</v>
       </c>
-      <c r="R14" s="65"/>
       <c r="S14" s="65"/>
       <c r="T14" s="65"/>
       <c r="U14" s="65"/>
@@ -2027,14 +2090,16 @@
       <c r="X14" s="65"/>
       <c r="Y14" s="65"/>
       <c r="Z14" s="65"/>
-      <c r="AA14" s="26" t="s">
+      <c r="AA14" s="65"/>
+      <c r="AB14" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="AB14" s="73" t="s">
+      <c r="AC14" s="73" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AD14" s="73"/>
+    </row>
+    <row r="15" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39"/>
       <c r="B15" s="71"/>
       <c r="C15" s="84"/>
@@ -2051,8 +2116,8 @@
       <c r="N15" s="41"/>
       <c r="O15" s="41"/>
       <c r="P15" s="41"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="42"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="32"/>
       <c r="S15" s="42"/>
       <c r="T15" s="42"/>
       <c r="U15" s="42"/>
@@ -2063,8 +2128,10 @@
       <c r="Z15" s="42"/>
       <c r="AA15" s="42"/>
       <c r="AB15" s="42"/>
-    </row>
-    <row r="16" spans="1:28" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+    </row>
+    <row r="16" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="43" t="s">
         <v>17</v>
       </c>
@@ -2089,8 +2156,8 @@
       <c r="N16" s="47"/>
       <c r="O16" s="47"/>
       <c r="P16" s="47"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="48"/>
+      <c r="Q16" s="47"/>
+      <c r="R16" s="45"/>
       <c r="S16" s="48"/>
       <c r="T16" s="48"/>
       <c r="U16" s="48"/>
@@ -2101,8 +2168,10 @@
       <c r="Z16" s="48"/>
       <c r="AA16" s="48"/>
       <c r="AB16" s="48"/>
-    </row>
-    <row r="17" spans="1:28" ht="134" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC16" s="48"/>
+      <c r="AD16" s="48"/>
+    </row>
+    <row r="17" spans="1:30" ht="134" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A17" s="66" t="s">
         <v>19</v>
       </c>
@@ -2131,29 +2200,27 @@
       <c r="N17" s="28"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
-      <c r="Q17" s="70">
+      <c r="Q17" s="28"/>
+      <c r="R17" s="70">
         <v>46278</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="S17" s="6" t="s">
+      <c r="T17" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="T17" s="3" t="s">
+      <c r="U17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="U17" s="3" t="s">
+      <c r="V17" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="V17" s="3" t="s">
+      <c r="W17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="W17" s="73" t="s">
+      <c r="X17" s="73" t="s">
         <v>139</v>
-      </c>
-      <c r="X17" s="79" t="s">
-        <v>175</v>
       </c>
       <c r="Y17" s="79" t="s">
         <v>175</v>
@@ -2167,8 +2234,14 @@
       <c r="AB17" s="79" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" ht="99.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC17" s="79" t="s">
+        <v>175</v>
+      </c>
+      <c r="AD17" s="79" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" ht="99.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A18" s="66" t="s">
         <v>21</v>
       </c>
@@ -2184,16 +2257,16 @@
       <c r="E18" s="70">
         <v>46279</v>
       </c>
-      <c r="F18" s="105" t="s">
+      <c r="F18" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="106" t="s">
+      <c r="G18" s="103" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="106" t="s">
+      <c r="H18" s="103" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="106" t="s">
+      <c r="I18" s="103" t="s">
         <v>98</v>
       </c>
       <c r="J18" s="74" t="s">
@@ -2207,36 +2280,38 @@
       <c r="N18" s="28"/>
       <c r="O18" s="28"/>
       <c r="P18" s="28"/>
-      <c r="Q18" s="70">
+      <c r="Q18" s="28"/>
+      <c r="R18" s="70">
         <v>46280</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>109</v>
       </c>
       <c r="T18" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="U18" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="U18" s="6" t="s">
+      <c r="V18" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="W18" s="75" t="s">
+      <c r="W18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="X18" s="75" t="s">
         <v>136</v>
       </c>
-      <c r="X18" s="73" t="s">
+      <c r="Y18" s="73" t="s">
         <v>144</v>
       </c>
-      <c r="Y18" s="73"/>
       <c r="Z18" s="73"/>
       <c r="AA18" s="73"/>
       <c r="AB18" s="73"/>
-    </row>
-    <row r="19" spans="1:28" ht="53" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC18" s="73"/>
+      <c r="AD18" s="73"/>
+    </row>
+    <row r="19" spans="1:30" ht="53" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A19" s="66" t="s">
         <v>23</v>
       </c>
@@ -2265,32 +2340,34 @@
       <c r="N19" s="28"/>
       <c r="O19" s="28"/>
       <c r="P19" s="28"/>
-      <c r="Q19" s="22">
+      <c r="Q19" s="28"/>
+      <c r="R19" s="22">
         <v>46288</v>
-      </c>
-      <c r="R19" s="26" t="s">
-        <v>99</v>
       </c>
       <c r="S19" s="26" t="s">
         <v>99</v>
       </c>
       <c r="T19" s="26" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="U19" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="V19" s="10" t="s">
+      <c r="V19" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="W19" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="W19" s="69"/>
       <c r="X19" s="69"/>
       <c r="Y19" s="69"/>
       <c r="Z19" s="69"/>
       <c r="AA19" s="69"/>
       <c r="AB19" s="69"/>
-    </row>
-    <row r="20" spans="1:28" ht="68" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC19" s="69"/>
+      <c r="AD19" s="69"/>
+    </row>
+    <row r="20" spans="1:30" ht="68" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A20" s="66" t="s">
         <v>24</v>
       </c>
@@ -2319,30 +2396,32 @@
       <c r="N20" s="28"/>
       <c r="O20" s="28"/>
       <c r="P20" s="28"/>
-      <c r="Q20" s="22">
+      <c r="Q20" s="28"/>
+      <c r="R20" s="22">
         <v>46288</v>
       </c>
-      <c r="R20" s="65"/>
       <c r="S20" s="65"/>
       <c r="T20" s="65"/>
-      <c r="U20" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="U20" s="65"/>
       <c r="V20" s="3" t="s">
         <v>95</v>
       </c>
       <c r="W20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="X20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="X20" s="73" t="s">
+      <c r="Y20" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="Y20" s="73"/>
       <c r="Z20" s="73"/>
       <c r="AA20" s="73"/>
       <c r="AB20" s="73"/>
-    </row>
-    <row r="21" spans="1:28" ht="54.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC20" s="73"/>
+      <c r="AD20" s="73"/>
+    </row>
+    <row r="21" spans="1:30" ht="54.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A21" s="66" t="s">
         <v>26</v>
       </c>
@@ -2371,32 +2450,34 @@
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
       <c r="P21" s="28"/>
-      <c r="Q21" s="22">
+      <c r="Q21" s="28"/>
+      <c r="R21" s="22">
         <v>46288</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="S21" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="U21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="U21" s="6" t="s">
+      <c r="V21" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="V21" s="10" t="s">
+      <c r="W21" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="W21" s="67"/>
       <c r="X21" s="67"/>
       <c r="Y21" s="67"/>
       <c r="Z21" s="67"/>
       <c r="AA21" s="67"/>
       <c r="AB21" s="67"/>
-    </row>
-    <row r="22" spans="1:28" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="67"/>
+    </row>
+    <row r="22" spans="1:30" ht="43" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A22" s="66" t="s">
         <v>28</v>
       </c>
@@ -2425,24 +2506,26 @@
       <c r="N22" s="24"/>
       <c r="O22" s="24"/>
       <c r="P22" s="24"/>
-      <c r="Q22" s="22">
+      <c r="Q22" s="24"/>
+      <c r="R22" s="22">
         <v>46289</v>
       </c>
-      <c r="R22" s="65"/>
       <c r="S22" s="65"/>
       <c r="T22" s="65"/>
       <c r="U22" s="65"/>
-      <c r="V22" s="10" t="s">
+      <c r="V22" s="65"/>
+      <c r="W22" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="W22" s="65"/>
       <c r="X22" s="65"/>
       <c r="Y22" s="65"/>
       <c r="Z22" s="65"/>
       <c r="AA22" s="65"/>
       <c r="AB22" s="65"/>
-    </row>
-    <row r="23" spans="1:28" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+    </row>
+    <row r="23" spans="1:30" ht="38" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="39" t="s">
         <v>29</v>
       </c>
@@ -2471,10 +2554,10 @@
       <c r="N23" s="49"/>
       <c r="O23" s="49"/>
       <c r="P23" s="49"/>
-      <c r="Q23" s="32">
+      <c r="Q23" s="49"/>
+      <c r="R23" s="32">
         <v>46319</v>
       </c>
-      <c r="R23" s="37"/>
       <c r="S23" s="37"/>
       <c r="T23" s="37"/>
       <c r="U23" s="37"/>
@@ -2485,8 +2568,10 @@
       <c r="Z23" s="37"/>
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
-    </row>
-    <row r="24" spans="1:28" ht="44.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC23" s="37"/>
+      <c r="AD23" s="37"/>
+    </row>
+    <row r="24" spans="1:30" ht="44.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A24" s="51" t="s">
         <v>77</v>
       </c>
@@ -2515,13 +2600,13 @@
       <c r="N24" s="54"/>
       <c r="O24" s="54"/>
       <c r="P24" s="54"/>
-      <c r="Q24" s="70">
+      <c r="Q24" s="54"/>
+      <c r="R24" s="70">
         <v>46278</v>
       </c>
-      <c r="R24" s="10" t="s">
+      <c r="S24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -2531,8 +2616,10 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
-    </row>
-    <row r="25" spans="1:28" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC24" s="3"/>
+      <c r="AD24" s="3"/>
+    </row>
+    <row r="25" spans="1:30" ht="34" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A25" s="51" t="s">
         <v>78</v>
       </c>
@@ -2565,19 +2652,19 @@
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
       <c r="P25" s="56"/>
-      <c r="Q25" s="29">
+      <c r="Q25" s="56"/>
+      <c r="R25" s="29">
         <v>46281</v>
-      </c>
-      <c r="R25" s="6" t="s">
-        <v>95</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="T25" s="10" t="s">
+      <c r="T25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="U25" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
@@ -2585,8 +2672,10 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
-    </row>
-    <row r="26" spans="1:28" ht="52" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+    </row>
+    <row r="26" spans="1:30" ht="77.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A26" s="66" t="s">
         <v>79</v>
       </c>
@@ -2615,32 +2704,34 @@
       <c r="N26" s="28"/>
       <c r="O26" s="28"/>
       <c r="P26" s="28"/>
-      <c r="Q26" s="70">
+      <c r="Q26" s="28"/>
+      <c r="R26" s="70">
         <v>46285</v>
       </c>
-      <c r="R26" s="76"/>
       <c r="S26" s="76"/>
-      <c r="T26" s="6" t="s">
-        <v>95</v>
-      </c>
+      <c r="T26" s="76"/>
       <c r="U26" s="6" t="s">
         <v>95</v>
       </c>
       <c r="V26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="W26" s="75" t="s">
+      <c r="W26" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="X26" s="75" t="s">
         <v>138</v>
       </c>
-      <c r="X26" s="73" t="s">
+      <c r="Y26" s="73" t="s">
         <v>145</v>
       </c>
-      <c r="Y26" s="73"/>
       <c r="Z26" s="73"/>
       <c r="AA26" s="73"/>
       <c r="AB26" s="73"/>
-    </row>
-    <row r="27" spans="1:28" ht="49.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="73"/>
+    </row>
+    <row r="27" spans="1:30" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="30" t="s">
         <v>80</v>
       </c>
@@ -2653,7 +2744,7 @@
       <c r="D27" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="64">
+      <c r="E27" s="108">
         <v>46286</v>
       </c>
       <c r="F27" s="36"/>
@@ -2671,32 +2762,34 @@
       <c r="N27" s="49"/>
       <c r="O27" s="49"/>
       <c r="P27" s="49"/>
-      <c r="Q27" s="107">
+      <c r="Q27" s="49"/>
+      <c r="R27" s="104">
         <v>46293</v>
       </c>
-      <c r="R27" s="37"/>
       <c r="S27" s="37"/>
       <c r="T27" s="37"/>
       <c r="U27" s="37"/>
       <c r="V27" s="37"/>
       <c r="W27" s="37"/>
-      <c r="X27" s="77" t="s">
+      <c r="X27" s="37"/>
+      <c r="Y27" s="77" t="s">
         <v>95</v>
       </c>
-      <c r="Y27" s="77" t="s">
+      <c r="Z27" s="77" t="s">
         <v>156</v>
       </c>
-      <c r="Z27" s="77" t="s">
+      <c r="AA27" s="77" t="s">
         <v>165</v>
-      </c>
-      <c r="AA27" s="77" t="s">
-        <v>173</v>
       </c>
       <c r="AB27" s="77" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC27" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="AD27" s="77"/>
+    </row>
+    <row r="28" spans="1:30" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">
         <v>81</v>
       </c>
@@ -2709,7 +2802,7 @@
       <c r="D28" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="64">
         <v>46294</v>
       </c>
       <c r="F28" s="59"/>
@@ -2725,19 +2818,17 @@
       <c r="N28" s="49"/>
       <c r="O28" s="49"/>
       <c r="P28" s="49"/>
-      <c r="Q28" s="32">
+      <c r="Q28" s="49"/>
+      <c r="R28" s="32">
         <v>46319</v>
       </c>
-      <c r="R28" s="37"/>
       <c r="S28" s="37"/>
       <c r="T28" s="37"/>
       <c r="U28" s="37"/>
       <c r="V28" s="37"/>
       <c r="W28" s="37"/>
       <c r="X28" s="37"/>
-      <c r="Y28" s="77" t="s">
-        <v>95</v>
-      </c>
+      <c r="Y28" s="37"/>
       <c r="Z28" s="77" t="s">
         <v>95</v>
       </c>
@@ -2747,8 +2838,14 @@
       <c r="AB28" s="77" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC28" s="77" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD28" s="77" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="16"/>
       <c r="B29" s="16"/>
       <c r="D29" s="89"/>
@@ -2764,20 +2861,22 @@
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
-      <c r="Q29" s="60"/>
-      <c r="R29" s="61"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="60"/>
       <c r="S29" s="61"/>
       <c r="T29" s="61"/>
       <c r="U29" s="61"/>
-      <c r="V29" s="16"/>
+      <c r="V29" s="61"/>
       <c r="W29" s="16"/>
       <c r="X29" s="16"/>
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
       <c r="AA29" s="16"/>
       <c r="AB29" s="16"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="16"/>
       <c r="B30" s="16"/>
       <c r="E30" s="60"/>
@@ -2792,20 +2891,22 @@
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
-      <c r="Q30" s="60"/>
-      <c r="R30" s="61"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="60"/>
       <c r="S30" s="61"/>
       <c r="T30" s="61"/>
       <c r="U30" s="61"/>
-      <c r="V30" s="16"/>
+      <c r="V30" s="61"/>
       <c r="W30" s="16"/>
       <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
       <c r="AA30" s="16"/>
       <c r="AB30" s="16"/>
-    </row>
-    <row r="31" spans="1:28" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC30" s="16"/>
+      <c r="AD30" s="16"/>
+    </row>
+    <row r="31" spans="1:30" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="16"/>
       <c r="B31" s="62" t="s">
         <v>88</v>
@@ -2828,20 +2929,22 @@
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="61"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="60"/>
       <c r="S31" s="61"/>
       <c r="T31" s="61"/>
       <c r="U31" s="61"/>
-      <c r="V31" s="16"/>
+      <c r="V31" s="61"/>
       <c r="W31" s="16"/>
       <c r="X31" s="16"/>
       <c r="Y31" s="16"/>
       <c r="Z31" s="16"/>
       <c r="AA31" s="16"/>
       <c r="AB31" s="16"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="E32" s="60"/>
@@ -2856,20 +2959,22 @@
       <c r="N32" s="16"/>
       <c r="O32" s="16"/>
       <c r="P32" s="16"/>
-      <c r="Q32" s="60"/>
-      <c r="R32" s="61"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="60"/>
       <c r="S32" s="61"/>
       <c r="T32" s="61"/>
       <c r="U32" s="61"/>
-      <c r="V32" s="16"/>
+      <c r="V32" s="61"/>
       <c r="W32" s="16"/>
       <c r="X32" s="16"/>
       <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
       <c r="AA32" s="16"/>
       <c r="AB32" s="16"/>
-    </row>
-    <row r="33" spans="1:28" ht="173" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16"/>
+    </row>
+    <row r="33" spans="1:30" ht="173" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="16"/>
       <c r="B33" s="63" t="s">
         <v>91</v>
@@ -2892,26 +2997,28 @@
       <c r="N33" s="16"/>
       <c r="O33" s="16"/>
       <c r="P33" s="16"/>
-      <c r="Q33" s="60"/>
-      <c r="R33" s="61"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="60"/>
       <c r="S33" s="61"/>
       <c r="T33" s="61"/>
       <c r="U33" s="61"/>
-      <c r="V33" s="16"/>
+      <c r="V33" s="61"/>
       <c r="W33" s="16"/>
       <c r="X33" s="16"/>
       <c r="Y33" s="16"/>
       <c r="Z33" s="16"/>
       <c r="AA33" s="16"/>
       <c r="AB33" s="16"/>
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="8" scale="29" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="32" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{413395A2-674F-4822-8728-F0824E460520}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0285FF77-0B81-4457-9853-699748BBB242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="185">
   <si>
     <t>№ п/п</t>
   </si>
@@ -654,6 +654,13 @@
       </rPr>
       <t>техническое помещение (2 шланга): работы ожидают завершения  (на завершение влияют работы по электрике- 2.7.5.)</t>
     </r>
+  </si>
+  <si>
+    <t>выполнено 95 %</t>
+  </si>
+  <si>
+    <t>работы выполняются.  Выполнено 95%
+Ожидаемый срок завершения - 08.10.26</t>
   </si>
 </sst>
 </file>
@@ -1166,6 +1173,9 @@
     <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1173,9 +1183,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1426,26 +1433,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="105" t="s">
+      <c r="A2" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="107"/>
-      <c r="G2" s="107"/>
-      <c r="H2" s="107"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="107"/>
-      <c r="K2" s="107"/>
-      <c r="L2" s="107"/>
-      <c r="M2" s="107"/>
-      <c r="N2" s="107"/>
-      <c r="O2" s="107"/>
-      <c r="P2" s="107"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="107"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="108"/>
+      <c r="F2" s="108"/>
+      <c r="G2" s="108"/>
+      <c r="H2" s="108"/>
+      <c r="I2" s="108"/>
+      <c r="J2" s="108"/>
+      <c r="K2" s="108"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
     </row>
     <row r="3" spans="1:30" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11" t="s">
@@ -1840,60 +1847,62 @@
       <c r="AD9" s="38"/>
     </row>
     <row r="10" spans="1:30" ht="142" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="84" t="s">
+      <c r="B10" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="84" t="s">
+      <c r="C10" s="83" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="86" t="s">
+      <c r="D10" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="104">
+      <c r="E10" s="70">
         <v>46290</v>
       </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="41"/>
-      <c r="M10" s="78" t="s">
+      <c r="F10" s="23"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="96" t="s">
         <v>151</v>
       </c>
-      <c r="N10" s="78" t="s">
+      <c r="N10" s="96" t="s">
         <v>161</v>
       </c>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="104">
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="70">
         <v>46292</v>
       </c>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="78" t="s">
+      <c r="S10" s="65"/>
+      <c r="T10" s="65"/>
+      <c r="U10" s="65"/>
+      <c r="V10" s="65"/>
+      <c r="W10" s="65"/>
+      <c r="X10" s="65"/>
+      <c r="Y10" s="65"/>
+      <c r="Z10" s="96" t="s">
         <v>166</v>
       </c>
-      <c r="AA10" s="5" t="s">
+      <c r="AA10" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AB10" s="5" t="s">
+      <c r="AB10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AC10" s="5" t="s">
+      <c r="AC10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AD10" s="5"/>
+      <c r="AD10" s="73" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="11" spans="1:30" ht="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39"/>
@@ -2041,7 +2050,9 @@
       <c r="AC13" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="AD13" s="5"/>
+      <c r="AD13" s="5" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="14" spans="1:30" s="101" customFormat="1" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
       <c r="A14" s="66" t="s">
@@ -2744,7 +2755,7 @@
       <c r="D27" s="86" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="108">
+      <c r="E27" s="105">
         <v>46286</v>
       </c>
       <c r="F27" s="36"/>
@@ -2787,7 +2798,9 @@
       <c r="AC27" s="77" t="s">
         <v>173</v>
       </c>
-      <c r="AD27" s="77"/>
+      <c r="AD27" s="77" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="28" spans="1:30" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="30" t="s">

--- a/daily-monitoring.xlsx
+++ b/daily-monitoring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kakorolkova\Nextcloud\Проекты\Королькова\Двойное сердце\Ежедневный статус выполнения работ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0285FF77-0B81-4457-9853-699748BBB242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98D0D08-B467-4227-A029-47C639346BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="187">
   <si>
     <t>№ п/п</t>
   </si>
@@ -661,6 +661,13 @@
   <si>
     <t>работы выполняются.  Выполнено 95%
 Ожидаемый срок завершения - 08.10.26</t>
+  </si>
+  <si>
+    <t>по состоянию на 10.10</t>
+  </si>
+  <si>
+    <t>08.10.26
+выполнено/done</t>
   </si>
 </sst>
 </file>
@@ -861,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -875,9 +882,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -959,18 +963,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1099,9 +1094,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1170,12 +1162,6 @@
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1183,6 +1169,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1398,15 +1391,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:AD33"/>
+  <dimension ref="A2:AF33"/>
   <sheetFormatPr defaultRowHeight="21" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.26953125" customWidth="1"/>
     <col min="2" max="2" width="51.6328125" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="8.984375E-2" style="87" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="65.54296875" style="87" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.984375E-2" style="82" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="65.54296875" style="82" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.36328125" style="8" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="29.36328125" style="7" customWidth="1" outlineLevel="1"/>
     <col min="7" max="7" width="13.6328125" customWidth="1" outlineLevel="1"/>
     <col min="8" max="8" width="15" style="4" customWidth="1" outlineLevel="1" collapsed="1"/>
     <col min="9" max="9" width="17.08984375" style="4" customWidth="1" outlineLevel="1"/>
@@ -1420,7 +1413,7 @@
     <col min="18" max="18" width="15.08984375" style="1" customWidth="1"/>
     <col min="19" max="19" width="29.7265625" style="2" customWidth="1" outlineLevel="1"/>
     <col min="20" max="20" width="23.1796875" style="2" customWidth="1" outlineLevel="1"/>
-    <col min="21" max="21" width="17" style="9" customWidth="1"/>
+    <col min="21" max="21" width="17" style="8" customWidth="1"/>
     <col min="22" max="22" width="16.26953125" style="2" customWidth="1"/>
     <col min="23" max="23" width="14.453125" customWidth="1"/>
     <col min="24" max="24" width="19.36328125" customWidth="1"/>
@@ -1430,373 +1423,383 @@
     <col min="28" max="28" width="22.08984375" customWidth="1"/>
     <col min="29" max="29" width="18" customWidth="1"/>
     <col min="30" max="30" width="30.453125" customWidth="1"/>
+    <col min="31" max="31" width="20.7265625" customWidth="1"/>
+    <col min="32" max="32" width="8.7265625" style="103"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:30" ht="14.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="106" t="s">
+    <row r="2" spans="1:32" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="107"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-    </row>
-    <row r="3" spans="1:30" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="101"/>
+      <c r="I2" s="101"/>
+      <c r="J2" s="101"/>
+      <c r="K2" s="101"/>
+      <c r="L2" s="101"/>
+      <c r="M2" s="101"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="101"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="101"/>
+      <c r="R2" s="101"/>
+    </row>
+    <row r="3" spans="1:32" ht="87.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="81" t="s">
+      <c r="C3" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
-      <c r="R3" s="13" t="s">
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="S3" s="14"/>
-      <c r="T3" s="14"/>
-      <c r="U3" s="14"/>
-      <c r="V3" s="14"/>
-      <c r="W3" s="16"/>
-      <c r="X3" s="16"/>
-      <c r="Y3" s="16"/>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="16"/>
-      <c r="AB3" s="16"/>
-      <c r="AC3" s="16"/>
-      <c r="AD3" s="16"/>
-    </row>
-    <row r="4" spans="1:30" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="17" t="s">
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="15"/>
+      <c r="X3" s="15"/>
+      <c r="Y3" s="15"/>
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15"/>
+      <c r="AB3" s="15"/>
+      <c r="AC3" s="15"/>
+      <c r="AD3" s="15"/>
+    </row>
+    <row r="4" spans="1:32" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19" t="s">
+      <c r="E4" s="17"/>
+      <c r="F4" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="19" t="s">
+      <c r="H4" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="I4" s="19" t="s">
+      <c r="I4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="J4" s="19" t="s">
+      <c r="J4" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="K4" s="19" t="s">
+      <c r="K4" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="L4" s="91" t="s">
+      <c r="L4" s="86" t="s">
         <v>142</v>
       </c>
-      <c r="M4" s="91" t="s">
+      <c r="M4" s="86" t="s">
         <v>147</v>
       </c>
-      <c r="N4" s="91" t="s">
+      <c r="N4" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="O4" s="91" t="s">
+      <c r="O4" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="P4" s="91" t="s">
+      <c r="P4" s="86" t="s">
         <v>174</v>
       </c>
-      <c r="Q4" s="91" t="s">
+      <c r="Q4" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="R4" s="92"/>
-      <c r="S4" s="93" t="s">
+      <c r="R4" s="87"/>
+      <c r="S4" s="88" t="s">
         <v>92</v>
       </c>
-      <c r="T4" s="93" t="s">
+      <c r="T4" s="88" t="s">
         <v>105</v>
       </c>
-      <c r="U4" s="93" t="s">
+      <c r="U4" s="88" t="s">
         <v>108</v>
       </c>
-      <c r="V4" s="93" t="s">
+      <c r="V4" s="88" t="s">
         <v>114</v>
       </c>
-      <c r="W4" s="94" t="s">
+      <c r="W4" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="X4" s="94" t="s">
+      <c r="X4" s="89" t="s">
         <v>128</v>
       </c>
-      <c r="Y4" s="95" t="s">
+      <c r="Y4" s="90" t="s">
         <v>142</v>
       </c>
-      <c r="Z4" s="95" t="s">
+      <c r="Z4" s="90" t="s">
         <v>147</v>
       </c>
-      <c r="AA4" s="95" t="s">
+      <c r="AA4" s="90" t="s">
         <v>158</v>
       </c>
-      <c r="AB4" s="95" t="s">
+      <c r="AB4" s="90" t="s">
         <v>168</v>
       </c>
-      <c r="AC4" s="95" t="s">
+      <c r="AC4" s="90" t="s">
         <v>174</v>
       </c>
-      <c r="AD4" s="95" t="s">
+      <c r="AD4" s="90" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" ht="69" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="AE4" s="90" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" ht="69" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="83" t="s">
+      <c r="C5" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="21">
         <v>46268</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="70">
+      <c r="F5" s="22"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="66">
         <v>46277</v>
       </c>
-      <c r="S5" s="25" t="s">
+      <c r="S5" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="T5" s="26"/>
-      <c r="U5" s="26"/>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="26"/>
-      <c r="AA5" s="26"/>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-    </row>
-    <row r="6" spans="1:30" ht="64" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="T5" s="25"/>
+      <c r="U5" s="25"/>
+      <c r="V5" s="25"/>
+      <c r="W5" s="25"/>
+      <c r="X5" s="25"/>
+      <c r="Y5" s="25"/>
+      <c r="Z5" s="25"/>
+      <c r="AA5" s="25"/>
+      <c r="AB5" s="25"/>
+      <c r="AC5" s="25"/>
+      <c r="AD5" s="25"/>
+      <c r="AE5" s="25"/>
+    </row>
+    <row r="6" spans="1:32" ht="64" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="78" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="83" t="s">
+      <c r="C6" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="85" t="s">
+      <c r="D6" s="80" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="21">
         <v>46274</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="70">
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="66">
         <v>46280</v>
       </c>
-      <c r="S6" s="26" t="s">
+      <c r="S6" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="T6" s="26" t="s">
+      <c r="T6" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="U6" s="25" t="s">
+      <c r="U6" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="26"/>
-      <c r="AA6" s="26"/>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-    </row>
-    <row r="7" spans="1:30" ht="95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="66" t="s">
+      <c r="V6" s="25"/>
+      <c r="W6" s="25"/>
+      <c r="X6" s="25"/>
+      <c r="Y6" s="25"/>
+      <c r="Z6" s="25"/>
+      <c r="AA6" s="25"/>
+      <c r="AB6" s="25"/>
+      <c r="AC6" s="25"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="25"/>
+    </row>
+    <row r="7" spans="1:32" ht="95" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="78" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="85" t="s">
+      <c r="D7" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="21">
         <v>46281</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="23" t="s">
+      <c r="F7" s="22"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="70">
+      <c r="I7" s="52"/>
+      <c r="J7" s="52"/>
+      <c r="K7" s="52"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="52"/>
+      <c r="N7" s="52"/>
+      <c r="O7" s="52"/>
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="66">
         <v>46287</v>
       </c>
-      <c r="S7" s="76"/>
-      <c r="T7" s="76"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
       <c r="U7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="V7" s="76" t="s">
+      <c r="V7" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="W7" s="90" t="s">
+      <c r="W7" s="85" t="s">
         <v>95</v>
       </c>
-      <c r="X7" s="75" t="s">
+      <c r="X7" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="Y7" s="75" t="s">
+      <c r="Y7" s="71" t="s">
         <v>179</v>
       </c>
-      <c r="Z7" s="75" t="s">
+      <c r="Z7" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="AA7" s="73" t="s">
+      <c r="AA7" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="AB7" s="73" t="s">
+      <c r="AB7" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="AC7" s="73" t="s">
+      <c r="AC7" s="69" t="s">
         <v>160</v>
       </c>
-      <c r="AD7" s="73" t="s">
+      <c r="AD7" s="69" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="8" spans="1:30" ht="75.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="97" t="s">
+      <c r="AE7" s="69" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="75.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="83" t="s">
+      <c r="C8" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="85" t="s">
+      <c r="D8" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="66">
         <v>46288</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="27" t="s">
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="M8" s="96" t="s">
+      <c r="M8" s="91" t="s">
         <v>150</v>
       </c>
-      <c r="N8" s="96" t="s">
+      <c r="N8" s="91" t="s">
         <v>161</v>
       </c>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="70">
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="66">
         <v>46289</v>
       </c>
-      <c r="S8" s="65"/>
-      <c r="T8" s="65"/>
-      <c r="U8" s="65"/>
-      <c r="V8" s="65"/>
-      <c r="W8" s="65"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="96" t="s">
+      <c r="S8" s="61"/>
+      <c r="T8" s="61"/>
+      <c r="U8" s="61"/>
+      <c r="V8" s="61"/>
+      <c r="W8" s="61"/>
+      <c r="X8" s="61"/>
+      <c r="Y8" s="91" t="s">
         <v>159</v>
       </c>
-      <c r="Z8" s="65" t="s">
+      <c r="Z8" s="61" t="s">
         <v>149</v>
       </c>
       <c r="AA8" s="3" t="s">
@@ -1805,90 +1808,94 @@
       <c r="AB8" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AC8" s="73" t="s">
+      <c r="AC8" s="69" t="s">
         <v>176</v>
       </c>
-      <c r="AD8" s="73" t="s">
+      <c r="AD8" s="69" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="39"/>
-      <c r="B9" s="84"/>
-      <c r="C9" s="84"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="41"/>
-      <c r="R9" s="40" t="s">
+      <c r="AE8" s="69" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" ht="0.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="35"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="38"/>
-      <c r="Y9" s="38"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="38"/>
-      <c r="AB9" s="38"/>
-      <c r="AC9" s="38"/>
-      <c r="AD9" s="38"/>
-    </row>
-    <row r="10" spans="1:30" ht="142" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="97" t="s">
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="34"/>
+      <c r="X9" s="34"/>
+      <c r="Y9" s="34"/>
+      <c r="Z9" s="34"/>
+      <c r="AA9" s="34"/>
+      <c r="AB9" s="34"/>
+      <c r="AC9" s="34"/>
+      <c r="AD9" s="34"/>
+      <c r="AE9" s="34"/>
+    </row>
+    <row r="10" spans="1:32" ht="142" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="83" t="s">
+      <c r="C10" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="85" t="s">
+      <c r="D10" s="80" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="70">
+      <c r="E10" s="66">
         <v>46290</v>
       </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="96" t="s">
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="91" t="s">
         <v>151</v>
       </c>
-      <c r="N10" s="96" t="s">
+      <c r="N10" s="91" t="s">
         <v>161</v>
       </c>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="70">
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="66">
         <v>46292</v>
       </c>
-      <c r="S10" s="65"/>
-      <c r="T10" s="65"/>
-      <c r="U10" s="65"/>
-      <c r="V10" s="65"/>
-      <c r="W10" s="65"/>
-      <c r="X10" s="65"/>
-      <c r="Y10" s="65"/>
-      <c r="Z10" s="96" t="s">
+      <c r="S10" s="61"/>
+      <c r="T10" s="61"/>
+      <c r="U10" s="61"/>
+      <c r="V10" s="61"/>
+      <c r="W10" s="61"/>
+      <c r="X10" s="61"/>
+      <c r="Y10" s="61"/>
+      <c r="Z10" s="91" t="s">
         <v>166</v>
       </c>
       <c r="AA10" s="3" t="s">
@@ -1900,325 +1907,341 @@
       <c r="AC10" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="AD10" s="73" t="s">
+      <c r="AD10" s="69" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" ht="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="39"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="40" t="s">
+      <c r="AE10" s="69" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="35"/>
+      <c r="B11" s="79"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="41"/>
-      <c r="R11" s="40" t="s">
+      <c r="F11" s="32"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
+      <c r="O11" s="37"/>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="37"/>
+      <c r="R11" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="38"/>
-      <c r="Y11" s="38"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="38"/>
-      <c r="AB11" s="38"/>
-      <c r="AC11" s="38"/>
-      <c r="AD11" s="38"/>
-    </row>
-    <row r="12" spans="1:30" ht="172" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="30" t="s">
+      <c r="S11" s="38"/>
+      <c r="T11" s="38"/>
+      <c r="U11" s="38"/>
+      <c r="V11" s="38"/>
+      <c r="W11" s="34"/>
+      <c r="X11" s="34"/>
+      <c r="Y11" s="34"/>
+      <c r="Z11" s="34"/>
+      <c r="AA11" s="34"/>
+      <c r="AB11" s="34"/>
+      <c r="AC11" s="34"/>
+      <c r="AD11" s="34"/>
+      <c r="AE11" s="34"/>
+    </row>
+    <row r="12" spans="1:32" s="96" customFormat="1" ht="172" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="102" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="84" t="s">
+      <c r="B12" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="84" t="s">
+      <c r="C12" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="86" t="s">
+      <c r="D12" s="80" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="32">
+      <c r="E12" s="21">
         <v>46290</v>
       </c>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="80" t="s">
+      <c r="F12" s="22"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="34"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="104">
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="66">
         <v>46292</v>
       </c>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="5" t="s">
+      <c r="S12" s="61"/>
+      <c r="T12" s="61"/>
+      <c r="U12" s="61"/>
+      <c r="V12" s="61"/>
+      <c r="W12" s="61"/>
+      <c r="X12" s="61"/>
+      <c r="Y12" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="Z12" s="5" t="s">
+      <c r="Z12" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AA12" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AB12" s="5" t="s">
+      <c r="AB12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AC12" s="5" t="s">
+      <c r="AC12" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="AD12" s="5" t="s">
+      <c r="AD12" s="3" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" ht="122" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="30" t="s">
+      <c r="AE12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF12" s="103"/>
+    </row>
+    <row r="13" spans="1:32" s="96" customFormat="1" ht="122" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="84" t="s">
+      <c r="B13" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="84" t="s">
+      <c r="C13" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="80" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="21">
         <v>45197</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="80" t="s">
+      <c r="F13" s="22"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="95" t="s">
         <v>119</v>
       </c>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="104">
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="66">
         <v>46295</v>
       </c>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="5" t="s">
+      <c r="S13" s="61"/>
+      <c r="T13" s="61"/>
+      <c r="U13" s="61"/>
+      <c r="V13" s="61"/>
+      <c r="W13" s="61"/>
+      <c r="X13" s="61"/>
+      <c r="Y13" s="61"/>
+      <c r="Z13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AA13" s="5" t="s">
+      <c r="AA13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AB13" s="5" t="s">
+      <c r="AB13" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="AC13" s="5" t="s">
+      <c r="AC13" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="AD13" s="5" t="s">
+      <c r="AD13" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" s="101" customFormat="1" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="66" t="s">
+      <c r="AE13" s="69" t="s">
+        <v>93</v>
+      </c>
+      <c r="AF13" s="103"/>
+    </row>
+    <row r="14" spans="1:32" s="96" customFormat="1" ht="56.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="85" t="s">
+      <c r="D14" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="70">
+      <c r="E14" s="66">
         <v>46296</v>
       </c>
-      <c r="F14" s="23"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="98" t="s">
+      <c r="F14" s="22"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="93" t="s">
         <v>163</v>
       </c>
-      <c r="M14" s="24"/>
-      <c r="N14" s="99" t="s">
+      <c r="M14" s="23"/>
+      <c r="N14" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="O14" s="99" t="s">
+      <c r="O14" s="94" t="s">
         <v>171</v>
       </c>
-      <c r="P14" s="100" t="s">
+      <c r="P14" s="95" t="s">
         <v>119</v>
       </c>
-      <c r="Q14" s="100"/>
-      <c r="R14" s="22">
+      <c r="Q14" s="95"/>
+      <c r="R14" s="21">
         <v>46300</v>
       </c>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
-      <c r="W14" s="65"/>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="65"/>
-      <c r="Z14" s="65"/>
-      <c r="AA14" s="65"/>
-      <c r="AB14" s="26" t="s">
+      <c r="S14" s="61"/>
+      <c r="T14" s="61"/>
+      <c r="U14" s="61"/>
+      <c r="V14" s="61"/>
+      <c r="W14" s="61"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="61"/>
+      <c r="AA14" s="61"/>
+      <c r="AB14" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="AC14" s="73" t="s">
+      <c r="AC14" s="69" t="s">
         <v>178</v>
       </c>
-      <c r="AD14" s="73"/>
-    </row>
-    <row r="15" spans="1:30" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="39"/>
-      <c r="B15" s="71"/>
-      <c r="C15" s="84"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="72"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
-      <c r="U15" s="42"/>
-      <c r="V15" s="42"/>
-      <c r="W15" s="42"/>
-      <c r="X15" s="42"/>
-      <c r="Y15" s="42"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="42"/>
-      <c r="AB15" s="42"/>
-      <c r="AC15" s="42"/>
-      <c r="AD15" s="42"/>
-    </row>
-    <row r="16" spans="1:30" ht="34" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="43" t="s">
+      <c r="AD14" s="69"/>
+      <c r="AE14" s="69"/>
+      <c r="AF14" s="103"/>
+    </row>
+    <row r="15" spans="1:32" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="35"/>
+      <c r="B15" s="67"/>
+      <c r="C15" s="79"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="37"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="37"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+    </row>
+    <row r="16" spans="1:32" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="47"/>
-      <c r="L16" s="47"/>
-      <c r="M16" s="47"/>
-      <c r="N16" s="47"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="48"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="48"/>
-      <c r="V16" s="48"/>
-      <c r="W16" s="48"/>
-      <c r="X16" s="48"/>
-      <c r="Y16" s="48"/>
-      <c r="Z16" s="48"/>
-      <c r="AA16" s="48"/>
-      <c r="AB16" s="48"/>
-      <c r="AC16" s="48"/>
-      <c r="AD16" s="48"/>
-    </row>
-    <row r="17" spans="1:30" ht="134" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="66" t="s">
+      <c r="E16" s="41"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="44"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="44"/>
+      <c r="X16" s="44"/>
+      <c r="Y16" s="44"/>
+      <c r="Z16" s="44"/>
+      <c r="AA16" s="44"/>
+      <c r="AB16" s="44"/>
+      <c r="AC16" s="44"/>
+      <c r="AD16" s="44"/>
+      <c r="AE16" s="44"/>
+    </row>
+    <row r="17" spans="1:31" ht="134" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="83" t="s">
+      <c r="C17" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="85" t="s">
+      <c r="D17" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="21">
         <v>46274</v>
       </c>
-      <c r="F17" s="56" t="s">
+      <c r="F17" s="52" t="s">
         <v>94</v>
       </c>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="28"/>
-      <c r="P17" s="28"/>
-      <c r="Q17" s="28"/>
-      <c r="R17" s="70">
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="66">
         <v>46278</v>
       </c>
       <c r="S17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T17" s="6" t="s">
+      <c r="T17" s="5" t="s">
         <v>133</v>
       </c>
       <c r="U17" s="3" t="s">
@@ -2230,190 +2253,195 @@
       <c r="W17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="X17" s="73" t="s">
+      <c r="X17" s="69" t="s">
         <v>139</v>
       </c>
-      <c r="Y17" s="79" t="s">
+      <c r="Y17" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="Z17" s="79" t="s">
+      <c r="Z17" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="AA17" s="79" t="s">
+      <c r="AA17" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="AB17" s="79" t="s">
+      <c r="AB17" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="AC17" s="79" t="s">
+      <c r="AC17" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="AD17" s="79" t="s">
+      <c r="AD17" s="75" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" ht="99.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="66" t="s">
+      <c r="AE17" s="75" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" ht="99.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="83" t="s">
+      <c r="C18" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="85" t="s">
+      <c r="D18" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="E18" s="70">
+      <c r="E18" s="66">
         <v>46279</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="97" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="103" t="s">
+      <c r="G18" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="H18" s="103" t="s">
+      <c r="H18" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="I18" s="103" t="s">
+      <c r="I18" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="J18" s="74" t="s">
+      <c r="J18" s="70" t="s">
         <v>130</v>
       </c>
-      <c r="K18" s="74" t="s">
+      <c r="K18" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="L18" s="28"/>
-      <c r="M18" s="28"/>
-      <c r="N18" s="28"/>
-      <c r="O18" s="28"/>
-      <c r="P18" s="28"/>
-      <c r="Q18" s="28"/>
-      <c r="R18" s="70">
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="27"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="27"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="66">
         <v>46280</v>
       </c>
-      <c r="S18" s="6" t="s">
+      <c r="S18" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="T18" s="6" t="s">
+      <c r="T18" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="U18" s="6" t="s">
+      <c r="U18" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="V18" s="6" t="s">
+      <c r="V18" s="5" t="s">
         <v>132</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="X18" s="75" t="s">
+      <c r="X18" s="71" t="s">
         <v>136</v>
       </c>
-      <c r="Y18" s="73" t="s">
+      <c r="Y18" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="Z18" s="73"/>
-      <c r="AA18" s="73"/>
-      <c r="AB18" s="73"/>
-      <c r="AC18" s="73"/>
-      <c r="AD18" s="73"/>
-    </row>
-    <row r="19" spans="1:30" ht="53" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="66" t="s">
+      <c r="Z18" s="69"/>
+      <c r="AA18" s="69"/>
+      <c r="AB18" s="69"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="69"/>
+      <c r="AE18" s="69"/>
+    </row>
+    <row r="19" spans="1:31" ht="53" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="85" t="s">
+      <c r="D19" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="E19" s="68">
+      <c r="E19" s="64">
         <v>46282</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="F19" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="28"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="22">
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="27"/>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="27"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="27"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="21">
         <v>46288</v>
       </c>
-      <c r="S19" s="26" t="s">
+      <c r="S19" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="T19" s="26" t="s">
+      <c r="T19" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="U19" s="26" t="s">
+      <c r="U19" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="V19" s="26" t="s">
+      <c r="V19" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="W19" s="10" t="s">
+      <c r="W19" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X19" s="69"/>
-      <c r="Y19" s="69"/>
-      <c r="Z19" s="69"/>
-      <c r="AA19" s="69"/>
-      <c r="AB19" s="69"/>
-      <c r="AC19" s="69"/>
-      <c r="AD19" s="69"/>
-    </row>
-    <row r="20" spans="1:30" ht="68" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="66" t="s">
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
+      <c r="Z19" s="65"/>
+      <c r="AA19" s="65"/>
+      <c r="AB19" s="65"/>
+      <c r="AC19" s="65"/>
+      <c r="AD19" s="65"/>
+      <c r="AE19" s="65"/>
+    </row>
+    <row r="20" spans="1:31" ht="68" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="85" t="s">
+      <c r="D20" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="68">
+      <c r="E20" s="64">
         <v>46282</v>
       </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="56" t="s">
+      <c r="F20" s="22"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="52" t="s">
         <v>119</v>
       </c>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="22">
+      <c r="J20" s="27"/>
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="21">
         <v>46288</v>
       </c>
-      <c r="S20" s="65"/>
-      <c r="T20" s="65"/>
-      <c r="U20" s="65"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="61"/>
+      <c r="U20" s="61"/>
       <c r="V20" s="3" t="s">
         <v>95</v>
       </c>
@@ -2423,199 +2451,203 @@
       <c r="X20" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="Y20" s="73" t="s">
+      <c r="Y20" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Z20" s="73"/>
-      <c r="AA20" s="73"/>
-      <c r="AB20" s="73"/>
-      <c r="AC20" s="73"/>
-      <c r="AD20" s="73"/>
-    </row>
-    <row r="21" spans="1:30" ht="54.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="66" t="s">
+      <c r="Z20" s="69"/>
+      <c r="AA20" s="69"/>
+      <c r="AB20" s="69"/>
+      <c r="AC20" s="69"/>
+      <c r="AD20" s="69"/>
+      <c r="AE20" s="69"/>
+    </row>
+    <row r="21" spans="1:31" ht="54.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="78" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="21">
         <v>46276</v>
       </c>
-      <c r="F21" s="56" t="s">
+      <c r="F21" s="52" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-      <c r="N21" s="28"/>
-      <c r="O21" s="28"/>
-      <c r="P21" s="28"/>
-      <c r="Q21" s="28"/>
-      <c r="R21" s="22">
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="27"/>
+      <c r="N21" s="27"/>
+      <c r="O21" s="27"/>
+      <c r="P21" s="27"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="21">
         <v>46288</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="S21" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="T21" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="U21" s="6" t="s">
+      <c r="U21" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="V21" s="6" t="s">
+      <c r="V21" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="W21" s="10" t="s">
+      <c r="W21" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X21" s="67"/>
-      <c r="Y21" s="67"/>
-      <c r="Z21" s="67"/>
-      <c r="AA21" s="67"/>
-      <c r="AB21" s="67"/>
-      <c r="AC21" s="67"/>
-      <c r="AD21" s="67"/>
-    </row>
-    <row r="22" spans="1:30" ht="43" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="66" t="s">
+      <c r="X21" s="63"/>
+      <c r="Y21" s="63"/>
+      <c r="Z21" s="63"/>
+      <c r="AA21" s="63"/>
+      <c r="AB21" s="63"/>
+      <c r="AC21" s="63"/>
+      <c r="AD21" s="63"/>
+      <c r="AE21" s="63"/>
+    </row>
+    <row r="22" spans="1:31" ht="43" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="62" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="78" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="85" t="s">
+      <c r="D22" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="21">
         <v>46289</v>
       </c>
-      <c r="F22" s="23"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="7" t="s">
+      <c r="F22" s="22"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="22">
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="21">
         <v>46289</v>
       </c>
-      <c r="S22" s="65"/>
-      <c r="T22" s="65"/>
-      <c r="U22" s="65"/>
-      <c r="V22" s="65"/>
-      <c r="W22" s="10" t="s">
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="61"/>
+      <c r="W22" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="65"/>
-    </row>
-    <row r="23" spans="1:30" ht="38" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="39" t="s">
+      <c r="X22" s="61"/>
+      <c r="Y22" s="61"/>
+      <c r="Z22" s="61"/>
+      <c r="AA22" s="61"/>
+      <c r="AB22" s="61"/>
+      <c r="AC22" s="61"/>
+      <c r="AD22" s="61"/>
+      <c r="AE22" s="61"/>
+    </row>
+    <row r="23" spans="1:31" ht="38" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="84" t="s">
+      <c r="C23" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="86" t="s">
+      <c r="D23" s="81" t="s">
         <v>137</v>
       </c>
-      <c r="E23" s="32">
+      <c r="E23" s="31">
         <v>46275</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="G23" s="49"/>
-      <c r="H23" s="49"/>
-      <c r="I23" s="49"/>
-      <c r="J23" s="49"/>
-      <c r="K23" s="49"/>
-      <c r="L23" s="49"/>
-      <c r="M23" s="49"/>
-      <c r="N23" s="49"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="49"/>
-      <c r="Q23" s="49"/>
-      <c r="R23" s="32">
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="31">
         <v>46319</v>
       </c>
-      <c r="S23" s="37"/>
-      <c r="T23" s="37"/>
-      <c r="U23" s="37"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="37"/>
-      <c r="X23" s="37"/>
-      <c r="Y23" s="37"/>
-      <c r="Z23" s="37"/>
-      <c r="AA23" s="37"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="37"/>
-      <c r="AD23" s="37"/>
-    </row>
-    <row r="24" spans="1:30" ht="44.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="51" t="s">
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="33"/>
+      <c r="AB23" s="33"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="33"/>
+      <c r="AE23" s="33"/>
+    </row>
+    <row r="24" spans="1:31" ht="44.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="85" t="s">
+      <c r="C24" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="85" t="s">
+      <c r="D24" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="21">
         <v>46275</v>
       </c>
-      <c r="F24" s="53" t="s">
+      <c r="F24" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="G24" s="54"/>
-      <c r="H24" s="54"/>
-      <c r="I24" s="54"/>
-      <c r="J24" s="54"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="54"/>
-      <c r="M24" s="54"/>
-      <c r="N24" s="54"/>
-      <c r="O24" s="54"/>
-      <c r="P24" s="54"/>
-      <c r="Q24" s="54"/>
-      <c r="R24" s="70">
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="66">
         <v>46278</v>
       </c>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="9" t="s">
         <v>93</v>
       </c>
       <c r="T24" s="3"/>
@@ -2629,51 +2661,52 @@
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
-    </row>
-    <row r="25" spans="1:30" ht="34" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="51" t="s">
+      <c r="AE24" s="3"/>
+    </row>
+    <row r="25" spans="1:31" ht="34" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="47" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="85" t="s">
+      <c r="C25" s="80" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="85" t="s">
+      <c r="D25" s="80" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="28">
         <v>46278</v>
       </c>
-      <c r="F25" s="55" t="s">
+      <c r="F25" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="55" t="s">
+      <c r="G25" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="56"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="56"/>
-      <c r="R25" s="29">
+      <c r="I25" s="52"/>
+      <c r="J25" s="52"/>
+      <c r="K25" s="52"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
+      <c r="O25" s="52"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="28">
         <v>46281</v>
       </c>
-      <c r="S25" s="6" t="s">
+      <c r="S25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="T25" s="6" t="s">
+      <c r="T25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="U25" s="10" t="s">
+      <c r="U25" s="9" t="s">
         <v>93</v>
       </c>
       <c r="V25" s="3"/>
@@ -2685,345 +2718,353 @@
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
-    </row>
-    <row r="26" spans="1:30" ht="77.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="66" t="s">
+      <c r="AE25" s="3"/>
+    </row>
+    <row r="26" spans="1:31" ht="77.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="62" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="C26" s="85" t="s">
+      <c r="C26" s="80" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="85" t="s">
+      <c r="D26" s="80" t="s">
         <v>104</v>
       </c>
-      <c r="E26" s="68">
+      <c r="E26" s="64">
         <v>46281</v>
       </c>
-      <c r="F26" s="56"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="53" t="s">
+      <c r="F26" s="52"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="70">
+      <c r="I26" s="27"/>
+      <c r="J26" s="27"/>
+      <c r="K26" s="27"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="27"/>
+      <c r="N26" s="27"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="66">
         <v>46285</v>
       </c>
-      <c r="S26" s="76"/>
-      <c r="T26" s="76"/>
-      <c r="U26" s="6" t="s">
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="V26" s="6" t="s">
+      <c r="V26" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="W26" s="6" t="s">
+      <c r="W26" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="X26" s="75" t="s">
+      <c r="X26" s="71" t="s">
         <v>138</v>
       </c>
-      <c r="Y26" s="73" t="s">
+      <c r="Y26" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Z26" s="73"/>
-      <c r="AA26" s="73"/>
-      <c r="AB26" s="73"/>
-      <c r="AC26" s="73"/>
-      <c r="AD26" s="73"/>
-    </row>
-    <row r="27" spans="1:30" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="30" t="s">
+      <c r="Z26" s="69"/>
+      <c r="AA26" s="69"/>
+      <c r="AB26" s="69"/>
+      <c r="AC26" s="69"/>
+      <c r="AD26" s="69"/>
+      <c r="AE26" s="69"/>
+    </row>
+    <row r="27" spans="1:31" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="102" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="57" t="s">
+      <c r="B27" s="48" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="86" t="s">
+      <c r="C27" s="80" t="s">
         <v>116</v>
       </c>
-      <c r="D27" s="86" t="s">
+      <c r="D27" s="80" t="s">
         <v>153</v>
       </c>
-      <c r="E27" s="105">
+      <c r="E27" s="104">
         <v>46286</v>
       </c>
-      <c r="F27" s="36"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="49"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="78" t="s">
+      <c r="F27" s="52"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="65"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="L27" s="78" t="s">
+      <c r="L27" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="M27" s="49"/>
-      <c r="N27" s="49"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="49"/>
-      <c r="R27" s="104">
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="66">
         <v>46293</v>
       </c>
-      <c r="S27" s="37"/>
-      <c r="T27" s="37"/>
-      <c r="U27" s="37"/>
-      <c r="V27" s="37"/>
-      <c r="W27" s="37"/>
-      <c r="X27" s="37"/>
-      <c r="Y27" s="77" t="s">
+      <c r="S27" s="61"/>
+      <c r="T27" s="61"/>
+      <c r="U27" s="61"/>
+      <c r="V27" s="61"/>
+      <c r="W27" s="61"/>
+      <c r="X27" s="61"/>
+      <c r="Y27" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="Z27" s="77" t="s">
+      <c r="Z27" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="AA27" s="77" t="s">
+      <c r="AA27" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="AB27" s="77" t="s">
+      <c r="AB27" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="AC27" s="77" t="s">
+      <c r="AC27" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="AD27" s="77" t="s">
+      <c r="AD27" s="5" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
+      <c r="AE27" s="69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="57" t="s">
+      <c r="B28" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="86" t="s">
+      <c r="C28" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="D28" s="86" t="s">
+      <c r="D28" s="81" t="s">
         <v>154</v>
       </c>
-      <c r="E28" s="64">
+      <c r="E28" s="60">
         <v>46294</v>
       </c>
-      <c r="F28" s="59"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="78" t="s">
+      <c r="F28" s="55"/>
+      <c r="G28" s="54"/>
+      <c r="H28" s="54"/>
+      <c r="I28" s="45"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="32">
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+      <c r="R28" s="31">
         <v>46319</v>
       </c>
-      <c r="S28" s="37"/>
-      <c r="T28" s="37"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="37"/>
-      <c r="Z28" s="77" t="s">
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="AA28" s="77" t="s">
+      <c r="AA28" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="AB28" s="77" t="s">
+      <c r="AB28" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="AC28" s="77" t="s">
+      <c r="AC28" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="AD28" s="77" t="s">
+      <c r="AD28" s="73" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="D29" s="89"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="60"/>
-      <c r="S29" s="61"/>
-      <c r="T29" s="61"/>
-      <c r="U29" s="61"/>
-      <c r="V29" s="61"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="16"/>
-      <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A30" s="16"/>
-      <c r="B30" s="16"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="60"/>
-      <c r="S30" s="61"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="61"/>
-      <c r="V30" s="61"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-      <c r="AB30" s="16"/>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="16"/>
-    </row>
-    <row r="31" spans="1:30" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16"/>
-      <c r="B31" s="62" t="s">
+      <c r="AE28" s="73" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="D29" s="84"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="56"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
+      <c r="O29" s="15"/>
+      <c r="P29" s="15"/>
+      <c r="Q29" s="15"/>
+      <c r="R29" s="56"/>
+      <c r="S29" s="57"/>
+      <c r="T29" s="57"/>
+      <c r="U29" s="57"/>
+      <c r="V29" s="57"/>
+      <c r="W29" s="15"/>
+      <c r="X29" s="15"/>
+      <c r="Y29" s="15"/>
+      <c r="Z29" s="15"/>
+      <c r="AA29" s="15"/>
+      <c r="AB29" s="15"/>
+      <c r="AC29" s="15"/>
+      <c r="AD29" s="15"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
+      <c r="O30" s="15"/>
+      <c r="P30" s="15"/>
+      <c r="Q30" s="15"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="57"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="15"/>
+      <c r="X30" s="15"/>
+      <c r="Y30" s="15"/>
+      <c r="Z30" s="15"/>
+      <c r="AA30" s="15"/>
+      <c r="AB30" s="15"/>
+      <c r="AC30" s="15"/>
+      <c r="AD30" s="15"/>
+    </row>
+    <row r="31" spans="1:31" ht="128.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="15"/>
+      <c r="B31" s="58" t="s">
         <v>88</v>
       </c>
-      <c r="C31" s="88" t="s">
+      <c r="C31" s="83" t="s">
         <v>89</v>
       </c>
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="E31" s="60"/>
-      <c r="F31" s="60"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="60"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="61"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="16"/>
-      <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="60"/>
-      <c r="S32" s="61"/>
-      <c r="T32" s="61"/>
-      <c r="U32" s="61"/>
-      <c r="V32" s="61"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="16"/>
-      <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="16"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="56"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="15"/>
+      <c r="P31" s="15"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="56"/>
+      <c r="S31" s="57"/>
+      <c r="T31" s="57"/>
+      <c r="U31" s="57"/>
+      <c r="V31" s="57"/>
+      <c r="W31" s="15"/>
+      <c r="X31" s="15"/>
+      <c r="Y31" s="15"/>
+      <c r="Z31" s="15"/>
+      <c r="AA31" s="15"/>
+      <c r="AB31" s="15"/>
+      <c r="AC31" s="15"/>
+      <c r="AD31" s="15"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.35">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="56"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
+      <c r="O32" s="15"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="15"/>
+      <c r="R32" s="56"/>
+      <c r="S32" s="57"/>
+      <c r="T32" s="57"/>
+      <c r="U32" s="57"/>
+      <c r="V32" s="57"/>
+      <c r="W32" s="15"/>
+      <c r="X32" s="15"/>
+      <c r="Y32" s="15"/>
+      <c r="Z32" s="15"/>
+      <c r="AA32" s="15"/>
+      <c r="AB32" s="15"/>
+      <c r="AC32" s="15"/>
+      <c r="AD32" s="15"/>
     </row>
     <row r="33" spans="1:30" ht="173" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="16"/>
-      <c r="B33" s="63" t="s">
+      <c r="A33" s="15"/>
+      <c r="B33" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="C33" s="89" t="s">
+      <c r="C33" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="89" t="s">
+      <c r="D33" s="84" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="60"/>
-      <c r="F33" s="60"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="60"/>
-      <c r="S33" s="61"/>
-      <c r="T33" s="61"/>
-      <c r="U33" s="61"/>
-      <c r="V33" s="61"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
-      <c r="AC33" s="16"/>
-      <c r="AD33" s="16"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="56"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="15"/>
+      <c r="O33" s="15"/>
+      <c r="P33" s="15"/>
+      <c r="Q33" s="15"/>
+      <c r="R33" s="56"/>
+      <c r="S33" s="57"/>
+      <c r="T33" s="57"/>
+      <c r="U33" s="57"/>
+      <c r="V33" s="57"/>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
+      <c r="Y33" s="15"/>
+      <c r="Z33" s="15"/>
+      <c r="AA33" s="15"/>
+      <c r="AB33" s="15"/>
+      <c r="AC33" s="15"/>
+      <c r="AD33" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="1">
